--- a/output/audit_reports/B2G_Numbers_Audit.xlsx
+++ b/output/audit_reports/B2G_Numbers_Audit.xlsx
@@ -885,68 +885,60 @@
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="2" t="n">
+      <c r="B16" t="n">
         <v>3</v>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3.0000</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" t="n">
         <v>9</v>
       </c>
-      <c r="B17" s="2" t="n">
+      <c r="B17" t="n">
         <v>3</v>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>788,000</t>
         </is>
       </c>
-      <c r="D17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>788,000.0000</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>788,000</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
         <is>
           <t>บ.  uA} 788,000 au งบประมาณ ผู| |</t>
         </is>
@@ -989,180 +981,160 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" t="n">
         <v>9</v>
       </c>
-      <c r="B19" s="2" t="n">
+      <c r="B19" t="n">
         <v>3</v>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
       </c>
-      <c r="D19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>4.4000</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" t="n">
         <v>9</v>
       </c>
-      <c r="B20" s="2" t="n">
+      <c r="B20" t="n">
         <v>3</v>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>3.9</t>
         </is>
       </c>
-      <c r="D20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3.9000</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
         <is>
           <t>ล / GDP 3.9 4</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" t="n">
         <v>9</v>
       </c>
-      <c r="B21" s="2" t="n">
+      <c r="B21" t="n">
         <v>3</v>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
       </c>
-      <c r="D21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>3.3000</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
         <is>
           <t>|   3.3 | x        | 2.7</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" t="n">
         <v>9</v>
       </c>
-      <c r="B22" s="2" t="n">
+      <c r="B22" t="n">
         <v>3</v>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>2.7</t>
         </is>
       </c>
-      <c r="D22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>2.7000</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
         <is>
           <t>| 2.7 | 8</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" t="n">
         <v>9</v>
       </c>
-      <c r="B23" s="2" t="n">
+      <c r="B23" t="n">
         <v>3</v>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
       </c>
-      <c r="D23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>2.1000</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
         <is>
           <t>2.1 2 1  ปิีงบประมาณ</t>
         </is>
@@ -1205,180 +1177,160 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" t="n">
         <v>10</v>
       </c>
-      <c r="B25" s="2" t="n">
+      <c r="B25" t="n">
         <v>4</v>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>584,300</t>
         </is>
       </c>
-      <c r="D25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>584,300.0000</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>584,300</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
         <is>
           <t>ดเก็บ 3,584,300 au.  หักลด 584,30</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" t="n">
         <v>10</v>
       </c>
-      <c r="B26" s="2" t="n">
+      <c r="B26" t="n">
         <v>4</v>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>3,788,000</t>
         </is>
       </c>
-      <c r="D26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>3,788,000.0000</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>3,788,000</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
         <is>
           <t>G 2570  3,788,000 au.  ที่มา : กระท</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" t="n">
         <v>10</v>
       </c>
-      <c r="B27" s="2" t="n">
+      <c r="B27" t="n">
         <v>4</v>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>3,584,300</t>
         </is>
       </c>
-      <c r="D27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>3,584,300.0000</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>3,584,300</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
         <is>
           <t>จัดเก็บ 3,584,300 au.  หักลด 584,30</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" t="n">
         <v>10</v>
       </c>
-      <c r="B28" s="2" t="n">
+      <c r="B28" t="n">
         <v>4</v>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>788,000</t>
         </is>
       </c>
-      <c r="D28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>788,000.0000</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>788,000</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
         <is>
           <t>2570  3,788,000 au.  ที่มา : กระท</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" t="n">
         <v>10</v>
       </c>
-      <c r="B29" s="2" t="n">
+      <c r="B29" t="n">
         <v>4</v>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>3,000,000</t>
         </is>
       </c>
-      <c r="D29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>3,000,000.0000</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>3,000,000</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
         <is>
           <t>ินกู้ , 3,000,000 au.  SINUS:N1@UNI</t>
         </is>
@@ -1529,36 +1481,32 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" t="n">
         <v>10</v>
       </c>
-      <c r="B34" s="2" t="n">
+      <c r="B34" t="n">
         <v>4</v>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>155,880</t>
         </is>
       </c>
-      <c r="D34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>155,880.0000</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>155,880</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
         <is>
           <t>500 ลบ. 155,880 au.  REVENUE รายไ</t>
         </is>
@@ -1845,36 +1793,32 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" t="n">
         <v>12</v>
       </c>
-      <c r="B43" s="2" t="n">
+      <c r="B43" t="n">
         <v>6</v>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>151,520</t>
         </is>
       </c>
-      <c r="D43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>151,520.0000</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr"/>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>151,520</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -1949,36 +1893,32 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" t="n">
         <v>12</v>
       </c>
-      <c r="B46" s="2" t="n">
+      <c r="B46" t="n">
         <v>6</v>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>3,788,000</t>
         </is>
       </c>
-      <c r="D46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>3,788,000.0000</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>บาท (ต่อหน่วย)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>3,788,000</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
         <is>
           <t>บประมาณ 3,788,000 ลส้านบาท  ๕รรพ SS</t>
         </is>
@@ -2329,68 +2269,60 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" t="n">
         <v>13</v>
       </c>
-      <c r="B57" s="2" t="n">
+      <c r="B57" t="n">
         <v>7</v>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>407,165.1</t>
         </is>
       </c>
-      <c r="D57" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>407,165.1000</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr"/>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>407,165.1</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" t="n">
         <v>13</v>
       </c>
-      <c r="B58" s="2" t="n">
+      <c r="B58" t="n">
         <v>7</v>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>10.7</t>
         </is>
       </c>
-      <c r="D58" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>10.7000</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr"/>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>10.7</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2425,36 +2357,32 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" t="n">
         <v>13</v>
       </c>
-      <c r="B60" s="2" t="n">
+      <c r="B60" t="n">
         <v>7</v>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>348,427.4</t>
         </is>
       </c>
-      <c r="D60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>348,427.4000</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr"/>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>348,427.4</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2525,180 +2453,160 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" t="n">
         <v>14</v>
       </c>
-      <c r="B63" s="2" t="n">
+      <c r="B63" t="n">
         <v>8</v>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>230,941</t>
         </is>
       </c>
-      <c r="D63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>230,941.0000</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>230,941</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
         <is>
           <t>aso รวม 230,941 เมตร เพื่อลดความเ</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" t="n">
         <v>14</v>
       </c>
-      <c r="B64" s="2" t="n">
+      <c r="B64" t="n">
         <v>8</v>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>7.48</t>
         </is>
       </c>
-      <c r="D64" s="2" t="n">
+      <c r="D64" t="n">
         <v>2</v>
       </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>7.4800</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>จำนวน (ล้านราย)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>7.48</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
         <is>
           <t>- 29 ปี 7.48 ล้านราย และผู้ต้อ</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" t="n">
         <v>14</v>
       </c>
-      <c r="B65" s="2" t="n">
+      <c r="B65" t="n">
         <v>8</v>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>210,000</t>
         </is>
       </c>
-      <c r="D65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>210,000.0000</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>210,000</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
         <is>
           <t>รือนจํา 210,000 sig ได้รับการสร้า</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" t="n">
         <v>14</v>
       </c>
-      <c r="B66" s="2" t="n">
+      <c r="B66" t="n">
         <v>8</v>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>34,334</t>
         </is>
       </c>
-      <c r="D66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>34,334.0000</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>34,334</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
         <is>
           <t>าเสพติด 34,334 aso</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" t="n">
         <v>14</v>
       </c>
-      <c r="B67" s="2" t="n">
+      <c r="B67" t="n">
         <v>8</v>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>10,000</t>
         </is>
       </c>
-      <c r="D67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>10,000.0000</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
         <is>
           <t>ือนจํา 210,000 sig ได้รับการสร้า</t>
         </is>
@@ -2769,36 +2677,32 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" t="n">
         <v>14</v>
       </c>
-      <c r="B70" s="2" t="n">
+      <c r="B70" t="n">
         <v>8</v>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>1,478</t>
         </is>
       </c>
-      <c r="D70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>1,478.0000</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1,478</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
         <is>
           <t>(จชต.) 1,478 หมู่บ้าน ได้รับคว</t>
         </is>
@@ -2869,108 +2773,96 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" t="n">
         <v>14</v>
       </c>
-      <c r="B73" s="2" t="n">
+      <c r="B73" t="n">
         <v>8</v>
       </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>48,000</t>
         </is>
       </c>
-      <c r="D73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>48,000.0000</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>48,000</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
         <is>
           <t>ประชาชน 48,000 sig ได้รับการส่งเ</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" t="n">
         <v>14</v>
       </c>
-      <c r="B74" s="2" t="n">
+      <c r="B74" t="n">
         <v>8</v>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>750,000</t>
         </is>
       </c>
-      <c r="D74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>750,000.0000</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>750,000</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
         <is>
           <t>้อยกว่า 750,000 ครัง ช่วยเหลือผู้</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" t="n">
         <v>14</v>
       </c>
-      <c r="B75" s="2" t="n">
+      <c r="B75" t="n">
         <v>8</v>
       </c>
-      <c r="C75" s="2" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>60,500</t>
         </is>
       </c>
-      <c r="D75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>60,500.0000</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>60,500</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
         <is>
           <t>ทางทะเล 60,500 aso รวม 230,941 เ</t>
         </is>
@@ -3329,36 +3221,32 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" t="n">
         <v>16</v>
       </c>
-      <c r="B87" s="2" t="n">
+      <c r="B87" t="n">
         <v>10</v>
       </c>
-      <c r="C87" s="2" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>1.08</t>
         </is>
       </c>
-      <c r="D87" s="2" t="n">
+      <c r="D87" t="n">
         <v>2</v>
       </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>1.0800</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>จำนวน (ล้านคน)</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
         <is>
           <t>ละ อสม. 1.08 ล้านคน ๑ พพัฒนาระ</t>
         </is>
@@ -3777,72 +3665,64 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" t="n">
         <v>17</v>
       </c>
-      <c r="B101" s="2" t="n">
+      <c r="B101" t="n">
         <v>11</v>
       </c>
-      <c r="C101" s="2" t="inlineStr">
+      <c r="C101" t="inlineStr">
         <is>
           <t>10.20</t>
         </is>
       </c>
-      <c r="D101" s="2" t="n">
+      <c r="D101" t="n">
         <v>2</v>
       </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>10.2000</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>จำนวน (ล้านคน)</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>10.20</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
         <is>
           <t>้อยกว่า 10.20 ล้านคน ได้รับการศ</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" t="n">
         <v>17</v>
       </c>
-      <c r="B102" s="2" t="n">
+      <c r="B102" t="n">
         <v>11</v>
       </c>
-      <c r="C102" s="2" t="inlineStr">
+      <c r="C102" t="inlineStr">
         <is>
           <t>1.45</t>
         </is>
       </c>
-      <c r="D102" s="2" t="n">
+      <c r="D102" t="n">
         <v>2</v>
       </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>1.4500</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>จำนวน (ล้านคน)</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
         <is>
           <t>ารศึกษา 1.45 ล้านคน ได้รับทุนก</t>
         </is>
@@ -3913,72 +3793,64 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" t="n">
         <v>17</v>
       </c>
-      <c r="B105" s="2" t="n">
+      <c r="B105" t="n">
         <v>11</v>
       </c>
-      <c r="C105" s="2" t="inlineStr">
+      <c r="C105" t="inlineStr">
         <is>
           <t>2.53</t>
         </is>
       </c>
-      <c r="D105" s="2" t="n">
+      <c r="D105" t="n">
         <v>2</v>
       </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>2.5300</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>จำนวน (ล้านคน)</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr">
         <is>
           <t>0- 6 U) 2.53 ล้านคน ได้รับเงิน</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" t="n">
         <v>17</v>
       </c>
-      <c r="B106" s="2" t="n">
+      <c r="B106" t="n">
         <v>11</v>
       </c>
-      <c r="C106" s="2" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>2.47</t>
         </is>
       </c>
-      <c r="D106" s="2" t="n">
+      <c r="D106" t="n">
         <v>2</v>
       </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>2.4700</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>จำนวน (ล้านคน)</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr">
         <is>
           <t>ู้พิการ 2.47 ล้านคน ได้รับเบี้</t>
         </is>
@@ -4017,36 +3889,32 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" t="n">
         <v>17</v>
       </c>
-      <c r="B108" s="2" t="n">
+      <c r="B108" t="n">
         <v>11</v>
       </c>
-      <c r="C108" s="2" t="inlineStr">
+      <c r="C108" t="inlineStr">
         <is>
           <t>13.47</t>
         </is>
       </c>
-      <c r="D108" s="2" t="n">
+      <c r="D108" t="n">
         <v>2</v>
       </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>13.4700</t>
-        </is>
-      </c>
-      <c r="G108" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>จำนวน (ล้านคน)</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>13.47</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
         <is>
           <t>สูงอายุ 13.47 ล้านคน ได้รับเบี้</t>
         </is>
@@ -4085,72 +3953,64 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" t="n">
         <v>17</v>
       </c>
-      <c r="B110" s="2" t="n">
+      <c r="B110" t="n">
         <v>11</v>
       </c>
-      <c r="C110" s="2" t="inlineStr">
+      <c r="C110" t="inlineStr">
         <is>
           <t>10.14</t>
         </is>
       </c>
-      <c r="D110" s="2" t="n">
+      <c r="D110" t="n">
         <v>2</v>
       </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>10.1400</t>
-        </is>
-      </c>
-      <c r="G110" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>จำนวน (ล้านคน)</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>10.14</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr">
         <is>
           <t>แห่งรัฐ 10.14 ล้านคน  ได้รับเงิ</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" t="n">
         <v>17</v>
       </c>
-      <c r="B111" s="2" t="n">
+      <c r="B111" t="n">
         <v>11</v>
       </c>
-      <c r="C111" s="2" t="inlineStr">
+      <c r="C111" t="inlineStr">
         <is>
           <t>47.17</t>
         </is>
       </c>
-      <c r="D111" s="2" t="n">
+      <c r="D111" t="n">
         <v>2</v>
       </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t>47.1700</t>
-        </is>
-      </c>
-      <c r="G111" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>จำนวน (ล้านคน)</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>47.17</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr">
         <is>
           <t>้วนหน้า 47.17 ล้านคน  แวง  สิทธ</t>
         </is>
@@ -4221,108 +4081,96 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" t="n">
         <v>17</v>
       </c>
-      <c r="B114" s="2" t="n">
+      <c r="B114" t="n">
         <v>11</v>
       </c>
-      <c r="C114" s="2" t="inlineStr">
+      <c r="C114" t="inlineStr">
         <is>
           <t>4.97</t>
         </is>
       </c>
-      <c r="D114" s="2" t="n">
+      <c r="D114" t="n">
         <v>2</v>
       </c>
-      <c r="E114" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>4.9700</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>จำนวน (ล้านคน)</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>4.97</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr">
         <is>
           <t>งภาครัช 4.97 ล้านคน  ๑ พัฒนากา</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" t="n">
         <v>17</v>
       </c>
-      <c r="B115" s="2" t="n">
+      <c r="B115" t="n">
         <v>11</v>
       </c>
-      <c r="C115" s="2" t="inlineStr">
+      <c r="C115" t="inlineStr">
         <is>
           <t>65.92</t>
         </is>
       </c>
-      <c r="D115" s="2" t="n">
+      <c r="D115" t="n">
         <v>2</v>
       </c>
-      <c r="E115" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>65.9200</t>
-        </is>
-      </c>
-      <c r="G115" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>จำนวน (ล้านคน)</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>65.92</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr">
         <is>
           <t>ประชาชน 65.92 ล้านคน ได้รับบริก</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" t="n">
         <v>17</v>
       </c>
-      <c r="B116" s="2" t="n">
+      <c r="B116" t="n">
         <v>11</v>
       </c>
-      <c r="C116" s="2" t="inlineStr">
+      <c r="C116" t="inlineStr">
         <is>
           <t>13.78</t>
         </is>
       </c>
-      <c r="D116" s="2" t="n">
+      <c r="D116" t="n">
         <v>2</v>
       </c>
-      <c r="E116" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>13.7800</t>
-        </is>
-      </c>
-      <c r="G116" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>จำนวน (ล้านคน)</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>13.78</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr">
         <is>
           <t>คองทุนข 13.78 ล้านคน  สิทธิประโ</t>
         </is>
@@ -4361,36 +4209,32 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" t="n">
         <v>18</v>
       </c>
-      <c r="B118" s="2" t="n">
+      <c r="B118" t="n">
         <v>12</v>
       </c>
-      <c r="C118" s="2" t="inlineStr">
+      <c r="C118" t="inlineStr">
         <is>
           <t>9.44</t>
         </is>
       </c>
-      <c r="D118" s="2" t="n">
+      <c r="D118" t="n">
         <v>2</v>
       </c>
-      <c r="E118" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F118" s="2" t="inlineStr">
-        <is>
-          <t>9.4400</t>
-        </is>
-      </c>
-      <c r="G118" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>9.44</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr">
         <is>
           <t>บประปา  9.44 ล้านลูกบาศก์เมตร</t>
         </is>
@@ -4621,36 +4465,32 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" t="n">
         <v>18</v>
       </c>
-      <c r="B126" s="2" t="n">
+      <c r="B126" t="n">
         <v>12</v>
       </c>
-      <c r="C126" s="2" t="inlineStr">
+      <c r="C126" t="inlineStr">
         <is>
           <t>1,620</t>
         </is>
       </c>
-      <c r="D126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E126" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F126" s="2" t="inlineStr">
-        <is>
-          <t>1,620.0000</t>
-        </is>
-      </c>
-      <c r="G126" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="D126" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>1,620</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr">
         <is>
           <t>ากขึ้น  1,620 ล้านลูกบาศก์เมตร</t>
         </is>
@@ -4737,7 +4577,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>ไม่ทราบหน่วย</t>
+          <t>จำนวน (นับ)</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4753,72 +4593,64 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" t="n">
         <v>18</v>
       </c>
-      <c r="B130" s="2" t="n">
+      <c r="B130" t="n">
         <v>12</v>
       </c>
-      <c r="C130" s="2" t="inlineStr">
+      <c r="C130" t="inlineStr">
         <is>
           <t>1.40</t>
         </is>
       </c>
-      <c r="D130" s="2" t="n">
+      <c r="D130" t="n">
         <v>2</v>
       </c>
-      <c r="E130" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F130" s="2" t="inlineStr">
-        <is>
-          <t>1.4000</t>
-        </is>
-      </c>
-      <c r="G130" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr">
         <is>
           <t>มาตรชาน 1.40 ล้านต้น เฟพื่อควา</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" t="n">
         <v>18</v>
       </c>
-      <c r="B131" s="2" t="n">
+      <c r="B131" t="n">
         <v>12</v>
       </c>
-      <c r="C131" s="2" t="inlineStr">
+      <c r="C131" t="inlineStr">
         <is>
           <t>2.32</t>
         </is>
       </c>
-      <c r="D131" s="2" t="n">
+      <c r="D131" t="n">
         <v>2</v>
       </c>
-      <c r="E131" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F131" s="2" t="inlineStr">
-        <is>
-          <t>2.3200</t>
-        </is>
-      </c>
-      <c r="G131" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>จำนวน (ล้านราย)</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr">
         <is>
           <t>ประชาชน 2.32 ล้านราย เพื่อขับเ</t>
         </is>
@@ -4889,36 +4721,32 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" t="n">
         <v>19</v>
       </c>
-      <c r="B134" s="2" t="n">
+      <c r="B134" t="n">
         <v>13</v>
       </c>
-      <c r="C134" s="2" t="inlineStr">
+      <c r="C134" t="inlineStr">
         <is>
           <t>13.65</t>
         </is>
       </c>
-      <c r="D134" s="2" t="n">
+      <c r="D134" t="n">
         <v>2</v>
       </c>
-      <c r="E134" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F134" s="2" t="inlineStr">
-        <is>
-          <t>13.6500</t>
-        </is>
-      </c>
-      <c r="G134" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>จำนวน (ล้านราย)</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>13.65</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr">
         <is>
           <t>้บริการ 13.65 ล้านราย  ต่อต้านก</t>
         </is>
@@ -6353,36 +6181,32 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n">
+      <c r="A175" t="n">
         <v>23</v>
       </c>
-      <c r="B175" s="2" t="n">
+      <c r="B175" t="n">
         <v>17</v>
       </c>
-      <c r="C175" s="2" t="inlineStr">
+      <c r="C175" t="inlineStr">
         <is>
           <t>1,503,088.8</t>
         </is>
       </c>
-      <c r="D175" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E175" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F175" s="2" t="inlineStr">
-        <is>
-          <t>1,503,088.8000</t>
-        </is>
-      </c>
-      <c r="G175" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H175" s="2" t="inlineStr">
+      <c r="D175" t="n">
+        <v>1</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>1,503,088.8</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr">
         <is>
           <t>ล       1,503,088.8 aun  ด้านเศรษฐกิจ</t>
         </is>
@@ -6569,36 +6393,32 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n">
+      <c r="A181" t="n">
         <v>24</v>
       </c>
-      <c r="B181" s="2" t="n">
+      <c r="B181" t="n">
         <v>18</v>
       </c>
-      <c r="C181" s="2" t="inlineStr">
+      <c r="C181" t="inlineStr">
         <is>
           <t>4,825.3</t>
         </is>
       </c>
-      <c r="D181" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E181" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F181" s="2" t="inlineStr">
-        <is>
-          <t>4,825.3000</t>
-        </is>
-      </c>
-      <c r="G181" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H181" s="2" t="inlineStr"/>
+      <c r="D181" t="n">
+        <v>1</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>4,825.3</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
@@ -6637,72 +6457,64 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n">
+      <c r="A183" t="n">
         <v>24</v>
       </c>
-      <c r="B183" s="2" t="n">
+      <c r="B183" t="n">
         <v>18</v>
       </c>
-      <c r="C183" s="2" t="inlineStr">
+      <c r="C183" t="inlineStr">
         <is>
           <t>185,939.3</t>
         </is>
       </c>
-      <c r="D183" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E183" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F183" s="2" t="inlineStr">
-        <is>
-          <t>185,939.3000</t>
-        </is>
-      </c>
-      <c r="G183" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H183" s="2" t="inlineStr">
+      <c r="D183" t="n">
+        <v>1</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>185,939.3</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr">
         <is>
           <t>185,939.3 au. ด้านการค้า “เ</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n">
+      <c r="A184" t="n">
         <v>24</v>
       </c>
-      <c r="B184" s="2" t="n">
+      <c r="B184" t="n">
         <v>18</v>
       </c>
-      <c r="C184" s="2" t="inlineStr">
+      <c r="C184" t="inlineStr">
         <is>
           <t>11,264.1</t>
         </is>
       </c>
-      <c r="D184" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E184" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F184" s="2" t="inlineStr">
-        <is>
-          <t>11,264.1000</t>
-        </is>
-      </c>
-      <c r="G184" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H184" s="2" t="inlineStr">
+      <c r="D184" t="n">
+        <v>1</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>11,264.1</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr">
         <is>
           <t>11,264.1 au.  ค้านการต่างป</t>
         </is>
@@ -6745,36 +6557,32 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n">
+      <c r="A186" t="n">
         <v>24</v>
       </c>
-      <c r="B186" s="2" t="n">
+      <c r="B186" t="n">
         <v>18</v>
       </c>
-      <c r="C186" s="2" t="inlineStr">
+      <c r="C186" t="inlineStr">
         <is>
           <t>436,287.9</t>
         </is>
       </c>
-      <c r="D186" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E186" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F186" s="2" t="inlineStr">
-        <is>
-          <t>436,287.9000</t>
-        </is>
-      </c>
-      <c r="G186" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H186" s="2" t="inlineStr">
+      <c r="D186" t="n">
+        <v>1</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>436,287.9</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr">
         <is>
           <t>436,287.9 au.  สร้างโอกาสกา</t>
         </is>
@@ -6817,36 +6625,32 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="n">
+      <c r="A188" t="n">
         <v>24</v>
       </c>
-      <c r="B188" s="2" t="n">
+      <c r="B188" t="n">
         <v>18</v>
       </c>
-      <c r="C188" s="2" t="inlineStr">
+      <c r="C188" t="inlineStr">
         <is>
           <t>1,117.6</t>
         </is>
       </c>
-      <c r="D188" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E188" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F188" s="2" t="inlineStr">
-        <is>
-          <t>1,117.6000</t>
-        </is>
-      </c>
-      <c r="G188" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H188" s="2" t="inlineStr">
+      <c r="D188" t="n">
+        <v>1</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>1,117.6</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr">
         <is>
           <t>1,117.6 au.  เสริมสร้างเส</t>
         </is>
@@ -6961,36 +6765,32 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n">
+      <c r="A192" t="n">
         <v>24</v>
       </c>
-      <c r="B192" s="2" t="n">
+      <c r="B192" t="n">
         <v>18</v>
       </c>
-      <c r="C192" s="2" t="inlineStr">
+      <c r="C192" t="inlineStr">
         <is>
           <t>2,114.5</t>
         </is>
       </c>
-      <c r="D192" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E192" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F192" s="2" t="inlineStr">
-        <is>
-          <t>2,114.5000</t>
-        </is>
-      </c>
-      <c r="G192" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H192" s="2" t="inlineStr">
+      <c r="D192" t="n">
+        <v>1</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>2,114.5</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr">
         <is>
           <t>2,114.5 au.  BUDGET BUREA</t>
         </is>
@@ -7177,36 +6977,32 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n">
+      <c r="A198" t="n">
         <v>25</v>
       </c>
-      <c r="B198" s="2" t="n">
+      <c r="B198" t="n">
         <v>19</v>
       </c>
-      <c r="C198" s="2" t="inlineStr">
+      <c r="C198" t="inlineStr">
         <is>
           <t>4,940.4</t>
         </is>
       </c>
-      <c r="D198" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E198" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F198" s="2" t="inlineStr">
-        <is>
-          <t>4,940.4000</t>
-        </is>
-      </c>
-      <c r="G198" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H198" s="2" t="inlineStr">
+      <c r="D198" t="n">
+        <v>1</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>4,940.4</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr"/>
+      <c r="H198" t="inlineStr">
         <is>
           <t>4,940.4 au.  ด้านภัยพิบัต</t>
         </is>
@@ -7285,108 +7081,96 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n">
+      <c r="A201" t="n">
         <v>25</v>
       </c>
-      <c r="B201" s="2" t="n">
+      <c r="B201" t="n">
         <v>19</v>
       </c>
-      <c r="C201" s="2" t="inlineStr">
+      <c r="C201" t="inlineStr">
         <is>
           <t>115,694.0</t>
         </is>
       </c>
-      <c r="D201" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E201" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F201" s="2" t="inlineStr">
-        <is>
-          <t>115,694.0000</t>
-        </is>
-      </c>
-      <c r="G201" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H201" s="2" t="inlineStr">
+      <c r="D201" t="n">
+        <v>1</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>115,694.0</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" t="inlineStr">
         <is>
           <t>115,694.0 au. พัฒนาระบบประก</t>
         </is>
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n">
+      <c r="A202" t="n">
         <v>25</v>
       </c>
-      <c r="B202" s="2" t="n">
+      <c r="B202" t="n">
         <v>19</v>
       </c>
-      <c r="C202" s="2" t="inlineStr">
+      <c r="C202" t="inlineStr">
         <is>
           <t>4,800.0</t>
         </is>
       </c>
-      <c r="D202" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E202" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F202" s="2" t="inlineStr">
-        <is>
-          <t>4,800.0000</t>
-        </is>
-      </c>
-      <c r="G202" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H202" s="2" t="inlineStr">
+      <c r="D202" t="n">
+        <v>1</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>4,800.0</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" t="inlineStr">
         <is>
           <t>4,800.0 au. ผลักด้นให้ประ</t>
         </is>
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n">
+      <c r="A203" t="n">
         <v>25</v>
       </c>
-      <c r="B203" s="2" t="n">
+      <c r="B203" t="n">
         <v>19</v>
       </c>
-      <c r="C203" s="2" t="inlineStr">
+      <c r="C203" t="inlineStr">
         <is>
           <t>44,492.1</t>
         </is>
       </c>
-      <c r="D203" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E203" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F203" s="2" t="inlineStr">
-        <is>
-          <t>44,492.1000</t>
-        </is>
-      </c>
-      <c r="G203" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H203" s="2" t="inlineStr">
+      <c r="D203" t="n">
+        <v>1</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>44,492.1</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr"/>
+      <c r="H203" t="inlineStr">
         <is>
           <t>44,492.1 au. การอนุรักษ์แล</t>
         </is>
@@ -7429,72 +7213,64 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="n">
+      <c r="A205" t="n">
         <v>25</v>
       </c>
-      <c r="B205" s="2" t="n">
+      <c r="B205" t="n">
         <v>19</v>
       </c>
-      <c r="C205" s="2" t="inlineStr">
+      <c r="C205" t="inlineStr">
         <is>
           <t>25,537.2</t>
         </is>
       </c>
-      <c r="D205" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E205" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F205" s="2" t="inlineStr">
-        <is>
-          <t>25,537.2000</t>
-        </is>
-      </c>
-      <c r="G205" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H205" s="2" t="inlineStr">
+      <c r="D205" t="n">
+        <v>1</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>25,537.2</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr"/>
+      <c r="H205" t="inlineStr">
         <is>
           <t>25,537.2 au.  การปฏิรูประบ</t>
         </is>
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="n">
+      <c r="A206" t="n">
         <v>25</v>
       </c>
-      <c r="B206" s="2" t="n">
+      <c r="B206" t="n">
         <v>19</v>
       </c>
-      <c r="C206" s="2" t="inlineStr">
+      <c r="C206" t="inlineStr">
         <is>
           <t>7,732.0</t>
         </is>
       </c>
-      <c r="D206" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E206" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F206" s="2" t="inlineStr">
-        <is>
-          <t>7,732.0000</t>
-        </is>
-      </c>
-      <c r="G206" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H206" s="2" t="inlineStr">
+      <c r="D206" t="n">
+        <v>1</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>7,732.0</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr"/>
+      <c r="H206" t="inlineStr">
         <is>
           <t>7,732.0 au.  การพัฒนากฎหม</t>
         </is>
@@ -7865,36 +7641,32 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="n">
+      <c r="A218" t="n">
         <v>28</v>
       </c>
-      <c r="B218" s="2" t="n">
+      <c r="B218" t="n">
         <v>22</v>
       </c>
-      <c r="C218" s="2" t="inlineStr">
+      <c r="C218" t="inlineStr">
         <is>
           <t>2.53</t>
         </is>
       </c>
-      <c r="D218" s="2" t="n">
+      <c r="D218" t="n">
         <v>2</v>
       </c>
-      <c r="E218" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F218" s="2" t="inlineStr">
-        <is>
-          <t>2.5300</t>
-        </is>
-      </c>
-      <c r="G218" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H218" s="2" t="inlineStr"/>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr"/>
+      <c r="H218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
@@ -8137,68 +7909,60 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="n">
+      <c r="A226" t="n">
         <v>29</v>
       </c>
-      <c r="B226" s="2" t="n">
+      <c r="B226" t="n">
         <v>23</v>
       </c>
-      <c r="C226" s="2" t="inlineStr">
+      <c r="C226" t="inlineStr">
         <is>
           <t>16,020</t>
         </is>
       </c>
-      <c r="D226" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E226" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F226" s="2" t="inlineStr">
-        <is>
-          <t>16,020.0000</t>
-        </is>
-      </c>
-      <c r="G226" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H226" s="2" t="inlineStr"/>
+      <c r="D226" t="n">
+        <v>0</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>16,020</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr"/>
+      <c r="H226" t="inlineStr"/>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="n">
+      <c r="A227" t="n">
         <v>29</v>
       </c>
-      <c r="B227" s="2" t="n">
+      <c r="B227" t="n">
         <v>23</v>
       </c>
-      <c r="C227" s="2" t="inlineStr">
+      <c r="C227" t="inlineStr">
         <is>
           <t>709.5</t>
         </is>
       </c>
-      <c r="D227" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E227" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F227" s="2" t="inlineStr">
-        <is>
-          <t>709.5000</t>
-        </is>
-      </c>
-      <c r="G227" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H227" s="2" t="inlineStr">
+      <c r="D227" t="n">
+        <v>1</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>709.5</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr"/>
+      <c r="H227" t="inlineStr">
         <is>
           <t>s:ui1du 709.5 auuain  BUDGET BU</t>
         </is>
@@ -8273,36 +8037,32 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="n">
+      <c r="A230" t="n">
         <v>29</v>
       </c>
-      <c r="B230" s="2" t="n">
+      <c r="B230" t="n">
         <v>23</v>
       </c>
-      <c r="C230" s="2" t="inlineStr">
+      <c r="C230" t="inlineStr">
         <is>
           <t>1.45</t>
         </is>
       </c>
-      <c r="D230" s="2" t="n">
+      <c r="D230" t="n">
         <v>2</v>
       </c>
-      <c r="E230" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F230" s="2" t="inlineStr">
-        <is>
-          <t>1.4500</t>
-        </is>
-      </c>
-      <c r="G230" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H230" s="2" t="inlineStr">
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>จำนวน (ล้านคน)</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr"/>
+      <c r="H230" t="inlineStr">
         <is>
           <t>อยกคว่า 1.45 ล้านคน      งบประ</t>
         </is>
@@ -8345,36 +8105,32 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="n">
+      <c r="A232" t="n">
         <v>29</v>
       </c>
-      <c r="B232" s="2" t="n">
+      <c r="B232" t="n">
         <v>23</v>
       </c>
-      <c r="C232" s="2" t="inlineStr">
+      <c r="C232" t="inlineStr">
         <is>
           <t>5.87</t>
         </is>
       </c>
-      <c r="D232" s="2" t="n">
+      <c r="D232" t="n">
         <v>2</v>
       </c>
-      <c r="E232" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F232" s="2" t="inlineStr">
-        <is>
-          <t>5.8700</t>
-        </is>
-      </c>
-      <c r="G232" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H232" s="2" t="inlineStr"/>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>5.87</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr"/>
+      <c r="H232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
@@ -8413,36 +8169,32 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="n">
+      <c r="A234" t="n">
         <v>29</v>
       </c>
-      <c r="B234" s="2" t="n">
+      <c r="B234" t="n">
         <v>23</v>
       </c>
-      <c r="C234" s="2" t="inlineStr">
+      <c r="C234" t="inlineStr">
         <is>
           <t>6.08</t>
         </is>
       </c>
-      <c r="D234" s="2" t="n">
+      <c r="D234" t="n">
         <v>2</v>
       </c>
-      <c r="E234" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F234" s="2" t="inlineStr">
-        <is>
-          <t>6.0800</t>
-        </is>
-      </c>
-      <c r="G234" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H234" s="2" t="inlineStr"/>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>6.08</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr"/>
+      <c r="H234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
@@ -8481,36 +8233,32 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="2" t="n">
+      <c r="A236" t="n">
         <v>29</v>
       </c>
-      <c r="B236" s="2" t="n">
+      <c r="B236" t="n">
         <v>23</v>
       </c>
-      <c r="C236" s="2" t="inlineStr">
+      <c r="C236" t="inlineStr">
         <is>
           <t>10.20</t>
         </is>
       </c>
-      <c r="D236" s="2" t="n">
+      <c r="D236" t="n">
         <v>2</v>
       </c>
-      <c r="E236" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F236" s="2" t="inlineStr">
-        <is>
-          <t>10.2000</t>
-        </is>
-      </c>
-      <c r="G236" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H236" s="2" t="inlineStr">
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>จำนวน (ล้านคน)</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>10.20</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr"/>
+      <c r="H236" t="inlineStr">
         <is>
           <t>้อยกว่า 10.20 ล้านคน      งบประ</t>
         </is>
@@ -8553,36 +8301,32 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="2" t="n">
+      <c r="A238" t="n">
         <v>30</v>
       </c>
-      <c r="B238" s="2" t="n">
+      <c r="B238" t="n">
         <v>24</v>
       </c>
-      <c r="C238" s="2" t="inlineStr">
+      <c r="C238" t="inlineStr">
         <is>
           <t>13.78</t>
         </is>
       </c>
-      <c r="D238" s="2" t="n">
+      <c r="D238" t="n">
         <v>2</v>
       </c>
-      <c r="E238" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F238" s="2" t="inlineStr">
-        <is>
-          <t>13.7800</t>
-        </is>
-      </c>
-      <c r="G238" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H238" s="2" t="inlineStr"/>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>13.78</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr"/>
+      <c r="H238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
@@ -8621,36 +8365,32 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="2" t="n">
+      <c r="A240" t="n">
         <v>30</v>
       </c>
-      <c r="B240" s="2" t="n">
+      <c r="B240" t="n">
         <v>24</v>
       </c>
-      <c r="C240" s="2" t="inlineStr">
+      <c r="C240" t="inlineStr">
         <is>
           <t>3.12</t>
         </is>
       </c>
-      <c r="D240" s="2" t="n">
+      <c r="D240" t="n">
         <v>2</v>
       </c>
-      <c r="E240" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F240" s="2" t="inlineStr">
-        <is>
-          <t>3.1200</t>
-        </is>
-      </c>
-      <c r="G240" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H240" s="2" t="inlineStr">
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>จำนวน (ล้านคน)</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr"/>
+      <c r="H240" t="inlineStr">
         <is>
           <t>จํานวน 3.12 ล้านคน</t>
         </is>
@@ -8693,104 +8433,92 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="2" t="n">
+      <c r="A242" t="n">
         <v>30</v>
       </c>
-      <c r="B242" s="2" t="n">
+      <c r="B242" t="n">
         <v>24</v>
       </c>
-      <c r="C242" s="2" t="inlineStr">
+      <c r="C242" t="inlineStr">
         <is>
           <t>8.8</t>
         </is>
       </c>
-      <c r="D242" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E242" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F242" s="2" t="inlineStr">
-        <is>
-          <t>8.8000</t>
-        </is>
-      </c>
-      <c r="G242" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H242" s="2" t="inlineStr"/>
+      <c r="D242" t="n">
+        <v>1</v>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr"/>
+      <c r="H242" t="inlineStr"/>
     </row>
     <row r="243">
-      <c r="A243" s="2" t="n">
+      <c r="A243" t="n">
         <v>30</v>
       </c>
-      <c r="B243" s="2" t="n">
+      <c r="B243" t="n">
         <v>24</v>
       </c>
-      <c r="C243" s="2" t="inlineStr">
+      <c r="C243" t="inlineStr">
         <is>
           <t>1.28</t>
         </is>
       </c>
-      <c r="D243" s="2" t="n">
+      <c r="D243" t="n">
         <v>2</v>
       </c>
-      <c r="E243" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F243" s="2" t="inlineStr">
-        <is>
-          <t>1.2800</t>
-        </is>
-      </c>
-      <c r="G243" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H243" s="2" t="inlineStr">
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>จำนวน (ล้านคน)</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr"/>
+      <c r="H243" t="inlineStr">
         <is>
           <t>จํานวน 1.28 ล้านคน         งจ</t>
         </is>
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="2" t="n">
+      <c r="A244" t="n">
         <v>30</v>
       </c>
-      <c r="B244" s="2" t="n">
+      <c r="B244" t="n">
         <v>24</v>
       </c>
-      <c r="C244" s="2" t="inlineStr">
+      <c r="C244" t="inlineStr">
         <is>
           <t>9.10</t>
         </is>
       </c>
-      <c r="D244" s="2" t="n">
+      <c r="D244" t="n">
         <v>2</v>
       </c>
-      <c r="E244" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F244" s="2" t="inlineStr">
-        <is>
-          <t>9.1000</t>
-        </is>
-      </c>
-      <c r="G244" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H244" s="2" t="inlineStr"/>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>9.10</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr"/>
+      <c r="H244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n">
@@ -8929,36 +8657,32 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="n">
+      <c r="A249" t="n">
         <v>31</v>
       </c>
-      <c r="B249" s="2" t="n">
+      <c r="B249" t="n">
         <v>25</v>
       </c>
-      <c r="C249" s="2" t="inlineStr">
+      <c r="C249" t="inlineStr">
         <is>
           <t>53.6</t>
         </is>
       </c>
-      <c r="D249" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E249" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F249" s="2" t="inlineStr">
-        <is>
-          <t>53.6000</t>
-        </is>
-      </c>
-      <c r="G249" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H249" s="2" t="inlineStr">
+      <c r="D249" t="n">
+        <v>1</v>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>บาท (ต่อหน่วย)</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>53.6</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr"/>
+      <c r="H249" t="inlineStr">
         <is>
           <t>บประมาณ 53.6 ส้านบาท  ค่าใช้จ่</t>
         </is>
@@ -9001,228 +8725,200 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="2" t="n">
+      <c r="A251" t="n">
         <v>31</v>
       </c>
-      <c r="B251" s="2" t="n">
+      <c r="B251" t="n">
         <v>25</v>
       </c>
-      <c r="C251" s="2" t="inlineStr">
+      <c r="C251" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
       </c>
-      <c r="D251" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E251" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F251" s="2" t="inlineStr">
-        <is>
-          <t>4,000.0000</t>
-        </is>
-      </c>
-      <c r="G251" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H251" s="2" t="inlineStr"/>
+      <c r="D251" t="n">
+        <v>0</v>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr"/>
+      <c r="H251" t="inlineStr"/>
     </row>
     <row r="252">
-      <c r="A252" s="2" t="n">
+      <c r="A252" t="n">
         <v>31</v>
       </c>
-      <c r="B252" s="2" t="n">
+      <c r="B252" t="n">
         <v>25</v>
       </c>
-      <c r="C252" s="2" t="inlineStr">
+      <c r="C252" t="inlineStr">
         <is>
           <t>10.0</t>
         </is>
       </c>
-      <c r="D252" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E252" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F252" s="2" t="inlineStr">
-        <is>
-          <t>10.0000</t>
-        </is>
-      </c>
-      <c r="G252" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H252" s="2" t="inlineStr"/>
+      <c r="D252" t="n">
+        <v>1</v>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr"/>
+      <c r="H252" t="inlineStr"/>
     </row>
     <row r="253">
-      <c r="A253" s="2" t="n">
+      <c r="A253" t="n">
         <v>31</v>
       </c>
-      <c r="B253" s="2" t="n">
+      <c r="B253" t="n">
         <v>25</v>
       </c>
-      <c r="C253" s="2" t="inlineStr">
+      <c r="C253" t="inlineStr">
         <is>
           <t>3,000</t>
         </is>
       </c>
-      <c r="D253" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E253" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F253" s="2" t="inlineStr">
-        <is>
-          <t>3,000.0000</t>
-        </is>
-      </c>
-      <c r="G253" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H253" s="2" t="inlineStr"/>
+      <c r="D253" t="n">
+        <v>0</v>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr"/>
+      <c r="H253" t="inlineStr"/>
     </row>
     <row r="254">
-      <c r="A254" s="2" t="n">
+      <c r="A254" t="n">
         <v>31</v>
       </c>
-      <c r="B254" s="2" t="n">
+      <c r="B254" t="n">
         <v>25</v>
       </c>
-      <c r="C254" s="2" t="inlineStr">
+      <c r="C254" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="D254" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E254" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F254" s="2" t="inlineStr">
-        <is>
-          <t>7.1000</t>
-        </is>
-      </c>
-      <c r="G254" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H254" s="2" t="inlineStr"/>
+      <c r="D254" t="n">
+        <v>1</v>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr"/>
+      <c r="H254" t="inlineStr"/>
     </row>
     <row r="255">
-      <c r="A255" s="2" t="n">
+      <c r="A255" t="n">
         <v>31</v>
       </c>
-      <c r="B255" s="2" t="n">
+      <c r="B255" t="n">
         <v>25</v>
       </c>
-      <c r="C255" s="2" t="inlineStr">
+      <c r="C255" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
       </c>
-      <c r="D255" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E255" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F255" s="2" t="inlineStr">
-        <is>
-          <t>2,500.0000</t>
-        </is>
-      </c>
-      <c r="G255" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H255" s="2" t="inlineStr"/>
+      <c r="D255" t="n">
+        <v>0</v>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr"/>
+      <c r="H255" t="inlineStr"/>
     </row>
     <row r="256">
-      <c r="A256" s="2" t="n">
+      <c r="A256" t="n">
         <v>31</v>
       </c>
-      <c r="B256" s="2" t="n">
+      <c r="B256" t="n">
         <v>25</v>
       </c>
-      <c r="C256" s="2" t="inlineStr">
+      <c r="C256" t="inlineStr">
         <is>
           <t>9.2</t>
         </is>
       </c>
-      <c r="D256" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E256" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F256" s="2" t="inlineStr">
-        <is>
-          <t>9.2000</t>
-        </is>
-      </c>
-      <c r="G256" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H256" s="2" t="inlineStr"/>
+      <c r="D256" t="n">
+        <v>1</v>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>9.2</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr"/>
+      <c r="H256" t="inlineStr"/>
     </row>
     <row r="257">
-      <c r="A257" s="2" t="n">
+      <c r="A257" t="n">
         <v>32</v>
       </c>
-      <c r="B257" s="2" t="n">
+      <c r="B257" t="n">
         <v>26</v>
       </c>
-      <c r="C257" s="2" t="inlineStr">
+      <c r="C257" t="inlineStr">
         <is>
           <t>462.5</t>
         </is>
       </c>
-      <c r="D257" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E257" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F257" s="2" t="inlineStr">
-        <is>
-          <t>462.5000</t>
-        </is>
-      </c>
-      <c r="G257" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H257" s="2" t="inlineStr">
+      <c r="D257" t="n">
+        <v>1</v>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>บาท (ต่อหน่วย)</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>462.5</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr"/>
+      <c r="H257" t="inlineStr">
         <is>
           <t>บประมาณ 462.5 ส้านบาท  BUDGET B</t>
         </is>
@@ -9261,36 +8957,32 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="2" t="n">
+      <c r="A259" t="n">
         <v>32</v>
       </c>
-      <c r="B259" s="2" t="n">
+      <c r="B259" t="n">
         <v>26</v>
       </c>
-      <c r="C259" s="2" t="inlineStr">
+      <c r="C259" t="inlineStr">
         <is>
           <t>13.47</t>
         </is>
       </c>
-      <c r="D259" s="2" t="n">
+      <c r="D259" t="n">
         <v>2</v>
       </c>
-      <c r="E259" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F259" s="2" t="inlineStr">
-        <is>
-          <t>13.4700</t>
-        </is>
-      </c>
-      <c r="G259" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H259" s="2" t="inlineStr">
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>จำนวน (ล้านคน)</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>13.47</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr"/>
+      <c r="H259" t="inlineStr">
         <is>
           <t>ป้าหมาย 13.47 ล้านคน งบประมาณ 1</t>
         </is>
@@ -9465,36 +9157,32 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="2" t="n">
+      <c r="A265" t="n">
         <v>32</v>
       </c>
-      <c r="B265" s="2" t="n">
+      <c r="B265" t="n">
         <v>26</v>
       </c>
-      <c r="C265" s="2" t="inlineStr">
+      <c r="C265" t="inlineStr">
         <is>
           <t>9,000</t>
         </is>
       </c>
-      <c r="D265" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E265" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F265" s="2" t="inlineStr">
-        <is>
-          <t>9,000.0000</t>
-        </is>
-      </c>
-      <c r="G265" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H265" s="2" t="inlineStr">
+      <c r="D265" t="n">
+        <v>0</v>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr"/>
+      <c r="H265" t="inlineStr">
         <is>
           <t>จํานวน 9,000 Kav      บประมาณ</t>
         </is>
@@ -9769,36 +9457,32 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="2" t="n">
+      <c r="A274" t="n">
         <v>35</v>
       </c>
-      <c r="B274" s="2" t="n">
+      <c r="B274" t="n">
         <v>29</v>
       </c>
-      <c r="C274" s="2" t="inlineStr">
+      <c r="C274" t="inlineStr">
         <is>
           <t>2.53</t>
         </is>
       </c>
-      <c r="D274" s="2" t="n">
+      <c r="D274" t="n">
         <v>2</v>
       </c>
-      <c r="E274" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F274" s="2" t="inlineStr">
-        <is>
-          <t>2.5300</t>
-        </is>
-      </c>
-      <c r="G274" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H274" s="2" t="inlineStr">
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>จำนวน (ล้านคน)</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr"/>
+      <c r="H274" t="inlineStr">
         <is>
           <t>- 6 ปี) 2.53 ล้านคน ที่อยู่ในค</t>
         </is>
@@ -9853,7 +9537,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>ไม่ทราบหน่วย</t>
+          <t>บาท (ต่อหน่วย)</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -9869,36 +9553,32 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="2" t="n">
+      <c r="A277" t="n">
         <v>35</v>
       </c>
-      <c r="B277" s="2" t="n">
+      <c r="B277" t="n">
         <v>29</v>
       </c>
-      <c r="C277" s="2" t="inlineStr">
+      <c r="C277" t="inlineStr">
         <is>
           <t>2.47</t>
         </is>
       </c>
-      <c r="D277" s="2" t="n">
+      <c r="D277" t="n">
         <v>2</v>
       </c>
-      <c r="E277" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F277" s="2" t="inlineStr">
-        <is>
-          <t>2.4700</t>
-        </is>
-      </c>
-      <c r="G277" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H277" s="2" t="inlineStr">
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>จำนวน (ล้านคน)</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr"/>
+      <c r="H277" t="inlineStr">
         <is>
           <t>ู้พิการ 2.47 ล้านคน ได้รับเบี้</t>
         </is>
@@ -9969,36 +9649,32 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="2" t="n">
+      <c r="A280" t="n">
         <v>35</v>
       </c>
-      <c r="B280" s="2" t="n">
+      <c r="B280" t="n">
         <v>29</v>
       </c>
-      <c r="C280" s="2" t="inlineStr">
+      <c r="C280" t="inlineStr">
         <is>
           <t>13.47</t>
         </is>
       </c>
-      <c r="D280" s="2" t="n">
+      <c r="D280" t="n">
         <v>2</v>
       </c>
-      <c r="E280" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F280" s="2" t="inlineStr">
-        <is>
-          <t>13.4700</t>
-        </is>
-      </c>
-      <c r="G280" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H280" s="2" t="inlineStr">
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>จำนวน (ล้านคน)</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>13.47</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr"/>
+      <c r="H280" t="inlineStr">
         <is>
           <t>สูงอายุ 13.47 ล้านคน ได้รับเบี้</t>
         </is>
@@ -10101,36 +9777,32 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="2" t="n">
+      <c r="A284" t="n">
         <v>35</v>
       </c>
-      <c r="B284" s="2" t="n">
+      <c r="B284" t="n">
         <v>29</v>
       </c>
-      <c r="C284" s="2" t="inlineStr">
+      <c r="C284" t="inlineStr">
         <is>
           <t>10.14</t>
         </is>
       </c>
-      <c r="D284" s="2" t="n">
+      <c r="D284" t="n">
         <v>2</v>
       </c>
-      <c r="E284" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F284" s="2" t="inlineStr">
-        <is>
-          <t>10.1400</t>
-        </is>
-      </c>
-      <c r="G284" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H284" s="2" t="inlineStr">
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>จำนวน (ล้านคน)</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>10.14</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr"/>
+      <c r="H284" t="inlineStr">
         <is>
           <t>แห่งรัฐ 10.14 ล้านคน ได้รับเงิน</t>
         </is>
@@ -10169,108 +9841,96 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="2" t="n">
+      <c r="A286" t="n">
         <v>36</v>
       </c>
-      <c r="B286" s="2" t="n">
+      <c r="B286" t="n">
         <v>30</v>
       </c>
-      <c r="C286" s="2" t="inlineStr">
+      <c r="C286" t="inlineStr">
         <is>
           <t>4,399</t>
         </is>
       </c>
-      <c r="D286" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E286" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F286" s="2" t="inlineStr">
-        <is>
-          <t>4,399.0000</t>
-        </is>
-      </c>
-      <c r="G286" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H286" s="2" t="inlineStr">
+      <c r="D286" t="n">
+        <v>0</v>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>4,399</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr"/>
+      <c r="H286" t="inlineStr">
         <is>
           <t>้อยกว่า 4,399 au.  ผู้ประกอบการ</t>
         </is>
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="2" t="n">
+      <c r="A287" t="n">
         <v>36</v>
       </c>
-      <c r="B287" s="2" t="n">
+      <c r="B287" t="n">
         <v>30</v>
       </c>
-      <c r="C287" s="2" t="inlineStr">
+      <c r="C287" t="inlineStr">
         <is>
           <t>7,600</t>
         </is>
       </c>
-      <c r="D287" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E287" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F287" s="2" t="inlineStr">
-        <is>
-          <t>7,600.0000</t>
-        </is>
-      </c>
-      <c r="G287" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H287" s="2" t="inlineStr">
+      <c r="D287" t="n">
+        <v>0</v>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>7,600</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr"/>
+      <c r="H287" t="inlineStr">
         <is>
           <t>นาดย่อม 7,600 sig ได้รับการส่งเ</t>
         </is>
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="2" t="n">
+      <c r="A288" t="n">
         <v>36</v>
       </c>
-      <c r="B288" s="2" t="n">
+      <c r="B288" t="n">
         <v>30</v>
       </c>
-      <c r="C288" s="2" t="inlineStr">
+      <c r="C288" t="inlineStr">
         <is>
           <t>26,000</t>
         </is>
       </c>
-      <c r="D288" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E288" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F288" s="2" t="inlineStr">
-        <is>
-          <t>26,000.0000</t>
-        </is>
-      </c>
-      <c r="G288" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H288" s="2" t="inlineStr">
+      <c r="D288" t="n">
+        <v>0</v>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>26,000</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr"/>
+      <c r="H288" t="inlineStr">
         <is>
           <t>ommerce 26,000 sig  พัฒนาศักยภาพ</t>
         </is>
@@ -10461,7 +10121,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>ไม่ทราบหน่วย</t>
+          <t>จำนวน (นับ)</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -10525,7 +10185,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>ไม่ทราบหน่วย</t>
+          <t>บาท (ต่อหน่วย)</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -10573,36 +10233,32 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="2" t="n">
+      <c r="A298" t="n">
         <v>39</v>
       </c>
-      <c r="B298" s="2" t="n">
+      <c r="B298" t="n">
         <v>33</v>
       </c>
-      <c r="C298" s="2" t="inlineStr">
+      <c r="C298" t="inlineStr">
         <is>
           <t>1.37</t>
         </is>
       </c>
-      <c r="D298" s="2" t="n">
+      <c r="D298" t="n">
         <v>2</v>
       </c>
-      <c r="E298" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F298" s="2" t="inlineStr">
-        <is>
-          <t>1.3700</t>
-        </is>
-      </c>
-      <c r="G298" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H298" s="2" t="inlineStr">
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>จำนวน (ล้านไร่)</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr"/>
+      <c r="H298" t="inlineStr">
         <is>
           <t>ารเกษตร 1.37 ล้านไร่ ได้รับการ</t>
         </is>
@@ -10641,36 +10297,32 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="2" t="n">
+      <c r="A300" t="n">
         <v>39</v>
       </c>
-      <c r="B300" s="2" t="n">
+      <c r="B300" t="n">
         <v>33</v>
       </c>
-      <c r="C300" s="2" t="inlineStr">
+      <c r="C300" t="inlineStr">
         <is>
           <t>2.06</t>
         </is>
       </c>
-      <c r="D300" s="2" t="n">
+      <c r="D300" t="n">
         <v>2</v>
       </c>
-      <c r="E300" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F300" s="2" t="inlineStr">
-        <is>
-          <t>2.0600</t>
-        </is>
-      </c>
-      <c r="G300" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H300" s="2" t="inlineStr">
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>จำนวน (ล้านราย)</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr"/>
+      <c r="H300" t="inlineStr">
         <is>
           <t>เกษตรกร 2.06 ล้านราย  ๑ บริหาร</t>
         </is>
@@ -10809,72 +10461,64 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="2" t="n">
+      <c r="A305" t="n">
         <v>41</v>
       </c>
-      <c r="B305" s="2" t="n">
+      <c r="B305" t="n">
         <v>35</v>
       </c>
-      <c r="C305" s="2" t="inlineStr">
+      <c r="C305" t="inlineStr">
         <is>
           <t>4,320</t>
         </is>
       </c>
-      <c r="D305" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E305" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F305" s="2" t="inlineStr">
-        <is>
-          <t>4,320.0000</t>
-        </is>
-      </c>
-      <c r="G305" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H305" s="2" t="inlineStr">
+      <c r="D305" t="n">
+        <v>0</v>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>บาท (ต่อหน่วย)</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>4,320</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr"/>
+      <c r="H305" t="inlineStr">
         <is>
           <t>้อยกว่า 4,320 จ้านบาท</t>
         </is>
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="2" t="n">
+      <c r="A306" t="n">
         <v>41</v>
       </c>
-      <c r="B306" s="2" t="n">
+      <c r="B306" t="n">
         <v>35</v>
       </c>
-      <c r="C306" s="2" t="inlineStr">
+      <c r="C306" t="inlineStr">
         <is>
           <t>14,668</t>
         </is>
       </c>
-      <c r="D306" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E306" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F306" s="2" t="inlineStr">
-        <is>
-          <t>14,668.0000</t>
-        </is>
-      </c>
-      <c r="G306" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H306" s="2" t="inlineStr">
+      <c r="D306" t="n">
+        <v>0</v>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>14,668</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr"/>
+      <c r="H306" t="inlineStr">
         <is>
           <t>้อยกว่า 14,668 Ig  ส่งเสริมและสน</t>
         </is>
@@ -11021,36 +10665,32 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="2" t="n">
+      <c r="A311" t="n">
         <v>45</v>
       </c>
-      <c r="B311" s="2" t="n">
+      <c r="B311" t="n">
         <v>39</v>
       </c>
-      <c r="C311" s="2" t="inlineStr">
+      <c r="C311" t="inlineStr">
         <is>
           <t>8,000</t>
         </is>
       </c>
-      <c r="D311" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E311" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F311" s="2" t="inlineStr">
-        <is>
-          <t>8,000.0000</t>
-        </is>
-      </c>
-      <c r="G311" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H311" s="2" t="inlineStr">
+      <c r="D311" t="n">
+        <v>0</v>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr"/>
+      <c r="H311" t="inlineStr">
         <is>
           <t>เที่ยว  8,000 นาย เข้าร่วมการฝึ</t>
         </is>
@@ -11073,7 +10713,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>ไม่ทราบหน่วย</t>
+          <t>บาท (ต่อหน่วย)</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
@@ -11105,7 +10745,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>ไม่ทราบหน่วย</t>
+          <t>บาท (ต่อหน่วย)</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
@@ -11693,104 +11333,92 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="2" t="n">
+      <c r="A332" t="n">
         <v>49</v>
       </c>
-      <c r="B332" s="2" t="n">
+      <c r="B332" t="n">
         <v>43</v>
       </c>
-      <c r="C332" s="2" t="inlineStr">
+      <c r="C332" t="inlineStr">
         <is>
           <t>121,123.7</t>
         </is>
       </c>
-      <c r="D332" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E332" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F332" s="2" t="inlineStr">
-        <is>
-          <t>121,123.7000</t>
-        </is>
-      </c>
-      <c r="G332" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H332" s="2" t="inlineStr"/>
+      <c r="D332" t="n">
+        <v>1</v>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>121,123.7</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr"/>
+      <c r="H332" t="inlineStr"/>
     </row>
     <row r="333">
-      <c r="A333" s="2" t="n">
+      <c r="A333" t="n">
         <v>49</v>
       </c>
-      <c r="B333" s="2" t="n">
+      <c r="B333" t="n">
         <v>43</v>
       </c>
-      <c r="C333" s="2" t="inlineStr">
+      <c r="C333" t="inlineStr">
         <is>
           <t>13,200</t>
         </is>
       </c>
-      <c r="D333" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E333" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F333" s="2" t="inlineStr">
-        <is>
-          <t>13,200.0000</t>
-        </is>
-      </c>
-      <c r="G333" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H333" s="2" t="inlineStr">
+      <c r="D333" t="n">
+        <v>0</v>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>13,200</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr"/>
+      <c r="H333" t="inlineStr">
         <is>
           <t>ฉพาะทาง 13,200 Ad เพื่อคุ้มครองป</t>
         </is>
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="2" t="n">
+      <c r="A334" t="n">
         <v>49</v>
       </c>
-      <c r="B334" s="2" t="n">
+      <c r="B334" t="n">
         <v>43</v>
       </c>
-      <c r="C334" s="2" t="inlineStr">
+      <c r="C334" t="inlineStr">
         <is>
           <t>4,158</t>
         </is>
       </c>
-      <c r="D334" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E334" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F334" s="2" t="inlineStr">
-        <is>
-          <t>4,158.0000</t>
-        </is>
-      </c>
-      <c r="G334" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H334" s="2" t="inlineStr">
+      <c r="D334" t="n">
+        <v>0</v>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>4,158</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr"/>
+      <c r="H334" t="inlineStr">
         <is>
           <t>้อยกว่า 4,158 คดี เพื่อป้องกัน</t>
         </is>
@@ -11957,36 +11585,32 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="2" t="n">
+      <c r="A340" t="n">
         <v>50</v>
       </c>
-      <c r="B340" s="2" t="n">
+      <c r="B340" t="n">
         <v>44</v>
       </c>
-      <c r="C340" s="2" t="inlineStr">
+      <c r="C340" t="inlineStr">
         <is>
           <t>7.48</t>
         </is>
       </c>
-      <c r="D340" s="2" t="n">
+      <c r="D340" t="n">
         <v>2</v>
       </c>
-      <c r="E340" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F340" s="2" t="inlineStr">
-        <is>
-          <t>7.4800</t>
-        </is>
-      </c>
-      <c r="G340" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H340" s="2" t="inlineStr">
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>จำนวน (ล้านราย)</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>7.48</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr"/>
+      <c r="H340" t="inlineStr">
         <is>
           <t>้อยกว่า 7.48 ล้านราย และผู้ต้อ</t>
         </is>
@@ -12089,36 +11713,32 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="2" t="n">
+      <c r="A344" t="n">
         <v>51</v>
       </c>
-      <c r="B344" s="2" t="n">
+      <c r="B344" t="n">
         <v>45</v>
       </c>
-      <c r="C344" s="2" t="inlineStr">
+      <c r="C344" t="inlineStr">
         <is>
           <t>1,000</t>
         </is>
       </c>
-      <c r="D344" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E344" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F344" s="2" t="inlineStr">
-        <is>
-          <t>1,000.0000</t>
-        </is>
-      </c>
-      <c r="G344" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H344" s="2" t="inlineStr">
+      <c r="D344" t="n">
+        <v>0</v>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>1,000</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr"/>
+      <c r="H344" t="inlineStr">
         <is>
           <t>niquet) 1,000 เส้น และเฝือกอ่อน</t>
         </is>
@@ -12361,36 +11981,32 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="2" t="n">
+      <c r="A352" t="n">
         <v>53</v>
       </c>
-      <c r="B352" s="2" t="n">
+      <c r="B352" t="n">
         <v>47</v>
       </c>
-      <c r="C352" s="2" t="inlineStr">
+      <c r="C352" t="inlineStr">
         <is>
           <t>607,655</t>
         </is>
       </c>
-      <c r="D352" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E352" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F352" s="2" t="inlineStr">
-        <is>
-          <t>607,655.0000</t>
-        </is>
-      </c>
-      <c r="G352" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H352" s="2" t="inlineStr"/>
+      <c r="D352" t="n">
+        <v>0</v>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>607,655</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr"/>
+      <c r="H352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" s="2" t="n">
@@ -12621,72 +12237,64 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="2" t="n">
+      <c r="A360" t="n">
         <v>55</v>
       </c>
-      <c r="B360" s="2" t="n">
+      <c r="B360" t="n">
         <v>49</v>
       </c>
-      <c r="C360" s="2" t="inlineStr">
+      <c r="C360" t="inlineStr">
         <is>
           <t>1.45</t>
         </is>
       </c>
-      <c r="D360" s="2" t="n">
+      <c r="D360" t="n">
         <v>2</v>
       </c>
-      <c r="E360" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F360" s="2" t="inlineStr">
-        <is>
-          <t>1.4500</t>
-        </is>
-      </c>
-      <c r="G360" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H360" s="2" t="inlineStr">
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>จำนวน (ล้านคน)</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr"/>
+      <c r="H360" t="inlineStr">
         <is>
           <t>้อยคว่า 1.45 ล้านคน ได้รับทุนก</t>
         </is>
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="2" t="n">
+      <c r="A361" t="n">
         <v>55</v>
       </c>
-      <c r="B361" s="2" t="n">
+      <c r="B361" t="n">
         <v>49</v>
       </c>
-      <c r="C361" s="2" t="inlineStr">
+      <c r="C361" t="inlineStr">
         <is>
           <t>5.94</t>
         </is>
       </c>
-      <c r="D361" s="2" t="n">
+      <c r="D361" t="n">
         <v>2</v>
       </c>
-      <c r="E361" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F361" s="2" t="inlineStr">
-        <is>
-          <t>5.9400</t>
-        </is>
-      </c>
-      <c r="G361" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H361" s="2" t="inlineStr">
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>จำนวน (ล้านคน)</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>5.94</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr"/>
+      <c r="H361" t="inlineStr">
         <is>
           <t>สพชซู. 5.94 ล้านคน และนักศึกษ</t>
         </is>
@@ -12885,36 +12493,32 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="2" t="n">
+      <c r="A368" t="n">
         <v>56</v>
       </c>
-      <c r="B368" s="2" t="n">
+      <c r="B368" t="n">
         <v>50</v>
       </c>
-      <c r="C368" s="2" t="inlineStr">
+      <c r="C368" t="inlineStr">
         <is>
           <t>47.17</t>
         </is>
       </c>
-      <c r="D368" s="2" t="n">
+      <c r="D368" t="n">
         <v>2</v>
       </c>
-      <c r="E368" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F368" s="2" t="inlineStr">
-        <is>
-          <t>47.1700</t>
-        </is>
-      </c>
-      <c r="G368" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H368" s="2" t="inlineStr">
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>จำนวน (ล้านคน)</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>47.17</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr"/>
+      <c r="H368" t="inlineStr">
         <is>
           <t>้อยกว่า 47.17 ล้านคน  DA  ของเต</t>
         </is>
@@ -13021,36 +12625,32 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" s="2" t="n">
+      <c r="A372" t="n">
         <v>56</v>
       </c>
-      <c r="B372" s="2" t="n">
+      <c r="B372" t="n">
         <v>50</v>
       </c>
-      <c r="C372" s="2" t="inlineStr">
+      <c r="C372" t="inlineStr">
         <is>
           <t>3,427,600</t>
         </is>
       </c>
-      <c r="D372" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E372" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F372" s="2" t="inlineStr">
-        <is>
-          <t>3,427,600.0000</t>
-        </is>
-      </c>
-      <c r="G372" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H372" s="2" t="inlineStr"/>
+      <c r="D372" t="n">
+        <v>0</v>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>3,427,600</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr"/>
+      <c r="H372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -13101,7 +12701,7 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>ไม่ทราบหน่วย</t>
+          <t>จำนวน (นับ)</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
@@ -13149,36 +12749,32 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="2" t="n">
+      <c r="A376" t="n">
         <v>57</v>
       </c>
-      <c r="B376" s="2" t="n">
+      <c r="B376" t="n">
         <v>51</v>
       </c>
-      <c r="C376" s="2" t="inlineStr">
+      <c r="C376" t="inlineStr">
         <is>
           <t>22.88</t>
         </is>
       </c>
-      <c r="D376" s="2" t="n">
+      <c r="D376" t="n">
         <v>2</v>
       </c>
-      <c r="E376" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F376" s="2" t="inlineStr">
-        <is>
-          <t>22.8800</t>
-        </is>
-      </c>
-      <c r="G376" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H376" s="2" t="inlineStr">
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>จำนวน (ล้านคน)</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>22.88</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr"/>
+      <c r="H376" t="inlineStr">
         <is>
           <t>้อยกว่า 22.88 ล้านคน คุ้มครองสิ</t>
         </is>
@@ -13253,72 +12849,64 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379" s="2" t="n">
+      <c r="A379" t="n">
         <v>58</v>
       </c>
-      <c r="B379" s="2" t="n">
+      <c r="B379" t="n">
         <v>52</v>
       </c>
-      <c r="C379" s="2" t="inlineStr">
+      <c r="C379" t="inlineStr">
         <is>
           <t>303,490</t>
         </is>
       </c>
-      <c r="D379" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E379" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F379" s="2" t="inlineStr">
-        <is>
-          <t>303,490.0000</t>
-        </is>
-      </c>
-      <c r="G379" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H379" s="2" t="inlineStr">
+      <c r="D379" t="n">
+        <v>0</v>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>303,490</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr"/>
+      <c r="H379" t="inlineStr">
         <is>
           <t>ในชุมชน 303,490 au ได้รับการส่งเส</t>
         </is>
       </c>
     </row>
     <row r="380">
-      <c r="A380" s="2" t="n">
+      <c r="A380" t="n">
         <v>58</v>
       </c>
-      <c r="B380" s="2" t="n">
+      <c r="B380" t="n">
         <v>52</v>
       </c>
-      <c r="C380" s="2" t="inlineStr">
+      <c r="C380" t="inlineStr">
         <is>
           <t>9,000</t>
         </is>
       </c>
-      <c r="D380" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E380" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F380" s="2" t="inlineStr">
-        <is>
-          <t>9,000.0000</t>
-        </is>
-      </c>
-      <c r="G380" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H380" s="2" t="inlineStr">
+      <c r="D380" t="n">
+        <v>0</v>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr"/>
+      <c r="H380" t="inlineStr">
         <is>
           <t>ู่อาศัย 9,000 Kav ให้ผู้สูงอายุ</t>
         </is>
@@ -13389,72 +12977,64 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383" s="2" t="n">
+      <c r="A383" t="n">
         <v>58</v>
       </c>
-      <c r="B383" s="2" t="n">
+      <c r="B383" t="n">
         <v>52</v>
       </c>
-      <c r="C383" s="2" t="inlineStr">
+      <c r="C383" t="inlineStr">
         <is>
           <t>1.8</t>
         </is>
       </c>
-      <c r="D383" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E383" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F383" s="2" t="inlineStr">
-        <is>
-          <t>1.8000</t>
-        </is>
-      </c>
-      <c r="G383" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H383" s="2" t="inlineStr">
+      <c r="D383" t="n">
+        <v>1</v>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>จำนวน (ล้านราย)</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr"/>
+      <c r="H383" t="inlineStr">
         <is>
           <t>้สูงอายุ1.8 ล้านราย ได้รับการ</t>
         </is>
       </c>
     </row>
     <row r="384">
-      <c r="A384" s="2" t="n">
+      <c r="A384" t="n">
         <v>59</v>
       </c>
-      <c r="B384" s="2" t="n">
+      <c r="B384" t="n">
         <v>53</v>
       </c>
-      <c r="C384" s="2" t="inlineStr">
+      <c r="C384" t="inlineStr">
         <is>
           <t>170,390.6</t>
         </is>
       </c>
-      <c r="D384" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E384" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F384" s="2" t="inlineStr">
-        <is>
-          <t>170,390.6000</t>
-        </is>
-      </c>
-      <c r="G384" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H384" s="2" t="inlineStr"/>
+      <c r="D384" t="n">
+        <v>1</v>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>170,390.6</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr"/>
+      <c r="H384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -13489,72 +13069,64 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="2" t="n">
+      <c r="A386" t="n">
         <v>60</v>
       </c>
-      <c r="B386" s="2" t="n">
+      <c r="B386" t="n">
         <v>54</v>
       </c>
-      <c r="C386" s="2" t="inlineStr">
+      <c r="C386" t="inlineStr">
         <is>
           <t>307,160</t>
         </is>
       </c>
-      <c r="D386" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E386" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F386" s="2" t="inlineStr">
-        <is>
-          <t>307,160.0000</t>
-        </is>
-      </c>
-      <c r="G386" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H386" s="2" t="inlineStr">
+      <c r="D386" t="n">
+        <v>0</v>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>307,160</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr"/>
+      <c r="H386" t="inlineStr">
         <is>
           <t>พื้นที่ 307,160 Is ได้รับการป้องก</t>
         </is>
       </c>
     </row>
     <row r="387">
-      <c r="A387" s="2" t="n">
+      <c r="A387" t="n">
         <v>60</v>
       </c>
-      <c r="B387" s="2" t="n">
+      <c r="B387" t="n">
         <v>54</v>
       </c>
-      <c r="C387" s="2" t="inlineStr">
+      <c r="C387" t="inlineStr">
         <is>
           <t>230,941</t>
         </is>
       </c>
-      <c r="D387" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E387" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F387" s="2" t="inlineStr">
-        <is>
-          <t>230,941.0000</t>
-        </is>
-      </c>
-      <c r="G387" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H387" s="2" t="inlineStr">
+      <c r="D387" t="n">
+        <v>0</v>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>230,941</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr"/>
+      <c r="H387" t="inlineStr">
         <is>
           <t>ลิ่งรวม 230,941 เมตร เพื่อลดความเ</t>
         </is>
@@ -13593,72 +13165,64 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" s="2" t="n">
+      <c r="A389" t="n">
         <v>60</v>
       </c>
-      <c r="B389" s="2" t="n">
+      <c r="B389" t="n">
         <v>54</v>
       </c>
-      <c r="C389" s="2" t="inlineStr">
+      <c r="C389" t="inlineStr">
         <is>
           <t>2,275</t>
         </is>
       </c>
-      <c r="D389" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E389" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F389" s="2" t="inlineStr">
-        <is>
-          <t>2,275.0000</t>
-        </is>
-      </c>
-      <c r="G389" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H389" s="2" t="inlineStr">
+      <c r="D389" t="n">
+        <v>0</v>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>2,275</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr"/>
+      <c r="H389" t="inlineStr">
         <is>
           <t>ด้านน้า 2,275 สถานี เพื่อแจ้งเต</t>
         </is>
       </c>
     </row>
     <row r="390">
-      <c r="A390" s="2" t="n">
+      <c r="A390" t="n">
         <v>60</v>
       </c>
-      <c r="B390" s="2" t="n">
+      <c r="B390" t="n">
         <v>54</v>
       </c>
-      <c r="C390" s="2" t="inlineStr">
+      <c r="C390" t="inlineStr">
         <is>
           <t>23,500</t>
         </is>
       </c>
-      <c r="D390" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E390" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F390" s="2" t="inlineStr">
-        <is>
-          <t>23,500.0000</t>
-        </is>
-      </c>
-      <c r="G390" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H390" s="2" t="inlineStr">
+      <c r="D390" t="n">
+        <v>0</v>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>23,500</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr"/>
+      <c r="H390" t="inlineStr">
         <is>
           <t>่อมโทรม 23,500 Is เพื่อคืนความสม</t>
         </is>
@@ -13761,36 +13325,32 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="2" t="n">
+      <c r="A394" t="n">
         <v>60</v>
       </c>
-      <c r="B394" s="2" t="n">
+      <c r="B394" t="n">
         <v>54</v>
       </c>
-      <c r="C394" s="2" t="inlineStr">
+      <c r="C394" t="inlineStr">
         <is>
           <t>9.44</t>
         </is>
       </c>
-      <c r="D394" s="2" t="n">
+      <c r="D394" t="n">
         <v>2</v>
       </c>
-      <c r="E394" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F394" s="2" t="inlineStr">
-        <is>
-          <t>9.4400</t>
-        </is>
-      </c>
-      <c r="G394" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H394" s="2" t="inlineStr">
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>9.44</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr"/>
+      <c r="H394" t="inlineStr">
         <is>
           <t>บประปา  9.44 ล้านลูกบาศก์เมตร</t>
         </is>
@@ -13865,108 +13425,96 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" s="2" t="n">
+      <c r="A397" t="n">
         <v>60</v>
       </c>
-      <c r="B397" s="2" t="n">
+      <c r="B397" t="n">
         <v>54</v>
       </c>
-      <c r="C397" s="2" t="inlineStr">
+      <c r="C397" t="inlineStr">
         <is>
           <t>277,698</t>
         </is>
       </c>
-      <c r="D397" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E397" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F397" s="2" t="inlineStr">
-        <is>
-          <t>277,698.0000</t>
-        </is>
-      </c>
-      <c r="G397" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H397" s="2" t="inlineStr">
+      <c r="D397" t="n">
+        <v>0</v>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>277,698</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr"/>
+      <c r="H397" t="inlineStr">
         <is>
           <t>ลประทาน 277,698 Is  เสริมความมั่น</t>
         </is>
       </c>
     </row>
     <row r="398">
-      <c r="A398" s="2" t="n">
+      <c r="A398" t="n">
         <v>60</v>
       </c>
-      <c r="B398" s="2" t="n">
+      <c r="B398" t="n">
         <v>54</v>
       </c>
-      <c r="C398" s="2" t="inlineStr">
+      <c r="C398" t="inlineStr">
         <is>
           <t>1,620</t>
         </is>
       </c>
-      <c r="D398" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E398" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F398" s="2" t="inlineStr">
-        <is>
-          <t>1,620.0000</t>
-        </is>
-      </c>
-      <c r="G398" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H398" s="2" t="inlineStr">
+      <c r="D398" t="n">
+        <v>0</v>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>1,620</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr"/>
+      <c r="H398" t="inlineStr">
         <is>
           <t>มากขึ้น 1,620 ล้านลูกบาศก์เมตร</t>
         </is>
       </c>
     </row>
     <row r="399">
-      <c r="A399" s="2" t="n">
+      <c r="A399" t="n">
         <v>60</v>
       </c>
-      <c r="B399" s="2" t="n">
+      <c r="B399" t="n">
         <v>54</v>
       </c>
-      <c r="C399" s="2" t="inlineStr">
+      <c r="C399" t="inlineStr">
         <is>
           <t>115,694.0</t>
         </is>
       </c>
-      <c r="D399" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E399" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F399" s="2" t="inlineStr">
-        <is>
-          <t>115,694.0000</t>
-        </is>
-      </c>
-      <c r="G399" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H399" s="2" t="inlineStr"/>
+      <c r="D399" t="n">
+        <v>1</v>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>115,694.0</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr"/>
+      <c r="H399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -14265,216 +13813,192 @@
       </c>
     </row>
     <row r="409">
-      <c r="A409" s="2" t="n">
+      <c r="A409" t="n">
         <v>62</v>
       </c>
-      <c r="B409" s="2" t="n">
+      <c r="B409" t="n">
         <v>56</v>
       </c>
-      <c r="C409" s="2" t="inlineStr">
+      <c r="C409" t="inlineStr">
         <is>
           <t>135,230</t>
         </is>
       </c>
-      <c r="D409" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E409" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F409" s="2" t="inlineStr">
-        <is>
-          <t>135,230.0000</t>
-        </is>
-      </c>
-      <c r="G409" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H409" s="2" t="inlineStr">
+      <c r="D409" t="n">
+        <v>0</v>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>135,230</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr"/>
+      <c r="H409" t="inlineStr">
         <is>
           <t>gri-Map 135,230 Ts เพื่อเพิ่ม ผลผ</t>
         </is>
       </c>
     </row>
     <row r="410">
-      <c r="A410" s="2" t="n">
+      <c r="A410" t="n">
         <v>62</v>
       </c>
-      <c r="B410" s="2" t="n">
+      <c r="B410" t="n">
         <v>56</v>
       </c>
-      <c r="C410" s="2" t="inlineStr">
+      <c r="C410" t="inlineStr">
         <is>
           <t>200,000</t>
         </is>
       </c>
-      <c r="D410" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E410" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F410" s="2" t="inlineStr">
-        <is>
-          <t>200,000.0000</t>
-        </is>
-      </c>
-      <c r="G410" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H410" s="2" t="inlineStr">
+      <c r="D410" t="n">
+        <v>0</v>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>200,000</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr"/>
+      <c r="H410" t="inlineStr">
         <is>
           <t>ดการเผา 200,000 Ts เพื่อลดฝุ่นละอ</t>
         </is>
       </c>
     </row>
     <row r="411">
-      <c r="A411" s="2" t="n">
+      <c r="A411" t="n">
         <v>62</v>
       </c>
-      <c r="B411" s="2" t="n">
+      <c r="B411" t="n">
         <v>56</v>
       </c>
-      <c r="C411" s="2" t="inlineStr">
+      <c r="C411" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="D411" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E411" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F411" s="2" t="inlineStr">
-        <is>
-          <t>2.5000</t>
-        </is>
-      </c>
-      <c r="G411" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H411" s="2" t="inlineStr">
+      <c r="D411" t="n">
+        <v>1</v>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr"/>
+      <c r="H411" t="inlineStr">
         <is>
           <t>ละออง PM2.5 ลดการปล่อยก๊าซเรื</t>
         </is>
       </c>
     </row>
     <row r="412">
-      <c r="A412" s="2" t="n">
+      <c r="A412" t="n">
         <v>62</v>
       </c>
-      <c r="B412" s="2" t="n">
+      <c r="B412" t="n">
         <v>56</v>
       </c>
-      <c r="C412" s="2" t="inlineStr">
+      <c r="C412" t="inlineStr">
         <is>
           <t>100,000</t>
         </is>
       </c>
-      <c r="D412" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E412" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F412" s="2" t="inlineStr">
-        <is>
-          <t>100,000.0000</t>
-        </is>
-      </c>
-      <c r="G412" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H412" s="2" t="inlineStr">
+      <c r="D412" t="n">
+        <v>0</v>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>100,000</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr"/>
+      <c r="H412" t="inlineStr">
         <is>
           <t>์บอนต่า 100,000 Ts เพื่อยกระดับคุ</t>
         </is>
       </c>
     </row>
     <row r="413">
-      <c r="A413" s="2" t="n">
+      <c r="A413" t="n">
         <v>62</v>
       </c>
-      <c r="B413" s="2" t="n">
+      <c r="B413" t="n">
         <v>56</v>
       </c>
-      <c r="C413" s="2" t="inlineStr">
+      <c r="C413" t="inlineStr">
         <is>
           <t>5,600</t>
         </is>
       </c>
-      <c r="D413" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E413" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F413" s="2" t="inlineStr">
-        <is>
-          <t>5,600.0000</t>
-        </is>
-      </c>
-      <c r="G413" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H413" s="2" t="inlineStr">
+      <c r="D413" t="n">
+        <v>0</v>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr"/>
+      <c r="H413" t="inlineStr">
         <is>
           <t>ะกอบการ 5,600 แตห่ง ให้ดําเนินธ</t>
         </is>
       </c>
     </row>
     <row r="414">
-      <c r="A414" s="2" t="n">
+      <c r="A414" t="n">
         <v>62</v>
       </c>
-      <c r="B414" s="2" t="n">
+      <c r="B414" t="n">
         <v>56</v>
       </c>
-      <c r="C414" s="2" t="inlineStr">
+      <c r="C414" t="inlineStr">
         <is>
           <t>10,600</t>
         </is>
       </c>
-      <c r="D414" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E414" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F414" s="2" t="inlineStr">
-        <is>
-          <t>10,600.0000</t>
-        </is>
-      </c>
-      <c r="G414" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H414" s="2" t="inlineStr">
+      <c r="D414" t="n">
+        <v>0</v>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>10,600</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr"/>
+      <c r="H414" t="inlineStr">
         <is>
           <t>ะกอบการ 10,600 sig ให้ประยุกต์ใช</t>
         </is>
@@ -14497,7 +14021,7 @@
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>ล้านบาท</t>
+          <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
@@ -14681,36 +14205,32 @@
       </c>
     </row>
     <row r="421">
-      <c r="A421" s="2" t="n">
+      <c r="A421" t="n">
         <v>63</v>
       </c>
-      <c r="B421" s="2" t="n">
+      <c r="B421" t="n">
         <v>57</v>
       </c>
-      <c r="C421" s="2" t="inlineStr">
+      <c r="C421" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="D421" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E421" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F421" s="2" t="inlineStr">
-        <is>
-          <t>2.5000</t>
-        </is>
-      </c>
-      <c r="G421" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H421" s="2" t="inlineStr">
+      <c r="D421" t="n">
+        <v>1</v>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>จำนวน (ล้านคน)</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr"/>
+      <c r="H421" t="inlineStr">
         <is>
           <t>าชนกว่า 2.5 ล้านคน มีความรู้แ</t>
         </is>
@@ -14749,72 +14269,64 @@
       </c>
     </row>
     <row r="423">
-      <c r="A423" s="2" t="n">
+      <c r="A423" t="n">
         <v>63</v>
       </c>
-      <c r="B423" s="2" t="n">
+      <c r="B423" t="n">
         <v>57</v>
       </c>
-      <c r="C423" s="2" t="inlineStr">
+      <c r="C423" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="D423" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E423" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F423" s="2" t="inlineStr">
-        <is>
-          <t>1.5000</t>
-        </is>
-      </c>
-      <c r="G423" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H423" s="2" t="inlineStr">
+      <c r="D423" t="n">
+        <v>1</v>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr"/>
+      <c r="H423" t="inlineStr">
         <is>
           <t>เสียได้ 1.5 ล้านลิตรต่อวัน</t>
         </is>
       </c>
     </row>
     <row r="424">
-      <c r="A424" s="2" t="n">
+      <c r="A424" t="n">
         <v>64</v>
       </c>
-      <c r="B424" s="2" t="n">
+      <c r="B424" t="n">
         <v>58</v>
       </c>
-      <c r="C424" s="2" t="inlineStr">
+      <c r="C424" t="inlineStr">
         <is>
           <t>27.38</t>
         </is>
       </c>
-      <c r="D424" s="2" t="n">
+      <c r="D424" t="n">
         <v>2</v>
       </c>
-      <c r="E424" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F424" s="2" t="inlineStr">
-        <is>
-          <t>27.3800</t>
-        </is>
-      </c>
-      <c r="G424" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H424" s="2" t="inlineStr">
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>จำนวน (ล้านไร่)</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>27.38</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr"/>
+      <c r="H424" t="inlineStr">
         <is>
           <t>่ยงกว่า 27.38 ล้านไร่ พร้อมจัดต</t>
         </is>
@@ -14853,36 +14365,32 @@
       </c>
     </row>
     <row r="426">
-      <c r="A426" s="2" t="n">
+      <c r="A426" t="n">
         <v>64</v>
       </c>
-      <c r="B426" s="2" t="n">
+      <c r="B426" t="n">
         <v>58</v>
       </c>
-      <c r="C426" s="2" t="inlineStr">
+      <c r="C426" t="inlineStr">
         <is>
           <t>73.85</t>
         </is>
       </c>
-      <c r="D426" s="2" t="n">
+      <c r="D426" t="n">
         <v>2</v>
       </c>
-      <c r="E426" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F426" s="2" t="inlineStr">
-        <is>
-          <t>73.8500</t>
-        </is>
-      </c>
-      <c r="G426" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H426" s="2" t="inlineStr">
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>จำนวน (ล้านไร่)</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>73.85</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr"/>
+      <c r="H426" t="inlineStr">
         <is>
           <t>นุรักษ์ 73.85 ล้านไร่ และป่าสงว</t>
         </is>
@@ -14905,7 +14413,7 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>ไม่ทราบหน่วย</t>
+          <t>จำนวน (นับ)</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
@@ -14953,36 +14461,32 @@
       </c>
     </row>
     <row r="429">
-      <c r="A429" s="2" t="n">
+      <c r="A429" t="n">
         <v>64</v>
       </c>
-      <c r="B429" s="2" t="n">
+      <c r="B429" t="n">
         <v>58</v>
       </c>
-      <c r="C429" s="2" t="inlineStr">
+      <c r="C429" t="inlineStr">
         <is>
           <t>1.74</t>
         </is>
       </c>
-      <c r="D429" s="2" t="n">
+      <c r="D429" t="n">
         <v>2</v>
       </c>
-      <c r="E429" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F429" s="2" t="inlineStr">
-        <is>
-          <t>1.7400</t>
-        </is>
-      </c>
-      <c r="G429" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H429" s="2" t="inlineStr">
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>จำนวน (ล้านไร่)</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr"/>
+      <c r="H429" t="inlineStr">
         <is>
           <t>้อยกว่า 1.74 ล้านไร่ และคําหนด</t>
         </is>
@@ -15053,36 +14557,32 @@
       </c>
     </row>
     <row r="432">
-      <c r="A432" s="2" t="n">
+      <c r="A432" t="n">
         <v>65</v>
       </c>
-      <c r="B432" s="2" t="n">
+      <c r="B432" t="n">
         <v>59</v>
       </c>
-      <c r="C432" s="2" t="inlineStr">
+      <c r="C432" t="inlineStr">
         <is>
           <t>1.40</t>
         </is>
       </c>
-      <c r="D432" s="2" t="n">
+      <c r="D432" t="n">
         <v>2</v>
       </c>
-      <c r="E432" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F432" s="2" t="inlineStr">
-        <is>
-          <t>1.4000</t>
-        </is>
-      </c>
-      <c r="G432" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H432" s="2" t="inlineStr">
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr"/>
+      <c r="H432" t="inlineStr">
         <is>
           <t>อันตราย 1.40 ล้านต้นต่อปี  และ</t>
         </is>
@@ -15281,36 +14781,32 @@
       </c>
     </row>
     <row r="439">
-      <c r="A439" s="2" t="n">
+      <c r="A439" t="n">
         <v>67</v>
       </c>
-      <c r="B439" s="2" t="n">
+      <c r="B439" t="n">
         <v>61</v>
       </c>
-      <c r="C439" s="2" t="inlineStr">
+      <c r="C439" t="inlineStr">
         <is>
           <t>13.65</t>
         </is>
       </c>
-      <c r="D439" s="2" t="n">
+      <c r="D439" t="n">
         <v>2</v>
       </c>
-      <c r="E439" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F439" s="2" t="inlineStr">
-        <is>
-          <t>13.6500</t>
-        </is>
-      </c>
-      <c r="G439" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H439" s="2" t="inlineStr">
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>จำนวน (ล้านราย)</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>13.65</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr"/>
+      <c r="H439" t="inlineStr">
         <is>
           <t>้บริการ 13.65 ล้านราย  พัฒนาโคร</t>
         </is>
@@ -15409,108 +14905,96 @@
       </c>
     </row>
     <row r="443">
-      <c r="A443" s="2" t="n">
+      <c r="A443" t="n">
         <v>68</v>
       </c>
-      <c r="B443" s="2" t="n">
+      <c r="B443" t="n">
         <v>62</v>
       </c>
-      <c r="C443" s="2" t="inlineStr">
+      <c r="C443" t="inlineStr">
         <is>
           <t>611,220</t>
         </is>
       </c>
-      <c r="D443" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E443" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F443" s="2" t="inlineStr">
-        <is>
-          <t>611,220.0000</t>
-        </is>
-      </c>
-      <c r="G443" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H443" s="2" t="inlineStr">
+      <c r="D443" t="n">
+        <v>0</v>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>611,220</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr"/>
+      <c r="H443" t="inlineStr">
         <is>
           <t>้อยกว่า 611,220 au.  จากสินค้าและ</t>
         </is>
       </c>
     </row>
     <row r="444">
-      <c r="A444" s="2" t="n">
+      <c r="A444" t="n">
         <v>68</v>
       </c>
-      <c r="B444" s="2" t="n">
+      <c r="B444" t="n">
         <v>62</v>
       </c>
-      <c r="C444" s="2" t="inlineStr">
+      <c r="C444" t="inlineStr">
         <is>
           <t>2,517,700</t>
         </is>
       </c>
-      <c r="D444" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E444" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F444" s="2" t="inlineStr">
-        <is>
-          <t>2,517,700.0000</t>
-        </is>
-      </c>
-      <c r="G444" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H444" s="2" t="inlineStr">
+      <c r="D444" t="n">
+        <v>0</v>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>จำนวน (นับ)</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>2,517,700</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr"/>
+      <c r="H444" t="inlineStr">
         <is>
           <t>้อยกว่า 2,517,700 au. อากภาษีรายได้</t>
         </is>
       </c>
     </row>
     <row r="445">
-      <c r="A445" s="2" t="n">
+      <c r="A445" t="n">
         <v>68</v>
       </c>
-      <c r="B445" s="2" t="n">
+      <c r="B445" t="n">
         <v>62</v>
       </c>
-      <c r="C445" s="2" t="inlineStr">
+      <c r="C445" t="inlineStr">
         <is>
           <t>7,732.0</t>
         </is>
       </c>
-      <c r="D445" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E445" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F445" s="2" t="inlineStr">
-        <is>
-          <t>7,732.0000</t>
-        </is>
-      </c>
-      <c r="G445" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H445" s="2" t="inlineStr"/>
+      <c r="D445" t="n">
+        <v>1</v>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>7,732.0</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr"/>
+      <c r="H445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" s="2" t="n">
@@ -15549,72 +15033,64 @@
       </c>
     </row>
     <row r="447">
-      <c r="A447" s="2" t="n">
+      <c r="A447" t="n">
         <v>68</v>
       </c>
-      <c r="B447" s="2" t="n">
+      <c r="B447" t="n">
         <v>62</v>
       </c>
-      <c r="C447" s="2" t="inlineStr">
+      <c r="C447" t="inlineStr">
         <is>
           <t>41,170</t>
         </is>
       </c>
-      <c r="D447" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E447" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F447" s="2" t="inlineStr">
-        <is>
-          <t>41,170.0000</t>
-        </is>
-      </c>
-      <c r="G447" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H447" s="2" t="inlineStr">
+      <c r="D447" t="n">
+        <v>0</v>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>41,170</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr"/>
+      <c r="H447" t="inlineStr">
         <is>
           <t>ศุลภากร 41,170 sig  และถําเนินคด</t>
         </is>
       </c>
     </row>
     <row r="448">
-      <c r="A448" s="2" t="n">
+      <c r="A448" t="n">
         <v>69</v>
       </c>
-      <c r="B448" s="2" t="n">
+      <c r="B448" t="n">
         <v>63</v>
       </c>
-      <c r="C448" s="2" t="inlineStr">
+      <c r="C448" t="inlineStr">
         <is>
           <t>1,247.0</t>
         </is>
       </c>
-      <c r="D448" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E448" s="2" t="inlineStr">
-        <is>
-          <t>ล้านบาท</t>
-        </is>
-      </c>
-      <c r="F448" s="2" t="inlineStr">
-        <is>
-          <t>1,247.0000</t>
-        </is>
-      </c>
-      <c r="G448" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
-      <c r="H448" s="2" t="inlineStr"/>
+      <c r="D448" t="n">
+        <v>1</v>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>ไม่ทราบหน่วย</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>1,247.0</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr"/>
+      <c r="H448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" s="2" t="n">

--- a/output/audit_reports/B2G_Numbers_Audit.xlsx
+++ b/output/audit_reports/B2G_Numbers_Audit.xlsx
@@ -913,32 +913,36 @@
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>788,000</t>
         </is>
       </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>ไม่ทราบหน่วย</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>788,000</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
+      <c r="D17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>ล้านบาท</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>788,000.0000</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>บ.  uA} 788,000 au งบประมาณ ผู| |</t>
         </is>
@@ -1177,160 +1181,180 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
+      <c r="A25" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>584,300</t>
         </is>
       </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>ไม่ทราบหน่วย</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>584,300</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
+      <c r="D25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>ล้านบาท</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>584,300.0000</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>ดเก็บ 3,584,300 au.  หักลด 584,30</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
+      <c r="A26" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>3,788,000</t>
         </is>
       </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>ไม่ทราบหน่วย</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>3,788,000</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
+      <c r="D26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>ล้านบาท</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>3,788,000.0000</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>G 2570  3,788,000 au.  ที่มา : กระท</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
+      <c r="A27" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>3,584,300</t>
         </is>
       </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>ไม่ทราบหน่วย</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>3,584,300</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
+      <c r="D27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>ล้านบาท</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>3,584,300.0000</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>จัดเก็บ 3,584,300 au.  หักลด 584,30</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
+      <c r="A28" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>788,000</t>
         </is>
       </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>ไม่ทราบหน่วย</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>788,000</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
+      <c r="D28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>ล้านบาท</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>788,000.0000</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>2570  3,788,000 au.  ที่มา : กระท</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
+      <c r="A29" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>3,000,000</t>
         </is>
       </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>ไม่ทราบหน่วย</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>3,000,000</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
+      <c r="D29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>ล้านบาท</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>3,000,000.0000</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>ินกู้ , 3,000,000 au.  SINUS:N1@UNI</t>
         </is>
@@ -1481,32 +1505,36 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
+      <c r="A34" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="B34" t="n">
+      <c r="B34" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>155,880</t>
         </is>
       </c>
-      <c r="D34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>ไม่ทราบหน่วย</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>155,880</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
+      <c r="D34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>ล้านบาท</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>155,880.0000</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>500 ลบ. 155,880 au.  REVENUE รายไ</t>
         </is>
@@ -1893,32 +1921,36 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="n">
+      <c r="A46" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="B46" t="n">
+      <c r="B46" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>3,788,000</t>
         </is>
       </c>
-      <c r="D46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>บาท (ต่อหน่วย)</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>3,788,000</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr">
+      <c r="D46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>ล้านบาท</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>3,788,000.0000</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>บประมาณ 3,788,000 ลส้านบาท  ๕รรพ SS</t>
         </is>
@@ -2501,7 +2533,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>จำนวน (ล้านราย)</t>
+          <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3237,7 +3269,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>จำนวน (ล้านคน)</t>
+          <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3681,7 +3713,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>จำนวน (ล้านคน)</t>
+          <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3713,7 +3745,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>จำนวน (ล้านคน)</t>
+          <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3809,7 +3841,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>จำนวน (ล้านคน)</t>
+          <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -3841,7 +3873,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>จำนวน (ล้านคน)</t>
+          <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -3905,7 +3937,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>จำนวน (ล้านคน)</t>
+          <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -3969,7 +4001,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>จำนวน (ล้านคน)</t>
+          <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4001,7 +4033,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>จำนวน (ล้านคน)</t>
+          <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4097,7 +4129,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>จำนวน (ล้านคน)</t>
+          <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4129,7 +4161,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>จำนวน (ล้านคน)</t>
+          <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4161,7 +4193,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>จำนวน (ล้านคน)</t>
+          <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4641,7 +4673,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>จำนวน (ล้านราย)</t>
+          <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -4737,7 +4769,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>จำนวน (ล้านราย)</t>
+          <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -6181,32 +6213,36 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="n">
+      <c r="A175" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="B175" t="n">
+      <c r="B175" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="C175" t="inlineStr">
+      <c r="C175" s="2" t="inlineStr">
         <is>
           <t>1,503,088.8</t>
         </is>
       </c>
-      <c r="D175" t="n">
-        <v>1</v>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>ไม่ทราบหน่วย</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>1,503,088.8</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr"/>
-      <c r="H175" t="inlineStr">
+      <c r="D175" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>ล้านบาท</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>1,503,088.8000</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t>ล       1,503,088.8 aun  ด้านเศรษฐกิจ</t>
         </is>
@@ -6457,64 +6493,72 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="n">
+      <c r="A183" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="B183" t="n">
+      <c r="B183" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="C183" t="inlineStr">
+      <c r="C183" s="2" t="inlineStr">
         <is>
           <t>185,939.3</t>
         </is>
       </c>
-      <c r="D183" t="n">
-        <v>1</v>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>ไม่ทราบหน่วย</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>185,939.3</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr"/>
-      <c r="H183" t="inlineStr">
+      <c r="D183" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>ล้านบาท</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>185,939.3000</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
         <is>
           <t>185,939.3 au. ด้านการค้า “เ</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="n">
+      <c r="A184" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="B184" t="n">
+      <c r="B184" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="C184" t="inlineStr">
+      <c r="C184" s="2" t="inlineStr">
         <is>
           <t>11,264.1</t>
         </is>
       </c>
-      <c r="D184" t="n">
-        <v>1</v>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>ไม่ทราบหน่วย</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>11,264.1</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr"/>
-      <c r="H184" t="inlineStr">
+      <c r="D184" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>ล้านบาท</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>11,264.1000</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
         <is>
           <t>11,264.1 au.  ค้านการต่างป</t>
         </is>
@@ -6557,32 +6601,36 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="n">
+      <c r="A186" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="B186" t="n">
+      <c r="B186" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="C186" t="inlineStr">
+      <c r="C186" s="2" t="inlineStr">
         <is>
           <t>436,287.9</t>
         </is>
       </c>
-      <c r="D186" t="n">
-        <v>1</v>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>ไม่ทราบหน่วย</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>436,287.9</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr"/>
-      <c r="H186" t="inlineStr">
+      <c r="D186" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>ล้านบาท</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>436,287.9000</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
         <is>
           <t>436,287.9 au.  สร้างโอกาสกา</t>
         </is>
@@ -6625,32 +6673,36 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="n">
+      <c r="A188" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="B188" t="n">
+      <c r="B188" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="C188" t="inlineStr">
+      <c r="C188" s="2" t="inlineStr">
         <is>
           <t>1,117.6</t>
         </is>
       </c>
-      <c r="D188" t="n">
-        <v>1</v>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>ไม่ทราบหน่วย</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>1,117.6</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr"/>
-      <c r="H188" t="inlineStr">
+      <c r="D188" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>ล้านบาท</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>1,117.6000</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="inlineStr">
         <is>
           <t>1,117.6 au.  เสริมสร้างเส</t>
         </is>
@@ -6765,32 +6817,36 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="n">
+      <c r="A192" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="B192" t="n">
+      <c r="B192" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="C192" t="inlineStr">
+      <c r="C192" s="2" t="inlineStr">
         <is>
           <t>2,114.5</t>
         </is>
       </c>
-      <c r="D192" t="n">
-        <v>1</v>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>ไม่ทราบหน่วย</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>2,114.5</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr"/>
-      <c r="H192" t="inlineStr">
+      <c r="D192" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>ล้านบาท</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>2,114.5000</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="inlineStr">
         <is>
           <t>2,114.5 au.  BUDGET BUREA</t>
         </is>
@@ -6977,32 +7033,36 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" t="n">
+      <c r="A198" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="B198" t="n">
+      <c r="B198" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="C198" t="inlineStr">
+      <c r="C198" s="2" t="inlineStr">
         <is>
           <t>4,940.4</t>
         </is>
       </c>
-      <c r="D198" t="n">
-        <v>1</v>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>ไม่ทราบหน่วย</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>4,940.4</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr"/>
-      <c r="H198" t="inlineStr">
+      <c r="D198" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>ล้านบาท</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>4,940.4000</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
         <is>
           <t>4,940.4 au.  ด้านภัยพิบัต</t>
         </is>
@@ -7081,96 +7141,108 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" t="n">
+      <c r="A201" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="B201" t="n">
+      <c r="B201" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="C201" t="inlineStr">
+      <c r="C201" s="2" t="inlineStr">
         <is>
           <t>115,694.0</t>
         </is>
       </c>
-      <c r="D201" t="n">
-        <v>1</v>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>ไม่ทราบหน่วย</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>115,694.0</t>
-        </is>
-      </c>
-      <c r="G201" t="inlineStr"/>
-      <c r="H201" t="inlineStr">
+      <c r="D201" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>ล้านบาท</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>115,694.0000</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="H201" s="2" t="inlineStr">
         <is>
           <t>115,694.0 au. พัฒนาระบบประก</t>
         </is>
       </c>
     </row>
     <row r="202">
-      <c r="A202" t="n">
+      <c r="A202" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="B202" t="n">
+      <c r="B202" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="C202" t="inlineStr">
+      <c r="C202" s="2" t="inlineStr">
         <is>
           <t>4,800.0</t>
         </is>
       </c>
-      <c r="D202" t="n">
-        <v>1</v>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>ไม่ทราบหน่วย</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>4,800.0</t>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr"/>
-      <c r="H202" t="inlineStr">
+      <c r="D202" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>ล้านบาท</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>4,800.0000</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="inlineStr">
         <is>
           <t>4,800.0 au. ผลักด้นให้ประ</t>
         </is>
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="n">
+      <c r="A203" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="B203" t="n">
+      <c r="B203" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="C203" t="inlineStr">
+      <c r="C203" s="2" t="inlineStr">
         <is>
           <t>44,492.1</t>
         </is>
       </c>
-      <c r="D203" t="n">
-        <v>1</v>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>ไม่ทราบหน่วย</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>44,492.1</t>
-        </is>
-      </c>
-      <c r="G203" t="inlineStr"/>
-      <c r="H203" t="inlineStr">
+      <c r="D203" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>ล้านบาท</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>44,492.1000</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="H203" s="2" t="inlineStr">
         <is>
           <t>44,492.1 au. การอนุรักษ์แล</t>
         </is>
@@ -7213,64 +7285,72 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" t="n">
+      <c r="A205" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="B205" t="n">
+      <c r="B205" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="C205" t="inlineStr">
+      <c r="C205" s="2" t="inlineStr">
         <is>
           <t>25,537.2</t>
         </is>
       </c>
-      <c r="D205" t="n">
-        <v>1</v>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>ไม่ทราบหน่วย</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>25,537.2</t>
-        </is>
-      </c>
-      <c r="G205" t="inlineStr"/>
-      <c r="H205" t="inlineStr">
+      <c r="D205" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>ล้านบาท</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>25,537.2000</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="H205" s="2" t="inlineStr">
         <is>
           <t>25,537.2 au.  การปฏิรูประบ</t>
         </is>
       </c>
     </row>
     <row r="206">
-      <c r="A206" t="n">
+      <c r="A206" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="B206" t="n">
+      <c r="B206" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="C206" t="inlineStr">
+      <c r="C206" s="2" t="inlineStr">
         <is>
           <t>7,732.0</t>
         </is>
       </c>
-      <c r="D206" t="n">
-        <v>1</v>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>ไม่ทราบหน่วย</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>7,732.0</t>
-        </is>
-      </c>
-      <c r="G206" t="inlineStr"/>
-      <c r="H206" t="inlineStr">
+      <c r="D206" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>ล้านบาท</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>7,732.0000</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="inlineStr">
         <is>
           <t>7,732.0 au.  การพัฒนากฎหม</t>
         </is>
@@ -7937,32 +8017,36 @@
       <c r="H226" t="inlineStr"/>
     </row>
     <row r="227">
-      <c r="A227" t="n">
+      <c r="A227" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="B227" t="n">
+      <c r="B227" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="C227" t="inlineStr">
+      <c r="C227" s="2" t="inlineStr">
         <is>
           <t>709.5</t>
         </is>
       </c>
-      <c r="D227" t="n">
-        <v>1</v>
-      </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>ไม่ทราบหน่วย</t>
-        </is>
-      </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>709.5</t>
-        </is>
-      </c>
-      <c r="G227" t="inlineStr"/>
-      <c r="H227" t="inlineStr">
+      <c r="D227" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>ล้านบาท</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>709.5000</t>
+        </is>
+      </c>
+      <c r="G227" s="2" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="H227" s="2" t="inlineStr">
         <is>
           <t>s:ui1du 709.5 auuain  BUDGET BU</t>
         </is>
@@ -8053,7 +8137,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>จำนวน (ล้านคน)</t>
+          <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -8249,7 +8333,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>จำนวน (ล้านคน)</t>
+          <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -8381,7 +8465,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>จำนวน (ล้านคน)</t>
+          <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -8477,7 +8561,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>จำนวน (ล้านคน)</t>
+          <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -8973,7 +9057,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>จำนวน (ล้านคน)</t>
+          <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -9473,7 +9557,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>จำนวน (ล้านคน)</t>
+          <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -9521,32 +9605,36 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" t="n">
+      <c r="A276" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="B276" t="n">
+      <c r="B276" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="C276" t="inlineStr">
+      <c r="C276" s="2" t="inlineStr">
         <is>
           <t>219,902.2</t>
         </is>
       </c>
-      <c r="D276" t="n">
-        <v>1</v>
-      </c>
-      <c r="E276" t="inlineStr">
-        <is>
-          <t>บาท (ต่อหน่วย)</t>
-        </is>
-      </c>
-      <c r="F276" t="inlineStr">
-        <is>
-          <t>219,902.2</t>
-        </is>
-      </c>
-      <c r="G276" t="inlineStr"/>
-      <c r="H276" t="inlineStr">
+      <c r="D276" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E276" s="2" t="inlineStr">
+        <is>
+          <t>ล้านบาท</t>
+        </is>
+      </c>
+      <c r="F276" s="2" t="inlineStr">
+        <is>
+          <t>219,902.2000</t>
+        </is>
+      </c>
+      <c r="G276" s="2" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="H276" s="2" t="inlineStr">
         <is>
           <t>ป 219,902.2 ล่านบาท  เร่งจัดก</t>
         </is>
@@ -9569,7 +9657,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>จำนวน (ล้านคน)</t>
+          <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -9665,7 +9753,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>จำนวน (ล้านคน)</t>
+          <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -9793,7 +9881,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>จำนวน (ล้านคน)</t>
+          <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -9841,32 +9929,36 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" t="n">
+      <c r="A286" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="B286" t="n">
+      <c r="B286" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C286" t="inlineStr">
+      <c r="C286" s="2" t="inlineStr">
         <is>
           <t>4,399</t>
         </is>
       </c>
-      <c r="D286" t="n">
-        <v>0</v>
-      </c>
-      <c r="E286" t="inlineStr">
-        <is>
-          <t>ไม่ทราบหน่วย</t>
-        </is>
-      </c>
-      <c r="F286" t="inlineStr">
-        <is>
-          <t>4,399</t>
-        </is>
-      </c>
-      <c r="G286" t="inlineStr"/>
-      <c r="H286" t="inlineStr">
+      <c r="D286" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E286" s="2" t="inlineStr">
+        <is>
+          <t>ล้านบาท</t>
+        </is>
+      </c>
+      <c r="F286" s="2" t="inlineStr">
+        <is>
+          <t>4,399.0000</t>
+        </is>
+      </c>
+      <c r="G286" s="2" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="H286" s="2" t="inlineStr">
         <is>
           <t>้อยกว่า 4,399 au.  ผู้ประกอบการ</t>
         </is>
@@ -10169,32 +10261,36 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" t="n">
+      <c r="A296" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="B296" t="n">
+      <c r="B296" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="C296" t="inlineStr">
+      <c r="C296" s="2" t="inlineStr">
         <is>
           <t>14,357.0</t>
         </is>
       </c>
-      <c r="D296" t="n">
-        <v>1</v>
-      </c>
-      <c r="E296" t="inlineStr">
-        <is>
-          <t>บาท (ต่อหน่วย)</t>
-        </is>
-      </c>
-      <c r="F296" t="inlineStr">
-        <is>
-          <t>14,357.0</t>
-        </is>
-      </c>
-      <c r="G296" t="inlineStr"/>
-      <c r="H296" t="inlineStr">
+      <c r="D296" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E296" s="2" t="inlineStr">
+        <is>
+          <t>ล้านบาท</t>
+        </is>
+      </c>
+      <c r="F296" s="2" t="inlineStr">
+        <is>
+          <t>14,357.0000</t>
+        </is>
+      </c>
+      <c r="G296" s="2" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="H296" s="2" t="inlineStr">
         <is>
           <t>น”      14,357.0 ลานบาท  สร้างแรงอ</t>
         </is>
@@ -10249,7 +10345,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>จำนวน (ล้านไร่)</t>
+          <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -10313,7 +10409,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>จำนวน (ล้านราย)</t>
+          <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -10697,64 +10793,72 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" t="n">
+      <c r="A312" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="B312" t="n">
+      <c r="B312" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="C312" t="inlineStr">
+      <c r="C312" s="2" t="inlineStr">
         <is>
           <t>744.9</t>
         </is>
       </c>
-      <c r="D312" t="n">
-        <v>1</v>
-      </c>
-      <c r="E312" t="inlineStr">
-        <is>
-          <t>บาท (ต่อหน่วย)</t>
-        </is>
-      </c>
-      <c r="F312" t="inlineStr">
-        <is>
-          <t>744.9</t>
-        </is>
-      </c>
-      <c r="G312" t="inlineStr"/>
-      <c r="H312" t="inlineStr">
+      <c r="D312" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E312" s="2" t="inlineStr">
+        <is>
+          <t>ล้านบาท</t>
+        </is>
+      </c>
+      <c r="F312" s="2" t="inlineStr">
+        <is>
+          <t>744.9000</t>
+        </is>
+      </c>
+      <c r="G312" s="2" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="H312" s="2" t="inlineStr">
         <is>
           <t>”       744.9 ลานบาท  : การขับเ</t>
         </is>
       </c>
     </row>
     <row r="313">
-      <c r="A313" t="n">
+      <c r="A313" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="B313" t="n">
+      <c r="B313" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="C313" t="inlineStr">
+      <c r="C313" s="2" t="inlineStr">
         <is>
           <t>19,845.2</t>
         </is>
       </c>
-      <c r="D313" t="n">
-        <v>1</v>
-      </c>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>บาท (ต่อหน่วย)</t>
-        </is>
-      </c>
-      <c r="F313" t="inlineStr">
-        <is>
-          <t>19,845.2</t>
-        </is>
-      </c>
-      <c r="G313" t="inlineStr"/>
-      <c r="H313" t="inlineStr">
+      <c r="D313" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E313" s="2" t="inlineStr">
+        <is>
+          <t>ล้านบาท</t>
+        </is>
+      </c>
+      <c r="F313" s="2" t="inlineStr">
+        <is>
+          <t>19,845.2000</t>
+        </is>
+      </c>
+      <c r="G313" s="2" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="H313" s="2" t="inlineStr">
         <is>
           <t>อ 19,845.2 ล่านบาท  ปข้องกัน</t>
         </is>
@@ -11601,7 +11705,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>จำนวน (ล้านราย)</t>
+          <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
@@ -12253,7 +12357,7 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>จำนวน (ล้านคน)</t>
+          <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
@@ -12285,7 +12389,7 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>จำนวน (ล้านคน)</t>
+          <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
@@ -12509,7 +12613,7 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>จำนวน (ล้านคน)</t>
+          <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
@@ -12765,7 +12869,7 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>จำนวน (ล้านคน)</t>
+          <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
@@ -12849,32 +12953,36 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379" t="n">
+      <c r="A379" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="B379" t="n">
+      <c r="B379" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="C379" t="inlineStr">
+      <c r="C379" s="2" t="inlineStr">
         <is>
           <t>303,490</t>
         </is>
       </c>
-      <c r="D379" t="n">
-        <v>0</v>
-      </c>
-      <c r="E379" t="inlineStr">
-        <is>
-          <t>ไม่ทราบหน่วย</t>
-        </is>
-      </c>
-      <c r="F379" t="inlineStr">
-        <is>
-          <t>303,490</t>
-        </is>
-      </c>
-      <c r="G379" t="inlineStr"/>
-      <c r="H379" t="inlineStr">
+      <c r="D379" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E379" s="2" t="inlineStr">
+        <is>
+          <t>ล้านบาท</t>
+        </is>
+      </c>
+      <c r="F379" s="2" t="inlineStr">
+        <is>
+          <t>303,490.0000</t>
+        </is>
+      </c>
+      <c r="G379" s="2" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="H379" s="2" t="inlineStr">
         <is>
           <t>ในชุมชน 303,490 au ได้รับการส่งเส</t>
         </is>
@@ -12993,7 +13101,7 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>จำนวน (ล้านราย)</t>
+          <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
@@ -14221,7 +14329,7 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>จำนวน (ล้านคน)</t>
+          <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
@@ -14317,7 +14425,7 @@
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>จำนวน (ล้านไร่)</t>
+          <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
@@ -14381,7 +14489,7 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>จำนวน (ล้านไร่)</t>
+          <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
@@ -14477,7 +14585,7 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>จำนวน (ล้านไร่)</t>
+          <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
@@ -14797,7 +14905,7 @@
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>จำนวน (ล้านราย)</t>
+          <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
       <c r="F439" t="inlineStr">
@@ -14905,64 +15013,72 @@
       </c>
     </row>
     <row r="443">
-      <c r="A443" t="n">
+      <c r="A443" s="2" t="n">
         <v>68</v>
       </c>
-      <c r="B443" t="n">
+      <c r="B443" s="2" t="n">
         <v>62</v>
       </c>
-      <c r="C443" t="inlineStr">
+      <c r="C443" s="2" t="inlineStr">
         <is>
           <t>611,220</t>
         </is>
       </c>
-      <c r="D443" t="n">
-        <v>0</v>
-      </c>
-      <c r="E443" t="inlineStr">
-        <is>
-          <t>ไม่ทราบหน่วย</t>
-        </is>
-      </c>
-      <c r="F443" t="inlineStr">
-        <is>
-          <t>611,220</t>
-        </is>
-      </c>
-      <c r="G443" t="inlineStr"/>
-      <c r="H443" t="inlineStr">
+      <c r="D443" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E443" s="2" t="inlineStr">
+        <is>
+          <t>ล้านบาท</t>
+        </is>
+      </c>
+      <c r="F443" s="2" t="inlineStr">
+        <is>
+          <t>611,220.0000</t>
+        </is>
+      </c>
+      <c r="G443" s="2" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="H443" s="2" t="inlineStr">
         <is>
           <t>้อยกว่า 611,220 au.  จากสินค้าและ</t>
         </is>
       </c>
     </row>
     <row r="444">
-      <c r="A444" t="n">
+      <c r="A444" s="2" t="n">
         <v>68</v>
       </c>
-      <c r="B444" t="n">
+      <c r="B444" s="2" t="n">
         <v>62</v>
       </c>
-      <c r="C444" t="inlineStr">
+      <c r="C444" s="2" t="inlineStr">
         <is>
           <t>2,517,700</t>
         </is>
       </c>
-      <c r="D444" t="n">
-        <v>0</v>
-      </c>
-      <c r="E444" t="inlineStr">
-        <is>
-          <t>จำนวน (นับ)</t>
-        </is>
-      </c>
-      <c r="F444" t="inlineStr">
-        <is>
-          <t>2,517,700</t>
-        </is>
-      </c>
-      <c r="G444" t="inlineStr"/>
-      <c r="H444" t="inlineStr">
+      <c r="D444" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E444" s="2" t="inlineStr">
+        <is>
+          <t>ล้านบาท</t>
+        </is>
+      </c>
+      <c r="F444" s="2" t="inlineStr">
+        <is>
+          <t>2,517,700.0000</t>
+        </is>
+      </c>
+      <c r="G444" s="2" t="inlineStr">
+        <is>
+          <t>ใช่</t>
+        </is>
+      </c>
+      <c r="H444" s="2" t="inlineStr">
         <is>
           <t>้อยกว่า 2,517,700 au. อากภาษีรายได้</t>
         </is>

--- a/output/audit_reports/B2G_Numbers_Audit.xlsx
+++ b/output/audit_reports/B2G_Numbers_Audit.xlsx
@@ -470,12 +470,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>รูปแบบที่ควรเป็น</t>
+          <t>ถ้าวางจุด4จากขวา</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>ต้องแก้</t>
+          <t>ยืนยัน(ผู้ตรวจ)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -504,11 +504,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>19,882.4</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
@@ -536,11 +532,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>20,618.0</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
@@ -568,11 +560,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -596,11 +584,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -624,11 +608,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>1.7</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -652,11 +632,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2.7</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -680,11 +656,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -708,11 +680,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -736,11 +704,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -764,11 +728,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>3.3</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -792,11 +752,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -820,11 +776,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -848,11 +800,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -876,11 +824,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -904,11 +848,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -934,14 +874,10 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>788,000.0000</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>78.8000</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
           <t>บ.  uA} 788,000 au งบประมาณ ผู| |</t>
@@ -970,14 +906,10 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3,788,000.0000</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>378.8000</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t>2570 | 3,788,000 ลบ. รอยล 8</t>
@@ -1004,11 +936,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>4.4</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
@@ -1036,11 +964,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>3.9</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
@@ -1068,11 +992,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>3.3</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
@@ -1100,11 +1020,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2.7</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
@@ -1132,11 +1048,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
@@ -1166,14 +1078,10 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3,000,000.0000</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>300.0000</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
           <t>าลสุทธิ 3,000,000 ลบ.  uA} 788,000</t>
@@ -1202,14 +1110,10 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>584,300.0000</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>58.4300</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
           <t>ดเก็บ 3,584,300 au.  หักลด 584,30</t>
@@ -1238,14 +1142,10 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3,788,000.0000</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>378.8000</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
           <t>G 2570  3,788,000 au.  ที่มา : กระท</t>
@@ -1274,14 +1174,10 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3,584,300.0000</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>358.4300</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr">
         <is>
           <t>จัดเก็บ 3,584,300 au.  หักลด 584,30</t>
@@ -1310,14 +1206,10 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>788,000.0000</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>78.8000</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
           <t>2570  3,788,000 au.  ที่มา : กระท</t>
@@ -1346,14 +1238,10 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3,000,000.0000</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>300.0000</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
           <t>ินกู้ , 3,000,000 au.  SINUS:N1@UNI</t>
@@ -1382,14 +1270,10 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2,517,700.0000</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>251.7700</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
           <t>การอื่น 2,517,700 au. 611,220 ลบ. 1</t>
@@ -1418,14 +1302,10 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>611,220.0000</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>61.1220</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
           <t>700 au. 611,220 ลบ. 116,000 ลบ. 1</t>
@@ -1454,14 +1334,10 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>116,000.0000</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>11.6000</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
           <t>220 ลบ. 116,000 ลบ. 183,500 ลบ. 1</t>
@@ -1490,14 +1366,10 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>183,500.0000</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>18.3500</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
           <t>000 ลบ. 183,500 ลบ. 155,880 au.</t>
@@ -1526,14 +1398,10 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>155,880.0000</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>15.5880</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
           <t>500 ลบ. 155,880 au.  REVENUE รายไ</t>
@@ -1562,14 +1430,10 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>310,950.3000</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>310.9503</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr">
         <is>
           <t>310,950.3 ล้านบาท  ง ป | (4</t>
@@ -1596,11 +1460,7 @@
           <t>ร้อยละ/สัดส่วน</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>8.2</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
@@ -1630,14 +1490,10 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>12,868,850.9000</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>12,868.8509</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
           <t>2569 ก  12,868,850.9 ล้านบาท 66.8% ของ</t>
@@ -1664,11 +1520,7 @@
           <t>ร้อยละ/สัดส่วน</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>66.8</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
@@ -1698,14 +1550,10 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>462,470.3000</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>462.4703</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
           <t>ปี 2570 462,470.3 ล้านบาท  omนม แนน</t>
@@ -1734,14 +1582,10 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>151,520.0000</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>15.1520</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
           <t>รมเนียม 151,520 ล้านบาท</t>
@@ -1770,14 +1614,10 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>341,018.2000</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>341.0182</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
           <t>69      341,018.2 ล้านบาท  ที่มา: 1</t>
@@ -1806,14 +1646,10 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2,857,405.2000</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>2,857.4052</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr">
         <is>
           <t>) ก | 2,857,405.2 ล้านบาท /  J</t>
@@ -1840,11 +1676,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>151,520</t>
-        </is>
-      </c>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
     </row>
@@ -1870,14 +1702,10 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>71,038.1000</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>71.0381</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr">
         <is>
           <t>นคงคลัง 71,038.1 ล้านบาท 2. รายจ่า</t>
@@ -1906,14 +1734,10 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>10,096.7000</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>10.0967</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr">
         <is>
           <t>จํานวน 10,096.7 ล้านบาท</t>
@@ -1942,14 +1766,10 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>3,788,000.0000</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>378.8000</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr">
         <is>
           <t>บประมาณ 3,788,000 ลส้านบาท  ๕รรพ SS</t>
@@ -1978,14 +1798,10 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>789,171.5000</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>789.1715</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr">
         <is>
           <t>1  789,171.5 ล้านบาท .”  (เซีช</t>
@@ -2014,14 +1830,10 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>3,788,000.0000</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>3,788.0000</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>บประมาณ 3,788,000.0 ล้านบาท  ane  il</t>
@@ -2048,11 +1860,7 @@
           <t>ร้อยละ/สัดส่วน</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>3.6</t>
-        </is>
-      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
@@ -2082,14 +1890,10 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>137,507.8000</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>137.5078</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr">
         <is>
           <t>ภาครัช  137,507.8 ล้านบาท</t>
@@ -2116,11 +1920,7 @@
           <t>ร้อยละ/สัดส่วน</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>17.9</t>
-        </is>
-      </c>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
@@ -2150,14 +1950,10 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>676,320.2000</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>676.3202</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr">
         <is>
           <t>676,320.2 ล้านบาท (3.6%)</t>
@@ -2184,11 +1980,7 @@
           <t>ร้อยละ/สัดส่วน</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>16.1</t>
-        </is>
-      </c>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
@@ -2218,14 +2010,10 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>611,194.5000</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>611.1945</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr">
         <is>
           <t>งสังคม  611,194.5 ล้านบาท</t>
@@ -2252,11 +2040,7 @@
           <t>ร้อยละ/สัดส่วน</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>25.4</t>
-        </is>
-      </c>
+      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
@@ -2286,14 +2070,10 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>960,916.6000</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>960.9166</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr"/>
       <c r="H56" s="2" t="inlineStr">
         <is>
           <t>960,916.6 ล้านบาท (16.1%</t>
@@ -2320,11 +2100,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>407,165.1</t>
-        </is>
-      </c>
+      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
     </row>
@@ -2348,11 +2124,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>10.7</t>
-        </is>
-      </c>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -2376,11 +2148,7 @@
           <t>ร้อยละ/สัดส่วน</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>9.2</t>
-        </is>
-      </c>
+      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
@@ -2408,11 +2176,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>348,427.4</t>
-        </is>
-      </c>
+      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -2436,11 +2200,7 @@
           <t>ร้อยละ/สัดส่วน</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>17.1</t>
-        </is>
-      </c>
+      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
@@ -2470,14 +2230,10 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>646,468.4000</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>646.4684</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr">
         <is>
           <t>าครัฐช  646,468.4 ล้านบาท  (17.1%)</t>
@@ -2504,11 +2260,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>230,941</t>
-        </is>
-      </c>
+      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
@@ -2536,11 +2288,7 @@
           <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>7.48</t>
-        </is>
-      </c>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
@@ -2568,11 +2316,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>210,000</t>
-        </is>
-      </c>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
@@ -2600,11 +2344,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>34,334</t>
-        </is>
-      </c>
+      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
@@ -2632,11 +2372,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>10,000</t>
-        </is>
-      </c>
+      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
@@ -2664,11 +2400,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>192,870</t>
-        </is>
-      </c>
+      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
@@ -2696,11 +2428,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>35,800</t>
-        </is>
-      </c>
+      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
@@ -2728,11 +2456,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>1,478</t>
-        </is>
-      </c>
+      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
@@ -2760,11 +2484,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>8,617</t>
-        </is>
-      </c>
+      <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
@@ -2792,11 +2512,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>1,293</t>
-        </is>
-      </c>
+      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
@@ -2824,11 +2540,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>48,000</t>
-        </is>
-      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
@@ -2856,11 +2568,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>750,000</t>
-        </is>
-      </c>
+      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
@@ -2888,11 +2596,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>60,500</t>
-        </is>
-      </c>
+      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
@@ -2920,11 +2624,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>81,046</t>
-        </is>
-      </c>
+      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
@@ -2952,11 +2652,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>52,349</t>
-        </is>
-      </c>
+      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
@@ -2984,11 +2680,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>47,600</t>
-        </is>
-      </c>
+      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
@@ -3016,11 +2708,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>233,500</t>
-        </is>
-      </c>
+      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
@@ -3048,11 +2736,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>72,970</t>
-        </is>
-      </c>
+      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
@@ -3080,11 +2764,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>51,123</t>
-        </is>
-      </c>
+      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
@@ -3112,11 +2792,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>14,000</t>
-        </is>
-      </c>
+      <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
@@ -3144,11 +2820,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>30,000</t>
-        </is>
-      </c>
+      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
@@ -3176,11 +2848,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>26,000</t>
-        </is>
-      </c>
+      <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
@@ -3208,11 +2876,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>5,168</t>
-        </is>
-      </c>
+      <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
@@ -3240,11 +2904,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>7,256</t>
-        </is>
-      </c>
+      <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
@@ -3272,11 +2932,7 @@
           <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>1.08</t>
-        </is>
-      </c>
+      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
@@ -3304,11 +2960,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>4,800</t>
-        </is>
-      </c>
+      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
@@ -3336,11 +2988,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>1,400</t>
-        </is>
-      </c>
+      <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
@@ -3368,11 +3016,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>10,200</t>
-        </is>
-      </c>
+      <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
@@ -3400,11 +3044,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>125,785</t>
-        </is>
-      </c>
+      <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
@@ -3432,11 +3072,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>156,000</t>
-        </is>
-      </c>
+      <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
@@ -3464,11 +3100,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>16,681</t>
-        </is>
-      </c>
+      <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
@@ -3496,11 +3128,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>30,406</t>
-        </is>
-      </c>
+      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
@@ -3528,11 +3156,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>16,020</t>
-        </is>
-      </c>
+      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
@@ -3560,11 +3184,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>8,000</t>
-        </is>
-      </c>
+      <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
@@ -3592,11 +3212,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>38,833</t>
-        </is>
-      </c>
+      <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
@@ -3624,11 +3240,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>71,480</t>
-        </is>
-      </c>
+      <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
     </row>
@@ -3652,11 +3264,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>250,000</t>
-        </is>
-      </c>
+      <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
@@ -3684,11 +3292,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>17,250</t>
-        </is>
-      </c>
+      <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
@@ -3716,11 +3320,7 @@
           <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>10.20</t>
-        </is>
-      </c>
+      <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
@@ -3748,11 +3348,7 @@
           <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
+      <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
@@ -3780,11 +3376,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>13,540</t>
-        </is>
-      </c>
+      <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
@@ -3812,11 +3404,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>4,880</t>
-        </is>
-      </c>
+      <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
@@ -3844,11 +3432,7 @@
           <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2.53</t>
-        </is>
-      </c>
+      <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
@@ -3876,11 +3460,7 @@
           <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2.47</t>
-        </is>
-      </c>
+      <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
@@ -3908,11 +3488,7 @@
           <t>บาท (ต่อหน่วย)</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>1,000</t>
-        </is>
-      </c>
+      <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
@@ -3940,11 +3516,7 @@
           <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>13.47</t>
-        </is>
-      </c>
+      <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
@@ -3972,11 +3544,7 @@
           <t>บาท (ต่อหน่วย)</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>1,000</t>
-        </is>
-      </c>
+      <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
@@ -4004,11 +3572,7 @@
           <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>10.14</t>
-        </is>
-      </c>
+      <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
@@ -4036,11 +3600,7 @@
           <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>47.17</t>
-        </is>
-      </c>
+      <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
@@ -4068,11 +3628,7 @@
           <t>บาท (ต่อหน่วย)</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>4,175.99</t>
-        </is>
-      </c>
+      <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr">
         <is>
@@ -4100,11 +3656,7 @@
           <t>บาท (ต่อหน่วย)</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>4,669.74</t>
-        </is>
-      </c>
+      <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr">
         <is>
@@ -4132,11 +3684,7 @@
           <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>4.97</t>
-        </is>
-      </c>
+      <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
@@ -4164,11 +3712,7 @@
           <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>65.92</t>
-        </is>
-      </c>
+      <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr">
         <is>
@@ -4196,11 +3740,7 @@
           <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>13.78</t>
-        </is>
-      </c>
+      <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr">
         <is>
@@ -4228,11 +3768,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>148,929</t>
-        </is>
-      </c>
+      <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
@@ -4260,11 +3796,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>9.44</t>
-        </is>
-      </c>
+      <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
         <is>
@@ -4292,11 +3824,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>33,444</t>
-        </is>
-      </c>
+      <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
@@ -4324,11 +3852,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>23,500</t>
-        </is>
-      </c>
+      <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr">
         <is>
@@ -4356,11 +3880,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>240,901</t>
-        </is>
-      </c>
+      <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr">
         <is>
@@ -4388,11 +3908,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>307,160</t>
-        </is>
-      </c>
+      <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr">
         <is>
@@ -4420,11 +3936,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>120,000</t>
-        </is>
-      </c>
+      <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr">
         <is>
@@ -4452,11 +3964,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>77,889</t>
-        </is>
-      </c>
+      <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr">
         <is>
@@ -4484,11 +3992,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>277,698</t>
-        </is>
-      </c>
+      <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr">
         <is>
@@ -4516,11 +4020,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>1,620</t>
-        </is>
-      </c>
+      <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr">
         <is>
@@ -4548,11 +4048,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>110,000</t>
-        </is>
-      </c>
+      <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr">
         <is>
@@ -4580,11 +4076,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>200,000</t>
-        </is>
-      </c>
+      <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
@@ -4612,11 +4104,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
+      <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr">
         <is>
@@ -4644,11 +4132,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
+      <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr">
         <is>
@@ -4676,11 +4160,7 @@
           <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2.32</t>
-        </is>
-      </c>
+      <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
@@ -4708,11 +4188,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>6,592</t>
-        </is>
-      </c>
+      <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr">
         <is>
@@ -4740,11 +4216,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>23,497</t>
-        </is>
-      </c>
+      <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
@@ -4772,11 +4244,7 @@
           <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>13.65</t>
-        </is>
-      </c>
+      <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr">
         <is>
@@ -4804,11 +4272,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>170,000</t>
-        </is>
-      </c>
+      <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr">
         <is>
@@ -4836,11 +4300,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>760,000</t>
-        </is>
-      </c>
+      <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr">
         <is>
@@ -4870,14 +4330,10 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>154,176.8000</t>
-        </is>
-      </c>
-      <c r="G137" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>154.1768</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr"/>
       <c r="H137" s="2" t="inlineStr">
         <is>
           <t>154,176.8 2 | การต่างประเทศ</t>
@@ -4906,14 +4362,10 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>4,604.9000</t>
-        </is>
-      </c>
-      <c r="G138" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>4.6049</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr"/>
       <c r="H138" s="2" t="inlineStr">
         <is>
           <t>4,604.9  ยุทธศาสตร์ด้านกา</t>
@@ -4942,14 +4394,10 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>21,532.6000</t>
-        </is>
-      </c>
-      <c r="G139" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>21.5326</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr"/>
       <c r="H139" s="2" t="inlineStr">
         <is>
           <t>21,532.6 4 | อุตสาหกรรมและ</t>
@@ -4978,14 +4426,10 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>4,605.0000</t>
-        </is>
-      </c>
-      <c r="G140" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>4.6050</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr"/>
       <c r="H140" s="2" t="inlineStr">
         <is>
           <t>4,605.0 5 | คารท่องเที่ยว</t>
@@ -5014,14 +4458,10 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>7,864.3000</t>
-        </is>
-      </c>
-      <c r="G141" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>7.8643</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr"/>
       <c r="H141" s="2" t="inlineStr">
         <is>
           <t>7,864.3 6 | พื้นที่และเมื</t>
@@ -5050,14 +4490,10 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>10,836.6000</t>
-        </is>
-      </c>
-      <c r="G142" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>10.8366</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr"/>
       <c r="H142" s="2" t="inlineStr">
         <is>
           <t>10,836.6 7 | โครงสร้างพื้น</t>
@@ -5086,14 +4522,10 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>204,319.4000</t>
-        </is>
-      </c>
-      <c r="G143" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>204.3194</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr"/>
       <c r="H143" s="2" t="inlineStr">
         <is>
           <t>204,319.4 8 | ผู้ประกอบการแ</t>
@@ -5122,14 +4554,10 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>3,537.3000</t>
-        </is>
-      </c>
-      <c r="G144" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>3.5373</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr"/>
       <c r="H144" s="2" t="inlineStr">
         <is>
           <t>3,537.3 9 | เขตเศรษฐกิจพิ</t>
@@ -5158,14 +4586,10 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>2,036.2000</t>
-        </is>
-      </c>
-      <c r="G145" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>2.0362</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr"/>
       <c r="H145" s="2" t="inlineStr">
         <is>
           <t>2,036.2 10 | การวิจัยและพ</t>
@@ -5194,14 +4618,10 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>13,513.0000</t>
-        </is>
-      </c>
-      <c r="G146" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>13.5130</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr"/>
       <c r="H146" s="2" t="inlineStr">
         <is>
           <t>13,513.0  ยุทธศาสตร์ด้านกา</t>
@@ -5230,14 +4650,10 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>3,499.9000</t>
-        </is>
-      </c>
-      <c r="G147" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>3.4999</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr"/>
       <c r="H147" s="2" t="inlineStr">
         <is>
           <t>3,499.9 12 | การพัฒนาศักย</t>
@@ -5266,14 +4682,10 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>34,540.7000</t>
-        </is>
-      </c>
-      <c r="G148" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>34.5407</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr"/>
       <c r="H148" s="2" t="inlineStr">
         <is>
           <t>34,540.7 13 | การพัฒนาการเ</t>
@@ -5302,14 +4714,10 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>30,262.3000</t>
-        </is>
-      </c>
-      <c r="G149" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>30.2623</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr"/>
       <c r="H149" s="2" t="inlineStr">
         <is>
           <t>30,262.3 14 | การเสริมสร้า</t>
@@ -5338,14 +4746,10 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>68,556.7000</t>
-        </is>
-      </c>
-      <c r="G150" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>68.5567</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr"/>
       <c r="H150" s="2" t="inlineStr">
         <is>
           <t>68,556.7 15 | ศักยภาพการกี</t>
@@ -5374,14 +4778,10 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>3,413.7000</t>
-        </is>
-      </c>
-      <c r="G151" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>3.4137</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr"/>
       <c r="H151" s="2" t="inlineStr">
         <is>
           <t>3,413.7  BUDGET BUREAU</t>
@@ -5410,14 +4810,10 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>1,681,011.7000</t>
-        </is>
-      </c>
-      <c r="G152" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>1,681.0117</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr"/>
       <c r="H152" s="2" t="inlineStr">
         <is>
           <t>ร์ชาติ  1,681,011.7 ล้านบาท  แผนแม่บท</t>
@@ -5446,14 +4842,10 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>403,463.9000</t>
-        </is>
-      </c>
-      <c r="G153" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>403.4639</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr"/>
       <c r="H153" s="2" t="inlineStr">
         <is>
           <t>403,463.9 17 | เศรษฐกิจชานร</t>
@@ -5482,14 +4874,10 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>3,522.1000</t>
-        </is>
-      </c>
-      <c r="G154" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>3.5221</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr"/>
       <c r="H154" s="2" t="inlineStr">
         <is>
           <t>3,522.1 18 | ความเสมอภาคแ</t>
@@ -5518,14 +4906,10 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>543,087.4000</t>
-        </is>
-      </c>
-      <c r="G155" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>543.0874</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr"/>
       <c r="H155" s="2" t="inlineStr">
         <is>
           <t>543,087.4  ยุทธศาสตร์ด้านกา</t>
@@ -5554,14 +4938,10 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>12,260.4000</t>
-        </is>
-      </c>
-      <c r="G156" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>12.2604</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr"/>
       <c r="H156" s="2" t="inlineStr">
         <is>
           <t>12,260.4  20 | การบริหารจั</t>
@@ -5590,14 +4970,10 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>96,486.3000</t>
-        </is>
-      </c>
-      <c r="G157" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>96.4863</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr"/>
       <c r="H157" s="2" t="inlineStr">
         <is>
           <t>96,486.3  ยุทธศาสตร์ด้านกา</t>
@@ -5626,14 +5002,10 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>761.7000</t>
-        </is>
-      </c>
-      <c r="G158" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>0.7617</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr"/>
       <c r="H158" s="2" t="inlineStr">
         <is>
           <t>761.7 23 | กฎหมายและคระ</t>
@@ -5662,14 +5034,10 @@
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>15,756.6000</t>
-        </is>
-      </c>
-      <c r="G159" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>15.7566</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr"/>
       <c r="H159" s="2" t="inlineStr">
         <is>
           <t>15,756.6  BUDGET BUREAU</t>
@@ -5698,14 +5066,10 @@
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>38,373.9000</t>
-        </is>
-      </c>
-      <c r="G160" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>38.3739</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr"/>
       <c r="H160" s="2" t="inlineStr">
         <is>
           <t>38,373.9 22 | การต่อต้านกา</t>
@@ -5734,14 +5098,10 @@
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>1,595,714.7000</t>
-        </is>
-      </c>
-      <c r="G161" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>1,595.7147</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr"/>
       <c r="H161" s="2" t="inlineStr">
         <is>
           <t>บที 13  1,595,714.7 ล้านบาท  หมุดหมาย</t>
@@ -5770,14 +5130,10 @@
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>203,409.6000</t>
-        </is>
-      </c>
-      <c r="G162" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>203.4096</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr"/>
       <c r="H162" s="2" t="inlineStr">
         <is>
           <t>2,346.7 203,409.6 1,830.2 4,213.8 1</t>
@@ -5806,14 +5162,10 @@
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>69,078.7000</t>
-        </is>
-      </c>
-      <c r="G163" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>69.0787</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr"/>
       <c r="H163" s="2" t="inlineStr">
         <is>
           <t>านบาท)  69,078.7 11,595.8  4,061.3</t>
@@ -5842,14 +5194,10 @@
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>11,595.8000</t>
-        </is>
-      </c>
-      <c r="G164" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>11.5958</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr"/>
       <c r="H164" s="2" t="inlineStr">
         <is>
           <t>9,078.7 11,595.8  4,061.3 182,346.</t>
@@ -5878,14 +5226,10 @@
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>4,061.3000</t>
-        </is>
-      </c>
-      <c r="G165" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>4.0613</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr"/>
       <c r="H165" s="2" t="inlineStr">
         <is>
           <t>,595.8  4,061.3 182,346.7 203,409</t>
@@ -5914,14 +5258,10 @@
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>182,346.7000</t>
-        </is>
-      </c>
-      <c r="G166" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>182.3467</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr"/>
       <c r="H166" s="2" t="inlineStr">
         <is>
           <t>4,061.3 182,346.7 203,409.6 1,830.2</t>
@@ -5950,14 +5290,10 @@
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>1,830.2000</t>
-        </is>
-      </c>
-      <c r="G167" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>1.8302</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr"/>
       <c r="H167" s="2" t="inlineStr">
         <is>
           <t>3,409.6 1,830.2 4,213.8 107,918.7</t>
@@ -5986,14 +5322,10 @@
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>4,213.8000</t>
-        </is>
-      </c>
-      <c r="G168" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>4.2138</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr"/>
       <c r="H168" s="2" t="inlineStr">
         <is>
           <t>1,830.2 4,213.8 107,918.7  944,14</t>
@@ -6022,14 +5354,10 @@
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>107,918.7000</t>
-        </is>
-      </c>
-      <c r="G169" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>107.9187</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr"/>
       <c r="H169" s="2" t="inlineStr">
         <is>
           <t>4,213.8 107,918.7  944,145.1  15,82</t>
@@ -6058,14 +5386,10 @@
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>544,145.1000</t>
-        </is>
-      </c>
-      <c r="G170" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>544.1451</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr"/>
       <c r="H170" s="2" t="inlineStr"/>
     </row>
     <row r="171">
@@ -6090,14 +5414,10 @@
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>15,828.9000</t>
-        </is>
-      </c>
-      <c r="G171" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>15.8289</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr"/>
       <c r="H171" s="2" t="inlineStr">
         <is>
           <t>,145.1  15,828.9  29,724.1  307,47</t>
@@ -6126,14 +5446,10 @@
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>29,724.1000</t>
-        </is>
-      </c>
-      <c r="G172" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>29.7241</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr"/>
       <c r="H172" s="2" t="inlineStr">
         <is>
           <t>,828.9  29,724.1  307,475.3  114,0</t>
@@ -6162,14 +5478,10 @@
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>307,475.3000</t>
-        </is>
-      </c>
-      <c r="G173" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>307.4753</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr"/>
       <c r="H173" s="2" t="inlineStr">
         <is>
           <t>,724.1  307,475.3  114,086.5  BUDGE</t>
@@ -6198,14 +5510,10 @@
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>114,086.5000</t>
-        </is>
-      </c>
-      <c r="G174" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>114.0865</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr"/>
       <c r="H174" s="2" t="inlineStr">
         <is>
           <t>,475.3  114,086.5  BUDGET BUREAU</t>
@@ -6234,14 +5542,10 @@
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>1,503,088.8000</t>
-        </is>
-      </c>
-      <c r="G175" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>1,503.0888</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr"/>
       <c r="H175" s="2" t="inlineStr">
         <is>
           <t>ล       1,503,088.8 aun  ด้านเศรษฐกิจ</t>
@@ -6270,14 +5574,10 @@
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>436,287.9000</t>
-        </is>
-      </c>
-      <c r="G176" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>436.2879</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr"/>
       <c r="H176" s="2" t="inlineStr">
         <is>
           <t>436,287.9 ล้านบาท  ด้านการต</t>
@@ -6306,14 +5606,10 @@
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>162,951.5000</t>
-        </is>
-      </c>
-      <c r="G177" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>162.9515</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr"/>
       <c r="H177" s="2" t="inlineStr">
         <is>
           <t>162,951.5 ล้านบาท  ด้านสังค</t>
@@ -6342,14 +5638,10 @@
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>698,046.9000</t>
-        </is>
-      </c>
-      <c r="G178" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>698.0469</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr"/>
       <c r="H178" s="2" t="inlineStr">
         <is>
           <t>านสังคม 698,046.9 ล้านบาท  ด้านภัยพ</t>
@@ -6378,14 +5670,10 @@
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>170,390.6000</t>
-        </is>
-      </c>
-      <c r="G179" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>170.3906</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr"/>
       <c r="H179" s="2" t="inlineStr">
         <is>
           <t>แวดล้อม 170,390.6 ล้านบาท  4  ด้านก</t>
@@ -6414,14 +5702,10 @@
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>35,411.9000</t>
-        </is>
-      </c>
-      <c r="G180" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>35.4119</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr"/>
       <c r="H180" s="2" t="inlineStr">
         <is>
           <t>าย  Sia 35,411.9 ล้านบาท  หมายเหตุ</t>
@@ -6448,11 +5732,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>4,825.3</t>
-        </is>
-      </c>
+      <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr"/>
     </row>
@@ -6478,14 +5758,10 @@
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>219,902.2000</t>
-        </is>
-      </c>
-      <c r="G182" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>219.9022</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr"/>
       <c r="H182" s="2" t="inlineStr">
         <is>
           <t>219,902.2 ลบ. ปรับโครงสร้าง</t>
@@ -6514,14 +5790,10 @@
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>185,939.3000</t>
-        </is>
-      </c>
-      <c r="G183" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>185.9393</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr"/>
       <c r="H183" s="2" t="inlineStr">
         <is>
           <t>185,939.3 au. ด้านการค้า “เ</t>
@@ -6550,14 +5822,10 @@
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>11,264.1000</t>
-        </is>
-      </c>
-      <c r="G184" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>11.2641</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr"/>
       <c r="H184" s="2" t="inlineStr">
         <is>
           <t>11,264.1 au.  ค้านการต่างป</t>
@@ -6586,14 +5854,10 @@
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>14,357.0000</t>
-        </is>
-      </c>
-      <c r="G185" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>14.3570</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr"/>
       <c r="H185" s="2" t="inlineStr">
         <is>
           <t>14,357.0 ลบ.  ด้านการท่องเ</t>
@@ -6622,14 +5886,10 @@
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>436,287.9000</t>
-        </is>
-      </c>
-      <c r="G186" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>436.2879</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr"/>
       <c r="H186" s="2" t="inlineStr">
         <is>
           <t>436,287.9 au.  สร้างโอกาสกา</t>
@@ -6658,14 +5918,10 @@
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t>121,123.8000</t>
-        </is>
-      </c>
-      <c r="G187" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>121.1238</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr"/>
       <c r="H187" s="2" t="inlineStr">
         <is>
           <t>121,123.8 ลบ.  พัฒนาระบบการ</t>
@@ -6694,14 +5950,10 @@
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>1,117.6000</t>
-        </is>
-      </c>
-      <c r="G188" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>1.1176</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr"/>
       <c r="H188" s="2" t="inlineStr">
         <is>
           <t>1,117.6 au.  เสริมสร้างเส</t>
@@ -6730,14 +5982,10 @@
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>745.0000</t>
-        </is>
-      </c>
-      <c r="G189" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>0.7450</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr"/>
       <c r="H189" s="2" t="inlineStr">
         <is>
           <t>745.0 ลบ.  ส่งเสริมความ</t>
@@ -6766,14 +6014,10 @@
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>19,845.2000</t>
-        </is>
-      </c>
-      <c r="G190" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>19.8452</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr"/>
       <c r="H190" s="2" t="inlineStr">
         <is>
           <t>19,845.2 ลบ.  สร้างความมั่</t>
@@ -6802,14 +6046,10 @@
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>694.5000</t>
-        </is>
-      </c>
-      <c r="G191" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>0.6945</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr"/>
       <c r="H191" s="2" t="inlineStr">
         <is>
           <t>694.5 ลบ.  ขับเคลือนการ</t>
@@ -6838,14 +6078,10 @@
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>2,114.5000</t>
-        </is>
-      </c>
-      <c r="G192" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>2.1145</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr"/>
       <c r="H192" s="2" t="inlineStr">
         <is>
           <t>2,114.5 au.  BUDGET BUREA</t>
@@ -6874,14 +6110,10 @@
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t>162,951.5000</t>
-        </is>
-      </c>
-      <c r="G193" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>162.9515</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr"/>
       <c r="H193" s="2" t="inlineStr">
         <is>
           <t>มมั่นคง 162,951.5 ลบ.  เร่งเสริมสร้</t>
@@ -6910,14 +6142,10 @@
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>17,310.9000</t>
-        </is>
-      </c>
-      <c r="G194" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>17.3109</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr"/>
       <c r="H194" s="2" t="inlineStr">
         <is>
           <t>17,310.9 ลบ.  พัฒนาระบบทหา</t>
@@ -6946,14 +6174,10 @@
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
-          <t>698,046.9000</t>
-        </is>
-      </c>
-      <c r="G195" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>698.0469</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr"/>
       <c r="H195" s="2" t="inlineStr">
         <is>
           <t>698,046.9 ลบ.  เรียนฟรีมีจร</t>
@@ -6982,14 +6206,10 @@
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>214,931.7000</t>
-        </is>
-      </c>
-      <c r="G196" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>214.9317</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr"/>
       <c r="H196" s="2" t="inlineStr">
         <is>
           <t>214,931.7 ลบ. พัฒนาระบบประก</t>
@@ -7018,14 +6238,10 @@
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t>478,174.8000</t>
-        </is>
-      </c>
-      <c r="G197" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>478.1748</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr"/>
       <c r="H197" s="2" t="inlineStr">
         <is>
           <t>478,174.8 ลบ.  สร้างเสริมสถ</t>
@@ -7054,14 +6270,10 @@
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>4,940.4000</t>
-        </is>
-      </c>
-      <c r="G198" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>4.9404</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr"/>
       <c r="H198" s="2" t="inlineStr">
         <is>
           <t>4,940.4 au.  ด้านภัยพิบัต</t>
@@ -7090,14 +6302,10 @@
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t>170,390.6000</t>
-        </is>
-      </c>
-      <c r="G199" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>170.3906</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr"/>
       <c r="H199" s="2" t="inlineStr">
         <is>
           <t>170,390.6 ลบ. บริหารจัดการน</t>
@@ -7126,14 +6334,10 @@
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t>35,411.9000</t>
-        </is>
-      </c>
-      <c r="G200" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>35.4119</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr"/>
       <c r="H200" s="2" t="inlineStr">
         <is>
           <t>35,411.9 ลบ.  ราชการทันใจ</t>
@@ -7162,14 +6366,10 @@
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
-          <t>115,694.0000</t>
-        </is>
-      </c>
-      <c r="G201" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>115.6940</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr"/>
       <c r="H201" s="2" t="inlineStr">
         <is>
           <t>115,694.0 au. พัฒนาระบบประก</t>
@@ -7198,14 +6398,10 @@
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
-          <t>4,800.0000</t>
-        </is>
-      </c>
-      <c r="G202" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>4.8000</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr"/>
       <c r="H202" s="2" t="inlineStr">
         <is>
           <t>4,800.0 au. ผลักด้นให้ประ</t>
@@ -7234,14 +6430,10 @@
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t>44,492.1000</t>
-        </is>
-      </c>
-      <c r="G203" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>44.4921</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr"/>
       <c r="H203" s="2" t="inlineStr">
         <is>
           <t>44,492.1 au. การอนุรักษ์แล</t>
@@ -7270,14 +6462,10 @@
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>5,404.5000</t>
-        </is>
-      </c>
-      <c r="G204" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>5.4045</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr"/>
       <c r="H204" s="2" t="inlineStr">
         <is>
           <t>5,404.5 ลบ.  ด้านการบริหา</t>
@@ -7306,14 +6494,10 @@
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t>25,537.2000</t>
-        </is>
-      </c>
-      <c r="G205" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>25.5372</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr"/>
       <c r="H205" s="2" t="inlineStr">
         <is>
           <t>25,537.2 au.  การปฏิรูประบ</t>
@@ -7342,14 +6526,10 @@
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
-          <t>7,732.0000</t>
-        </is>
-      </c>
-      <c r="G206" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>7.7320</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr"/>
       <c r="H206" s="2" t="inlineStr">
         <is>
           <t>7,732.0 au.  การพัฒนากฎหม</t>
@@ -7378,14 +6558,10 @@
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
-          <t>1,247.0000</t>
-        </is>
-      </c>
-      <c r="G207" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>1.2470</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr"/>
       <c r="H207" s="2" t="inlineStr">
         <is>
           <t>1,247.0 ลบ. 895.7 ลบ.  แก</t>
@@ -7414,14 +6590,10 @@
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
-          <t>895.7000</t>
-        </is>
-      </c>
-      <c r="G208" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>0.8957</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr"/>
       <c r="H208" s="2" t="inlineStr">
         <is>
           <t>7.0 ลบ. 895.7 ลบ.  แก้ปัญหาคอร์</t>
@@ -7448,11 +6620,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>5,500</t>
-        </is>
-      </c>
+      <c r="F209" t="inlineStr"/>
       <c r="G209" t="inlineStr"/>
       <c r="H209" t="inlineStr">
         <is>
@@ -7480,11 +6648,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>2,096</t>
-        </is>
-      </c>
+      <c r="F210" t="inlineStr"/>
       <c r="G210" t="inlineStr"/>
       <c r="H210" t="inlineStr">
         <is>
@@ -7514,14 +6678,10 @@
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
-          <t>28.6000</t>
-        </is>
-      </c>
-      <c r="G211" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>0.0286</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr"/>
       <c r="H211" s="2" t="inlineStr">
         <is>
           <t>บประมาณ 28.6 ล้านบาท</t>
@@ -7548,11 +6708,7 @@
           <t>บาท (ต่อหน่วย)</t>
         </is>
       </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
-      </c>
+      <c r="F212" t="inlineStr"/>
       <c r="G212" t="inlineStr"/>
       <c r="H212" t="inlineStr">
         <is>
@@ -7580,11 +6736,7 @@
           <t>บาท (ต่อหน่วย)</t>
         </is>
       </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>1,000</t>
-        </is>
-      </c>
+      <c r="F213" t="inlineStr"/>
       <c r="G213" t="inlineStr"/>
       <c r="H213" t="inlineStr">
         <is>
@@ -7612,11 +6764,7 @@
           <t>บาท (ต่อหน่วย)</t>
         </is>
       </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>1,000</t>
-        </is>
-      </c>
+      <c r="F214" t="inlineStr"/>
       <c r="G214" t="inlineStr"/>
       <c r="H214" t="inlineStr">
         <is>
@@ -7644,11 +6792,7 @@
           <t>บาท (ต่อหน่วย)</t>
         </is>
       </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
-      </c>
+      <c r="F215" t="inlineStr"/>
       <c r="G215" t="inlineStr"/>
       <c r="H215" t="inlineStr">
         <is>
@@ -7676,11 +6820,7 @@
           <t>บาท (ต่อหน่วย)</t>
         </is>
       </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
+      <c r="F216" t="inlineStr"/>
       <c r="G216" t="inlineStr"/>
       <c r="H216" t="inlineStr">
         <is>
@@ -7708,11 +6848,7 @@
           <t>บาท (ต่อหน่วย)</t>
         </is>
       </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>100,000</t>
-        </is>
-      </c>
+      <c r="F217" t="inlineStr"/>
       <c r="G217" t="inlineStr"/>
       <c r="H217" t="inlineStr">
         <is>
@@ -7740,11 +6876,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>2.53</t>
-        </is>
-      </c>
+      <c r="F218" t="inlineStr"/>
       <c r="G218" t="inlineStr"/>
       <c r="H218" t="inlineStr"/>
     </row>
@@ -7770,14 +6902,10 @@
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
-          <t>15,810.1000</t>
-        </is>
-      </c>
-      <c r="G219" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>15.8101</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="inlineStr"/>
       <c r="H219" s="2" t="inlineStr">
         <is>
           <t>บประมาณ 15,810.1 ล้านบาท  เด็กขาดแ</t>
@@ -7804,11 +6932,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>172,625</t>
-        </is>
-      </c>
+      <c r="F220" t="inlineStr"/>
       <c r="G220" t="inlineStr"/>
       <c r="H220" t="inlineStr">
         <is>
@@ -7838,14 +6962,10 @@
       </c>
       <c r="F221" s="2" t="inlineStr">
         <is>
-          <t>172.6000</t>
-        </is>
-      </c>
-      <c r="G221" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>0.1726</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="inlineStr"/>
       <c r="H221" s="2" t="inlineStr">
         <is>
           <t>บประมาณ 172.6 ล้านบาท  =  -  เง</t>
@@ -7872,11 +6992,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>16,681</t>
-        </is>
-      </c>
+      <c r="F222" t="inlineStr"/>
       <c r="G222" t="inlineStr"/>
       <c r="H222" t="inlineStr">
         <is>
@@ -7906,14 +7022,10 @@
       </c>
       <c r="F223" s="2" t="inlineStr">
         <is>
-          <t>5,325.8000</t>
-        </is>
-      </c>
-      <c r="G223" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>5.3258</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="inlineStr"/>
       <c r="H223" s="2" t="inlineStr">
         <is>
           <t>บประมาณ 5,325.8 ล้านบาท เริดสก“ “</t>
@@ -7940,11 +7052,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>30,406</t>
-        </is>
-      </c>
+      <c r="F224" t="inlineStr"/>
       <c r="G224" t="inlineStr"/>
       <c r="H224" t="inlineStr">
         <is>
@@ -7974,14 +7082,10 @@
       </c>
       <c r="F225" s="2" t="inlineStr">
         <is>
-          <t>1,409.3000</t>
-        </is>
-      </c>
-      <c r="G225" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>1.4093</t>
+        </is>
+      </c>
+      <c r="G225" s="2" t="inlineStr"/>
       <c r="H225" s="2" t="inlineStr">
         <is>
           <t>บประมาณ 1,409.3 ล้านบาท ‘</t>
@@ -8008,11 +7112,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>16,020</t>
-        </is>
-      </c>
+      <c r="F226" t="inlineStr"/>
       <c r="G226" t="inlineStr"/>
       <c r="H226" t="inlineStr"/>
     </row>
@@ -8038,14 +7138,10 @@
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
-          <t>709.5000</t>
-        </is>
-      </c>
-      <c r="G227" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>0.7095</t>
+        </is>
+      </c>
+      <c r="G227" s="2" t="inlineStr"/>
       <c r="H227" s="2" t="inlineStr">
         <is>
           <t>s:ui1du 709.5 auuain  BUDGET BU</t>
@@ -8072,11 +7168,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>61,174</t>
-        </is>
-      </c>
+      <c r="F228" t="inlineStr"/>
       <c r="G228" t="inlineStr"/>
       <c r="H228" t="inlineStr">
         <is>
@@ -8106,14 +7198,10 @@
       </c>
       <c r="F229" s="2" t="inlineStr">
         <is>
-          <t>7,360.2000</t>
-        </is>
-      </c>
-      <c r="G229" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>7.3602</t>
+        </is>
+      </c>
+      <c r="G229" s="2" t="inlineStr"/>
       <c r="H229" s="2" t="inlineStr">
         <is>
           <t>บประมาณ 7,360.2 ล้านบาท  —  ๒2 4</t>
@@ -8140,11 +7228,7 @@
           <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
+      <c r="F230" t="inlineStr"/>
       <c r="G230" t="inlineStr"/>
       <c r="H230" t="inlineStr">
         <is>
@@ -8174,14 +7258,10 @@
       </c>
       <c r="F231" s="2" t="inlineStr">
         <is>
-          <t>7,121.9000</t>
-        </is>
-      </c>
-      <c r="G231" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>7.1219</t>
+        </is>
+      </c>
+      <c r="G231" s="2" t="inlineStr"/>
       <c r="H231" s="2" t="inlineStr">
         <is>
           <t>บประมาณ 7,121.9 ล้านบาท  สนับสนุน</t>
@@ -8208,11 +7288,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F232" t="inlineStr">
-        <is>
-          <t>5.87</t>
-        </is>
-      </c>
+      <c r="F232" t="inlineStr"/>
       <c r="G232" t="inlineStr"/>
       <c r="H232" t="inlineStr"/>
     </row>
@@ -8238,14 +7314,10 @@
       </c>
       <c r="F233" s="2" t="inlineStr">
         <is>
-          <t>29,128.2600</t>
-        </is>
-      </c>
-      <c r="G233" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>291.2826</t>
+        </is>
+      </c>
+      <c r="G233" s="2" t="inlineStr"/>
       <c r="H233" s="2" t="inlineStr">
         <is>
           <t>บประมาณ 29,128.26 ล้านบาท จงบประมาณ</t>
@@ -8272,11 +7344,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>6.08</t>
-        </is>
-      </c>
+      <c r="F234" t="inlineStr"/>
       <c r="G234" t="inlineStr"/>
       <c r="H234" t="inlineStr"/>
     </row>
@@ -8302,14 +7370,10 @@
       </c>
       <c r="F235" s="2" t="inlineStr">
         <is>
-          <t>12,408.0000</t>
-        </is>
-      </c>
-      <c r="G235" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>12.4080</t>
+        </is>
+      </c>
+      <c r="G235" s="2" t="inlineStr"/>
       <c r="H235" s="2" t="inlineStr">
         <is>
           <t>บประมาณ 12,408.0 ล้านบาท  ผู้ขาดแค</t>
@@ -8336,11 +7400,7 @@
           <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>10.20</t>
-        </is>
-      </c>
+      <c r="F236" t="inlineStr"/>
       <c r="G236" t="inlineStr"/>
       <c r="H236" t="inlineStr">
         <is>
@@ -8370,14 +7430,10 @@
       </c>
       <c r="F237" s="2" t="inlineStr">
         <is>
-          <t>88,615.0000</t>
-        </is>
-      </c>
-      <c r="G237" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>88.6150</t>
+        </is>
+      </c>
+      <c r="G237" s="2" t="inlineStr"/>
       <c r="H237" s="2" t="inlineStr">
         <is>
           <t>บประมาณ 88,615.0 ล้านบาท  ๒๕ ซีนับ</t>
@@ -8404,11 +7460,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F238" t="inlineStr">
-        <is>
-          <t>13.78</t>
-        </is>
-      </c>
+      <c r="F238" t="inlineStr"/>
       <c r="G238" t="inlineStr"/>
       <c r="H238" t="inlineStr"/>
     </row>
@@ -8434,14 +7486,10 @@
       </c>
       <c r="F239" s="2" t="inlineStr">
         <is>
-          <t>64,987.0000</t>
-        </is>
-      </c>
-      <c r="G239" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>64.9870</t>
+        </is>
+      </c>
+      <c r="G239" s="2" t="inlineStr"/>
       <c r="H239" s="2" t="inlineStr">
         <is>
           <t>บประมาณ 64,987.0 ล้านบาท</t>
@@ -8468,11 +7516,7 @@
           <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
-      <c r="F240" t="inlineStr">
-        <is>
-          <t>3.12</t>
-        </is>
-      </c>
+      <c r="F240" t="inlineStr"/>
       <c r="G240" t="inlineStr"/>
       <c r="H240" t="inlineStr">
         <is>
@@ -8502,14 +7546,10 @@
       </c>
       <c r="F241" s="2" t="inlineStr">
         <is>
-          <t>347.6000</t>
-        </is>
-      </c>
-      <c r="G241" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>0.3476</t>
+        </is>
+      </c>
+      <c r="G241" s="2" t="inlineStr"/>
       <c r="H241" s="2" t="inlineStr">
         <is>
           <t>บประมาณ 347.6 ล้านบาท  ม 2 อ ณะ</t>
@@ -8536,11 +7576,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F242" t="inlineStr">
-        <is>
-          <t>8.8</t>
-        </is>
-      </c>
+      <c r="F242" t="inlineStr"/>
       <c r="G242" t="inlineStr"/>
       <c r="H242" t="inlineStr"/>
     </row>
@@ -8564,11 +7600,7 @@
           <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
-      <c r="F243" t="inlineStr">
-        <is>
-          <t>1.28</t>
-        </is>
-      </c>
+      <c r="F243" t="inlineStr"/>
       <c r="G243" t="inlineStr"/>
       <c r="H243" t="inlineStr">
         <is>
@@ -8596,11 +7628,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F244" t="inlineStr">
-        <is>
-          <t>9.10</t>
-        </is>
-      </c>
+      <c r="F244" t="inlineStr"/>
       <c r="G244" t="inlineStr"/>
       <c r="H244" t="inlineStr"/>
     </row>
@@ -8626,14 +7654,10 @@
       </c>
       <c r="F245" s="2" t="inlineStr">
         <is>
-          <t>917.3000</t>
-        </is>
-      </c>
-      <c r="G245" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>0.9173</t>
+        </is>
+      </c>
+      <c r="G245" s="2" t="inlineStr"/>
       <c r="H245" s="2" t="inlineStr">
         <is>
           <t>บประมาณ 917.3 ล้านบาท  สพ๒9 สมท</t>
@@ -8662,14 +7686,10 @@
       </c>
       <c r="F246" s="2" t="inlineStr">
         <is>
-          <t>71,400.0000</t>
-        </is>
-      </c>
-      <c r="G246" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>7.1400</t>
+        </is>
+      </c>
+      <c r="G246" s="2" t="inlineStr"/>
       <c r="H246" s="2" t="inlineStr">
         <is>
           <t>บประมาณ 71,400 ล้านบาท  กองทุนบํ</t>
@@ -8696,11 +7716,7 @@
           <t>บาท (ต่อหน่วย)</t>
         </is>
       </c>
-      <c r="F247" t="inlineStr">
-        <is>
-          <t>1,800</t>
-        </is>
-      </c>
+      <c r="F247" t="inlineStr"/>
       <c r="G247" t="inlineStr"/>
       <c r="H247" t="inlineStr">
         <is>
@@ -8728,11 +7744,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F248" t="inlineStr">
-        <is>
-          <t>8,000</t>
-        </is>
-      </c>
+      <c r="F248" t="inlineStr"/>
       <c r="G248" t="inlineStr"/>
       <c r="H248" t="inlineStr">
         <is>
@@ -8760,11 +7772,7 @@
           <t>บาท (ต่อหน่วย)</t>
         </is>
       </c>
-      <c r="F249" t="inlineStr">
-        <is>
-          <t>53.6</t>
-        </is>
-      </c>
+      <c r="F249" t="inlineStr"/>
       <c r="G249" t="inlineStr"/>
       <c r="H249" t="inlineStr">
         <is>
@@ -8794,14 +7802,10 @@
       </c>
       <c r="F250" s="2" t="inlineStr">
         <is>
-          <t>5.1000</t>
-        </is>
-      </c>
-      <c r="G250" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>0.0051</t>
+        </is>
+      </c>
+      <c r="G250" s="2" t="inlineStr"/>
       <c r="H250" s="2" t="inlineStr">
         <is>
           <t>บประมาณ 5.1 ล้านบาท  ค่าใช้จ่</t>
@@ -8828,11 +7832,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t>4,000</t>
-        </is>
-      </c>
+      <c r="F251" t="inlineStr"/>
       <c r="G251" t="inlineStr"/>
       <c r="H251" t="inlineStr"/>
     </row>
@@ -8856,11 +7856,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F252" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
+      <c r="F252" t="inlineStr"/>
       <c r="G252" t="inlineStr"/>
       <c r="H252" t="inlineStr"/>
     </row>
@@ -8884,11 +7880,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F253" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
+      <c r="F253" t="inlineStr"/>
       <c r="G253" t="inlineStr"/>
       <c r="H253" t="inlineStr"/>
     </row>
@@ -8912,11 +7904,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F254" t="inlineStr">
-        <is>
-          <t>7.1</t>
-        </is>
-      </c>
+      <c r="F254" t="inlineStr"/>
       <c r="G254" t="inlineStr"/>
       <c r="H254" t="inlineStr"/>
     </row>
@@ -8940,11 +7928,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F255" t="inlineStr">
-        <is>
-          <t>2,500</t>
-        </is>
-      </c>
+      <c r="F255" t="inlineStr"/>
       <c r="G255" t="inlineStr"/>
       <c r="H255" t="inlineStr"/>
     </row>
@@ -8968,11 +7952,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F256" t="inlineStr">
-        <is>
-          <t>9.2</t>
-        </is>
-      </c>
+      <c r="F256" t="inlineStr"/>
       <c r="G256" t="inlineStr"/>
       <c r="H256" t="inlineStr"/>
     </row>
@@ -8996,11 +7976,7 @@
           <t>บาท (ต่อหน่วย)</t>
         </is>
       </c>
-      <c r="F257" t="inlineStr">
-        <is>
-          <t>462.5</t>
-        </is>
-      </c>
+      <c r="F257" t="inlineStr"/>
       <c r="G257" t="inlineStr"/>
       <c r="H257" t="inlineStr">
         <is>
@@ -9028,11 +8004,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F258" t="inlineStr">
-        <is>
-          <t>154,182</t>
-        </is>
-      </c>
+      <c r="F258" t="inlineStr"/>
       <c r="G258" t="inlineStr"/>
       <c r="H258" t="inlineStr">
         <is>
@@ -9060,11 +8032,7 @@
           <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
-      <c r="F259" t="inlineStr">
-        <is>
-          <t>13.47</t>
-        </is>
-      </c>
+      <c r="F259" t="inlineStr"/>
       <c r="G259" t="inlineStr"/>
       <c r="H259" t="inlineStr">
         <is>
@@ -9094,14 +8062,10 @@
       </c>
       <c r="F260" s="2" t="inlineStr">
         <is>
-          <t>107,365.5900</t>
-        </is>
-      </c>
-      <c r="G260" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>1,073.6559</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr"/>
       <c r="H260" s="2" t="inlineStr">
         <is>
           <t>บประมาณ 107,365.59 ล้านบาท  ได้รับเง</t>
@@ -9128,11 +8092,7 @@
           <t>บาท (ต่อหน่วย)</t>
         </is>
       </c>
-      <c r="F261" t="inlineStr">
-        <is>
-          <t>1,000</t>
-        </is>
-      </c>
+      <c r="F261" t="inlineStr"/>
       <c r="G261" t="inlineStr"/>
       <c r="H261" t="inlineStr">
         <is>
@@ -9160,11 +8120,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F262" t="inlineStr">
-        <is>
-          <t>12,500</t>
-        </is>
-      </c>
+      <c r="F262" t="inlineStr"/>
       <c r="G262" t="inlineStr"/>
       <c r="H262" t="inlineStr">
         <is>
@@ -9192,11 +8148,7 @@
           <t>บาท (ต่อหน่วย)</t>
         </is>
       </c>
-      <c r="F263" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
+      <c r="F263" t="inlineStr"/>
       <c r="G263" t="inlineStr"/>
       <c r="H263" t="inlineStr">
         <is>
@@ -9226,14 +8178,10 @@
       </c>
       <c r="F264" s="2" t="inlineStr">
         <is>
-          <t>37.5000</t>
-        </is>
-      </c>
-      <c r="G264" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>0.0375</t>
+        </is>
+      </c>
+      <c r="G264" s="2" t="inlineStr"/>
       <c r="H264" s="2" t="inlineStr">
         <is>
           <t>บประมาณ 37.5 ล้านบาท  เงินอุดห</t>
@@ -9260,11 +8208,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F265" t="inlineStr">
-        <is>
-          <t>9,000</t>
-        </is>
-      </c>
+      <c r="F265" t="inlineStr"/>
       <c r="G265" t="inlineStr"/>
       <c r="H265" t="inlineStr">
         <is>
@@ -9294,14 +8238,10 @@
       </c>
       <c r="F266" s="2" t="inlineStr">
         <is>
-          <t>540.0000</t>
-        </is>
-      </c>
-      <c r="G266" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>0.5400</t>
+        </is>
+      </c>
+      <c r="G266" s="2" t="inlineStr"/>
       <c r="H266" s="2" t="inlineStr">
         <is>
           <t>บประมาณ 540.0 ล้านบาท  สนับสนุน</t>
@@ -9328,11 +8268,7 @@
           <t>บาท (ต่อหน่วย)</t>
         </is>
       </c>
-      <c r="F267" t="inlineStr">
-        <is>
-          <t>60,000</t>
-        </is>
-      </c>
+      <c r="F267" t="inlineStr"/>
       <c r="G267" t="inlineStr"/>
       <c r="H267" t="inlineStr">
         <is>
@@ -9360,11 +8296,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F268" t="inlineStr">
-        <is>
-          <t>2,100</t>
-        </is>
-      </c>
+      <c r="F268" t="inlineStr"/>
       <c r="G268" t="inlineStr"/>
       <c r="H268" t="inlineStr">
         <is>
@@ -9394,14 +8326,10 @@
       </c>
       <c r="F269" s="2" t="inlineStr">
         <is>
-          <t>63.0000</t>
-        </is>
-      </c>
-      <c r="G269" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>0.0630</t>
+        </is>
+      </c>
+      <c r="G269" s="2" t="inlineStr"/>
       <c r="H269" s="2" t="inlineStr">
         <is>
           <t>บประมาณ 63.0 ล้านบาท  สนับสนุน</t>
@@ -9428,11 +8356,7 @@
           <t>บาท (ต่อหน่วย)</t>
         </is>
       </c>
-      <c r="F270" t="inlineStr">
-        <is>
-          <t>30,000</t>
-        </is>
-      </c>
+      <c r="F270" t="inlineStr"/>
       <c r="G270" t="inlineStr"/>
       <c r="H270" t="inlineStr">
         <is>
@@ -9460,11 +8384,7 @@
           <t>บาท (ต่อหน่วย)</t>
         </is>
       </c>
-      <c r="F271" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
+      <c r="F271" t="inlineStr"/>
       <c r="G271" t="inlineStr"/>
       <c r="H271" t="inlineStr">
         <is>
@@ -9494,14 +8414,10 @@
       </c>
       <c r="F272" s="2" t="inlineStr">
         <is>
-          <t>436,287.9000</t>
-        </is>
-      </c>
-      <c r="G272" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>436.2879</t>
+        </is>
+      </c>
+      <c r="G272" s="2" t="inlineStr"/>
       <c r="H272" s="2" t="inlineStr">
         <is>
           <t>BUREAU  436,287.9 ล้านบาท  สร้างโอก</t>
@@ -9528,11 +8444,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F273" t="inlineStr">
-        <is>
-          <t>55,910</t>
-        </is>
-      </c>
+      <c r="F273" t="inlineStr"/>
       <c r="G273" t="inlineStr"/>
       <c r="H273" t="inlineStr">
         <is>
@@ -9560,11 +8472,7 @@
           <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
-      <c r="F274" t="inlineStr">
-        <is>
-          <t>2.53</t>
-        </is>
-      </c>
+      <c r="F274" t="inlineStr"/>
       <c r="G274" t="inlineStr"/>
       <c r="H274" t="inlineStr">
         <is>
@@ -9592,11 +8500,7 @@
           <t>บาท (ต่อหน่วย)</t>
         </is>
       </c>
-      <c r="F275" t="inlineStr">
-        <is>
-          <t>100,000</t>
-        </is>
-      </c>
+      <c r="F275" t="inlineStr"/>
       <c r="G275" t="inlineStr"/>
       <c r="H275" t="inlineStr">
         <is>
@@ -9626,14 +8530,10 @@
       </c>
       <c r="F276" s="2" t="inlineStr">
         <is>
-          <t>219,902.2000</t>
-        </is>
-      </c>
-      <c r="G276" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>219.9022</t>
+        </is>
+      </c>
+      <c r="G276" s="2" t="inlineStr"/>
       <c r="H276" s="2" t="inlineStr">
         <is>
           <t>ป 219,902.2 ล่านบาท  เร่งจัดก</t>
@@ -9660,11 +8560,7 @@
           <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
-      <c r="F277" t="inlineStr">
-        <is>
-          <t>2.47</t>
-        </is>
-      </c>
+      <c r="F277" t="inlineStr"/>
       <c r="G277" t="inlineStr"/>
       <c r="H277" t="inlineStr">
         <is>
@@ -9692,11 +8588,7 @@
           <t>บาท (ต่อหน่วย)</t>
         </is>
       </c>
-      <c r="F278" t="inlineStr">
-        <is>
-          <t>1,000</t>
-        </is>
-      </c>
+      <c r="F278" t="inlineStr"/>
       <c r="G278" t="inlineStr"/>
       <c r="H278" t="inlineStr">
         <is>
@@ -9724,11 +8616,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F279" t="inlineStr">
-        <is>
-          <t>91,810</t>
-        </is>
-      </c>
+      <c r="F279" t="inlineStr"/>
       <c r="G279" t="inlineStr"/>
       <c r="H279" t="inlineStr">
         <is>
@@ -9756,11 +8644,7 @@
           <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
-      <c r="F280" t="inlineStr">
-        <is>
-          <t>13.47</t>
-        </is>
-      </c>
+      <c r="F280" t="inlineStr"/>
       <c r="G280" t="inlineStr"/>
       <c r="H280" t="inlineStr">
         <is>
@@ -9788,11 +8672,7 @@
           <t>บาท (ต่อหน่วย)</t>
         </is>
       </c>
-      <c r="F281" t="inlineStr">
-        <is>
-          <t>1,000</t>
-        </is>
-      </c>
+      <c r="F281" t="inlineStr"/>
       <c r="G281" t="inlineStr"/>
       <c r="H281" t="inlineStr">
         <is>
@@ -9820,11 +8700,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F282" t="inlineStr">
-        <is>
-          <t>1,318</t>
-        </is>
-      </c>
+      <c r="F282" t="inlineStr"/>
       <c r="G282" t="inlineStr"/>
       <c r="H282" t="inlineStr">
         <is>
@@ -9852,11 +8728,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F283" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
+      <c r="F283" t="inlineStr"/>
       <c r="G283" t="inlineStr"/>
       <c r="H283" t="inlineStr">
         <is>
@@ -9884,11 +8756,7 @@
           <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
-      <c r="F284" t="inlineStr">
-        <is>
-          <t>10.14</t>
-        </is>
-      </c>
+      <c r="F284" t="inlineStr"/>
       <c r="G284" t="inlineStr"/>
       <c r="H284" t="inlineStr">
         <is>
@@ -9916,11 +8784,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F285" t="inlineStr">
-        <is>
-          <t>11,378</t>
-        </is>
-      </c>
+      <c r="F285" t="inlineStr"/>
       <c r="G285" t="inlineStr"/>
       <c r="H285" t="inlineStr">
         <is>
@@ -9950,14 +8814,10 @@
       </c>
       <c r="F286" s="2" t="inlineStr">
         <is>
-          <t>4,399.0000</t>
-        </is>
-      </c>
-      <c r="G286" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>0.4399</t>
+        </is>
+      </c>
+      <c r="G286" s="2" t="inlineStr"/>
       <c r="H286" s="2" t="inlineStr">
         <is>
           <t>้อยกว่า 4,399 au.  ผู้ประกอบการ</t>
@@ -9984,11 +8844,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F287" t="inlineStr">
-        <is>
-          <t>7,600</t>
-        </is>
-      </c>
+      <c r="F287" t="inlineStr"/>
       <c r="G287" t="inlineStr"/>
       <c r="H287" t="inlineStr">
         <is>
@@ -10016,11 +8872,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F288" t="inlineStr">
-        <is>
-          <t>26,000</t>
-        </is>
-      </c>
+      <c r="F288" t="inlineStr"/>
       <c r="G288" t="inlineStr"/>
       <c r="H288" t="inlineStr">
         <is>
@@ -10050,14 +8902,10 @@
       </c>
       <c r="F289" s="2" t="inlineStr">
         <is>
-          <t>4,825.3000</t>
-        </is>
-      </c>
-      <c r="G289" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>4.8253</t>
+        </is>
+      </c>
+      <c r="G289" s="2" t="inlineStr"/>
       <c r="H289" s="2" t="inlineStr">
         <is>
           <t>4,825.3 ล้านบาท  สร้างควา</t>
@@ -10084,11 +8932,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F290" t="inlineStr">
-        <is>
-          <t>30,000</t>
-        </is>
-      </c>
+      <c r="F290" t="inlineStr"/>
       <c r="G290" t="inlineStr"/>
       <c r="H290" t="inlineStr">
         <is>
@@ -10118,14 +8962,10 @@
       </c>
       <c r="F291" s="2" t="inlineStr">
         <is>
-          <t>185,939.3000</t>
-        </is>
-      </c>
-      <c r="G291" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>185.9393</t>
+        </is>
+      </c>
+      <c r="G291" s="2" t="inlineStr"/>
       <c r="H291" s="2" t="inlineStr">
         <is>
           <t>185,939.3 ล้านบาท  ยกระดับศ</t>
@@ -10152,11 +8992,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F292" t="inlineStr">
-        <is>
-          <t>1,200</t>
-        </is>
-      </c>
+      <c r="F292" t="inlineStr"/>
       <c r="G292" t="inlineStr"/>
       <c r="H292" t="inlineStr">
         <is>
@@ -10184,11 +9020,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F293" t="inlineStr">
-        <is>
-          <t>81,046</t>
-        </is>
-      </c>
+      <c r="F293" t="inlineStr"/>
       <c r="G293" t="inlineStr"/>
       <c r="H293" t="inlineStr">
         <is>
@@ -10216,11 +9048,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F294" t="inlineStr">
-        <is>
-          <t>52,349</t>
-        </is>
-      </c>
+      <c r="F294" t="inlineStr"/>
       <c r="G294" t="inlineStr"/>
       <c r="H294" t="inlineStr">
         <is>
@@ -10248,11 +9076,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F295" t="inlineStr">
-        <is>
-          <t>3,118,747</t>
-        </is>
-      </c>
+      <c r="F295" t="inlineStr"/>
       <c r="G295" t="inlineStr"/>
       <c r="H295" t="inlineStr">
         <is>
@@ -10282,14 +9106,10 @@
       </c>
       <c r="F296" s="2" t="inlineStr">
         <is>
-          <t>14,357.0000</t>
-        </is>
-      </c>
-      <c r="G296" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>14.3570</t>
+        </is>
+      </c>
+      <c r="G296" s="2" t="inlineStr"/>
       <c r="H296" s="2" t="inlineStr">
         <is>
           <t>น”      14,357.0 ลานบาท  สร้างแรงอ</t>
@@ -10316,11 +9136,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F297" t="inlineStr">
-        <is>
-          <t>9,020</t>
-        </is>
-      </c>
+      <c r="F297" t="inlineStr"/>
       <c r="G297" t="inlineStr"/>
       <c r="H297" t="inlineStr">
         <is>
@@ -10348,11 +9164,7 @@
           <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
-      <c r="F298" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
+      <c r="F298" t="inlineStr"/>
       <c r="G298" t="inlineStr"/>
       <c r="H298" t="inlineStr">
         <is>
@@ -10380,11 +9192,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F299" t="inlineStr">
-        <is>
-          <t>570,200</t>
-        </is>
-      </c>
+      <c r="F299" t="inlineStr"/>
       <c r="G299" t="inlineStr"/>
       <c r="H299" t="inlineStr">
         <is>
@@ -10412,11 +9220,7 @@
           <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
-      <c r="F300" t="inlineStr">
-        <is>
-          <t>2.06</t>
-        </is>
-      </c>
+      <c r="F300" t="inlineStr"/>
       <c r="G300" t="inlineStr"/>
       <c r="H300" t="inlineStr">
         <is>
@@ -10444,11 +9248,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F301" t="inlineStr">
-        <is>
-          <t>51,123</t>
-        </is>
-      </c>
+      <c r="F301" t="inlineStr"/>
       <c r="G301" t="inlineStr"/>
       <c r="H301" t="inlineStr">
         <is>
@@ -10476,11 +9276,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F302" t="inlineStr">
-        <is>
-          <t>14,000</t>
-        </is>
-      </c>
+      <c r="F302" t="inlineStr"/>
       <c r="G302" t="inlineStr"/>
       <c r="H302" t="inlineStr">
         <is>
@@ -10510,14 +9306,10 @@
       </c>
       <c r="F303" s="2" t="inlineStr">
         <is>
-          <t>11,264.1000</t>
-        </is>
-      </c>
-      <c r="G303" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>11.2641</t>
+        </is>
+      </c>
+      <c r="G303" s="2" t="inlineStr"/>
       <c r="H303" s="2" t="inlineStr">
         <is>
           <t>11,264.1 ล้านบาท  พัฒนาให้</t>
@@ -10544,11 +9336,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F304" t="inlineStr">
-        <is>
-          <t>139,755</t>
-        </is>
-      </c>
+      <c r="F304" t="inlineStr"/>
       <c r="G304" t="inlineStr"/>
       <c r="H304" t="inlineStr">
         <is>
@@ -10576,11 +9364,7 @@
           <t>บาท (ต่อหน่วย)</t>
         </is>
       </c>
-      <c r="F305" t="inlineStr">
-        <is>
-          <t>4,320</t>
-        </is>
-      </c>
+      <c r="F305" t="inlineStr"/>
       <c r="G305" t="inlineStr"/>
       <c r="H305" t="inlineStr">
         <is>
@@ -10608,11 +9392,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F306" t="inlineStr">
-        <is>
-          <t>14,668</t>
-        </is>
-      </c>
+      <c r="F306" t="inlineStr"/>
       <c r="G306" t="inlineStr"/>
       <c r="H306" t="inlineStr">
         <is>
@@ -10642,14 +9422,10 @@
       </c>
       <c r="F307" s="2" t="inlineStr">
         <is>
-          <t>162,951.5000</t>
-        </is>
-      </c>
-      <c r="G307" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>162.9515</t>
+        </is>
+      </c>
+      <c r="G307" s="2" t="inlineStr"/>
       <c r="H307" s="2" t="inlineStr">
         <is>
           <t>BUREAU  162,951.5 ล้านบาท  เร่งเสริ</t>
@@ -10678,14 +9454,10 @@
       </c>
       <c r="F308" s="2" t="inlineStr">
         <is>
-          <t>1,117.5000</t>
-        </is>
-      </c>
-      <c r="G308" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>1.1175</t>
+        </is>
+      </c>
+      <c r="G308" s="2" t="inlineStr"/>
       <c r="H308" s="2" t="inlineStr">
         <is>
           <t>1,117.5 ล้านบาท  ขับเคลือ</t>
@@ -10712,11 +9484,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F309" t="inlineStr">
-        <is>
-          <t>95,000</t>
-        </is>
-      </c>
+      <c r="F309" t="inlineStr"/>
       <c r="G309" t="inlineStr"/>
       <c r="H309" t="inlineStr">
         <is>
@@ -10746,14 +9514,10 @@
       </c>
       <c r="F310" s="2" t="inlineStr">
         <is>
-          <t>694.5000</t>
-        </is>
-      </c>
-      <c r="G310" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>0.6945</t>
+        </is>
+      </c>
+      <c r="G310" s="2" t="inlineStr"/>
       <c r="H310" s="2" t="inlineStr">
         <is>
           <t>694.5 ล้านบาท  {</t>
@@ -10780,11 +9544,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F311" t="inlineStr">
-        <is>
-          <t>8,000</t>
-        </is>
-      </c>
+      <c r="F311" t="inlineStr"/>
       <c r="G311" t="inlineStr"/>
       <c r="H311" t="inlineStr">
         <is>
@@ -10814,14 +9574,10 @@
       </c>
       <c r="F312" s="2" t="inlineStr">
         <is>
-          <t>744.9000</t>
-        </is>
-      </c>
-      <c r="G312" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>0.7449</t>
+        </is>
+      </c>
+      <c r="G312" s="2" t="inlineStr"/>
       <c r="H312" s="2" t="inlineStr">
         <is>
           <t>”       744.9 ลานบาท  : การขับเ</t>
@@ -10850,14 +9606,10 @@
       </c>
       <c r="F313" s="2" t="inlineStr">
         <is>
-          <t>19,845.2000</t>
-        </is>
-      </c>
-      <c r="G313" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>19.8452</t>
+        </is>
+      </c>
+      <c r="G313" s="2" t="inlineStr"/>
       <c r="H313" s="2" t="inlineStr">
         <is>
           <t>อ 19,845.2 ล่านบาท  ปข้องกัน</t>
@@ -10884,11 +9636,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F314" t="inlineStr">
-        <is>
-          <t>2,500</t>
-        </is>
-      </c>
+      <c r="F314" t="inlineStr"/>
       <c r="G314" t="inlineStr"/>
       <c r="H314" t="inlineStr">
         <is>
@@ -10916,11 +9664,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F315" t="inlineStr">
-        <is>
-          <t>22,200</t>
-        </is>
-      </c>
+      <c r="F315" t="inlineStr"/>
       <c r="G315" t="inlineStr"/>
       <c r="H315" t="inlineStr">
         <is>
@@ -10948,11 +9692,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F316" t="inlineStr">
-        <is>
-          <t>750,000</t>
-        </is>
-      </c>
+      <c r="F316" t="inlineStr"/>
       <c r="G316" t="inlineStr"/>
       <c r="H316" t="inlineStr">
         <is>
@@ -10980,11 +9720,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F317" t="inlineStr">
-        <is>
-          <t>4,400</t>
-        </is>
-      </c>
+      <c r="F317" t="inlineStr"/>
       <c r="G317" t="inlineStr"/>
       <c r="H317" t="inlineStr">
         <is>
@@ -11012,11 +9748,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F318" t="inlineStr">
-        <is>
-          <t>7,000</t>
-        </is>
-      </c>
+      <c r="F318" t="inlineStr"/>
       <c r="G318" t="inlineStr"/>
       <c r="H318" t="inlineStr"/>
     </row>
@@ -11040,11 +9772,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F319" t="inlineStr">
-        <is>
-          <t>60,500</t>
-        </is>
-      </c>
+      <c r="F319" t="inlineStr"/>
       <c r="G319" t="inlineStr"/>
       <c r="H319" t="inlineStr">
         <is>
@@ -11072,11 +9800,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F320" t="inlineStr">
-        <is>
-          <t>5,500</t>
-        </is>
-      </c>
+      <c r="F320" t="inlineStr"/>
       <c r="G320" t="inlineStr"/>
       <c r="H320" t="inlineStr">
         <is>
@@ -11104,11 +9828,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F321" t="inlineStr">
-        <is>
-          <t>82,500</t>
-        </is>
-      </c>
+      <c r="F321" t="inlineStr"/>
       <c r="G321" t="inlineStr"/>
       <c r="H321" t="inlineStr">
         <is>
@@ -11136,11 +9856,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F322" t="inlineStr">
-        <is>
-          <t>500,000</t>
-        </is>
-      </c>
+      <c r="F322" t="inlineStr"/>
       <c r="G322" t="inlineStr"/>
       <c r="H322" t="inlineStr">
         <is>
@@ -11168,11 +9884,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F323" t="inlineStr">
-        <is>
-          <t>54,100</t>
-        </is>
-      </c>
+      <c r="F323" t="inlineStr"/>
       <c r="G323" t="inlineStr"/>
       <c r="H323" t="inlineStr">
         <is>
@@ -11200,11 +9912,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F324" t="inlineStr">
-        <is>
-          <t>9,100</t>
-        </is>
-      </c>
+      <c r="F324" t="inlineStr"/>
       <c r="G324" t="inlineStr"/>
       <c r="H324" t="inlineStr">
         <is>
@@ -11232,11 +9940,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F325" t="inlineStr">
-        <is>
-          <t>80,000</t>
-        </is>
-      </c>
+      <c r="F325" t="inlineStr"/>
       <c r="G325" t="inlineStr"/>
       <c r="H325" t="inlineStr">
         <is>
@@ -11264,11 +9968,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F326" t="inlineStr">
-        <is>
-          <t>5,500</t>
-        </is>
-      </c>
+      <c r="F326" t="inlineStr"/>
       <c r="G326" t="inlineStr"/>
       <c r="H326" t="inlineStr">
         <is>
@@ -11296,11 +9996,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F327" t="inlineStr">
-        <is>
-          <t>1,478</t>
-        </is>
-      </c>
+      <c r="F327" t="inlineStr"/>
       <c r="G327" t="inlineStr"/>
       <c r="H327" t="inlineStr">
         <is>
@@ -11328,11 +10024,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F328" t="inlineStr">
-        <is>
-          <t>8,617</t>
-        </is>
-      </c>
+      <c r="F328" t="inlineStr"/>
       <c r="G328" t="inlineStr"/>
       <c r="H328" t="inlineStr">
         <is>
@@ -11360,11 +10052,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F329" t="inlineStr">
-        <is>
-          <t>1,293</t>
-        </is>
-      </c>
+      <c r="F329" t="inlineStr"/>
       <c r="G329" t="inlineStr"/>
       <c r="H329" t="inlineStr">
         <is>
@@ -11392,11 +10080,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F330" t="inlineStr">
-        <is>
-          <t>48,000</t>
-        </is>
-      </c>
+      <c r="F330" t="inlineStr"/>
       <c r="G330" t="inlineStr"/>
       <c r="H330" t="inlineStr">
         <is>
@@ -11424,11 +10108,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F331" t="inlineStr">
-        <is>
-          <t>4,200</t>
-        </is>
-      </c>
+      <c r="F331" t="inlineStr"/>
       <c r="G331" t="inlineStr"/>
       <c r="H331" t="inlineStr">
         <is>
@@ -11456,11 +10136,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F332" t="inlineStr">
-        <is>
-          <t>121,123.7</t>
-        </is>
-      </c>
+      <c r="F332" t="inlineStr"/>
       <c r="G332" t="inlineStr"/>
       <c r="H332" t="inlineStr"/>
     </row>
@@ -11484,11 +10160,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F333" t="inlineStr">
-        <is>
-          <t>13,200</t>
-        </is>
-      </c>
+      <c r="F333" t="inlineStr"/>
       <c r="G333" t="inlineStr"/>
       <c r="H333" t="inlineStr">
         <is>
@@ -11516,11 +10188,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F334" t="inlineStr">
-        <is>
-          <t>4,158</t>
-        </is>
-      </c>
+      <c r="F334" t="inlineStr"/>
       <c r="G334" t="inlineStr"/>
       <c r="H334" t="inlineStr">
         <is>
@@ -11548,11 +10216,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F335" t="inlineStr">
-        <is>
-          <t>100,000</t>
-        </is>
-      </c>
+      <c r="F335" t="inlineStr"/>
       <c r="G335" t="inlineStr"/>
       <c r="H335" t="inlineStr">
         <is>
@@ -11580,11 +10244,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F336" t="inlineStr">
-        <is>
-          <t>1,200</t>
-        </is>
-      </c>
+      <c r="F336" t="inlineStr"/>
       <c r="G336" t="inlineStr"/>
       <c r="H336" t="inlineStr">
         <is>
@@ -11612,11 +10272,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F337" t="inlineStr">
-        <is>
-          <t>500,000</t>
-        </is>
-      </c>
+      <c r="F337" t="inlineStr"/>
       <c r="G337" t="inlineStr"/>
       <c r="H337" t="inlineStr">
         <is>
@@ -11644,11 +10300,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F338" t="inlineStr">
-        <is>
-          <t>192,870</t>
-        </is>
-      </c>
+      <c r="F338" t="inlineStr"/>
       <c r="G338" t="inlineStr"/>
       <c r="H338" t="inlineStr">
         <is>
@@ -11676,11 +10328,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F339" t="inlineStr">
-        <is>
-          <t>35,800</t>
-        </is>
-      </c>
+      <c r="F339" t="inlineStr"/>
       <c r="G339" t="inlineStr"/>
       <c r="H339" t="inlineStr">
         <is>
@@ -11708,11 +10356,7 @@
           <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
-      <c r="F340" t="inlineStr">
-        <is>
-          <t>7.48</t>
-        </is>
-      </c>
+      <c r="F340" t="inlineStr"/>
       <c r="G340" t="inlineStr"/>
       <c r="H340" t="inlineStr">
         <is>
@@ -11740,11 +10384,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F341" t="inlineStr">
-        <is>
-          <t>210,000</t>
-        </is>
-      </c>
+      <c r="F341" t="inlineStr"/>
       <c r="G341" t="inlineStr"/>
       <c r="H341" t="inlineStr">
         <is>
@@ -11772,11 +10412,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F342" t="inlineStr">
-        <is>
-          <t>34,334</t>
-        </is>
-      </c>
+      <c r="F342" t="inlineStr"/>
       <c r="G342" t="inlineStr"/>
       <c r="H342" t="inlineStr">
         <is>
@@ -11804,11 +10440,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F343" t="inlineStr">
-        <is>
-          <t>10,000</t>
-        </is>
-      </c>
+      <c r="F343" t="inlineStr"/>
       <c r="G343" t="inlineStr"/>
       <c r="H343" t="inlineStr">
         <is>
@@ -11836,11 +10468,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F344" t="inlineStr">
-        <is>
-          <t>1,000</t>
-        </is>
-      </c>
+      <c r="F344" t="inlineStr"/>
       <c r="G344" t="inlineStr"/>
       <c r="H344" t="inlineStr">
         <is>
@@ -11870,14 +10498,10 @@
       </c>
       <c r="F345" s="2" t="inlineStr">
         <is>
-          <t>17,310.9000</t>
-        </is>
-      </c>
-      <c r="G345" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>17.3109</t>
+        </is>
+      </c>
+      <c r="G345" s="2" t="inlineStr"/>
       <c r="H345" s="2" t="inlineStr">
         <is>
           <t>จ กะร1 17,310.9 ล้านบาท  oe Ca  ๑</t>
@@ -11906,14 +10530,10 @@
       </c>
       <c r="F346" s="2" t="inlineStr">
         <is>
-          <t>2,114.4000</t>
-        </is>
-      </c>
-      <c r="G346" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>2.1144</t>
+        </is>
+      </c>
+      <c r="G346" s="2" t="inlineStr"/>
       <c r="H346" s="2" t="inlineStr">
         <is>
           <t>มั่นคง  2,114.4 ล้านบาท  โครงการท</t>
@@ -11940,11 +10560,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F347" t="inlineStr">
-        <is>
-          <t>25,000</t>
-        </is>
-      </c>
+      <c r="F347" t="inlineStr"/>
       <c r="G347" t="inlineStr"/>
       <c r="H347" t="inlineStr">
         <is>
@@ -11974,14 +10590,10 @@
       </c>
       <c r="F348" s="2" t="inlineStr">
         <is>
-          <t>698,046.9000</t>
-        </is>
-      </c>
-      <c r="G348" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>698.0469</t>
+        </is>
+      </c>
+      <c r="G348" s="2" t="inlineStr"/>
       <c r="H348" s="2" t="inlineStr">
         <is>
           <t>านสังคม 698,046.9 ล้านบาท  ๑ เรียนฟ</t>
@@ -12008,11 +10620,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F349" t="inlineStr">
-        <is>
-          <t>250,000</t>
-        </is>
-      </c>
+      <c r="F349" t="inlineStr"/>
       <c r="G349" t="inlineStr"/>
       <c r="H349" t="inlineStr">
         <is>
@@ -12040,11 +10648,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F350" t="inlineStr">
-        <is>
-          <t>50,000</t>
-        </is>
-      </c>
+      <c r="F350" t="inlineStr"/>
       <c r="G350" t="inlineStr"/>
       <c r="H350" t="inlineStr">
         <is>
@@ -12072,11 +10676,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F351" t="inlineStr">
-        <is>
-          <t>5,500</t>
-        </is>
-      </c>
+      <c r="F351" t="inlineStr"/>
       <c r="G351" t="inlineStr"/>
       <c r="H351" t="inlineStr">
         <is>
@@ -12104,11 +10704,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F352" t="inlineStr">
-        <is>
-          <t>607,655</t>
-        </is>
-      </c>
+      <c r="F352" t="inlineStr"/>
       <c r="G352" t="inlineStr"/>
       <c r="H352" t="inlineStr"/>
     </row>
@@ -12134,14 +10730,10 @@
       </c>
       <c r="F353" s="2" t="inlineStr">
         <is>
-          <t>214,931.7000</t>
-        </is>
-      </c>
-      <c r="G353" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>214.9317</t>
+        </is>
+      </c>
+      <c r="G353" s="2" t="inlineStr"/>
       <c r="H353" s="2" t="inlineStr">
         <is>
           <t>พนโนโตน 214,931.7 ล้านบาท  เพัฒนาแพ</t>
@@ -12168,11 +10760,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F354" t="inlineStr">
-        <is>
-          <t>1,448</t>
-        </is>
-      </c>
+      <c r="F354" t="inlineStr"/>
       <c r="G354" t="inlineStr"/>
       <c r="H354" t="inlineStr">
         <is>
@@ -12200,11 +10788,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F355" t="inlineStr">
-        <is>
-          <t>125,785</t>
-        </is>
-      </c>
+      <c r="F355" t="inlineStr"/>
       <c r="G355" t="inlineStr"/>
       <c r="H355" t="inlineStr">
         <is>
@@ -12232,11 +10816,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F356" t="inlineStr">
-        <is>
-          <t>4,600</t>
-        </is>
-      </c>
+      <c r="F356" t="inlineStr"/>
       <c r="G356" t="inlineStr"/>
       <c r="H356" t="inlineStr">
         <is>
@@ -12264,11 +10844,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F357" t="inlineStr">
-        <is>
-          <t>3,120</t>
-        </is>
-      </c>
+      <c r="F357" t="inlineStr"/>
       <c r="G357" t="inlineStr"/>
       <c r="H357" t="inlineStr">
         <is>
@@ -12296,11 +10872,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F358" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
+      <c r="F358" t="inlineStr"/>
       <c r="G358" t="inlineStr"/>
       <c r="H358" t="inlineStr">
         <is>
@@ -12328,11 +10900,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F359" t="inlineStr">
-        <is>
-          <t>20,000</t>
-        </is>
-      </c>
+      <c r="F359" t="inlineStr"/>
       <c r="G359" t="inlineStr"/>
       <c r="H359" t="inlineStr">
         <is>
@@ -12360,11 +10928,7 @@
           <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
-      <c r="F360" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
+      <c r="F360" t="inlineStr"/>
       <c r="G360" t="inlineStr"/>
       <c r="H360" t="inlineStr">
         <is>
@@ -12392,11 +10956,7 @@
           <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
-      <c r="F361" t="inlineStr">
-        <is>
-          <t>5.94</t>
-        </is>
-      </c>
+      <c r="F361" t="inlineStr"/>
       <c r="G361" t="inlineStr"/>
       <c r="H361" t="inlineStr">
         <is>
@@ -12424,11 +10984,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F362" t="inlineStr">
-        <is>
-          <t>488,815</t>
-        </is>
-      </c>
+      <c r="F362" t="inlineStr"/>
       <c r="G362" t="inlineStr"/>
       <c r="H362" t="inlineStr">
         <is>
@@ -12456,11 +11012,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F363" t="inlineStr">
-        <is>
-          <t>16,681</t>
-        </is>
-      </c>
+      <c r="F363" t="inlineStr"/>
       <c r="G363" t="inlineStr"/>
       <c r="H363" t="inlineStr">
         <is>
@@ -12488,11 +11040,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F364" t="inlineStr">
-        <is>
-          <t>30,406</t>
-        </is>
-      </c>
+      <c r="F364" t="inlineStr"/>
       <c r="G364" t="inlineStr"/>
       <c r="H364" t="inlineStr">
         <is>
@@ -12520,11 +11068,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F365" t="inlineStr">
-        <is>
-          <t>16,020</t>
-        </is>
-      </c>
+      <c r="F365" t="inlineStr"/>
       <c r="G365" t="inlineStr"/>
       <c r="H365" t="inlineStr">
         <is>
@@ -12552,11 +11096,7 @@
           <t>บาท (ต่อหน่วย)</t>
         </is>
       </c>
-      <c r="F366" t="inlineStr">
-        <is>
-          <t>4,175.99</t>
-        </is>
-      </c>
+      <c r="F366" t="inlineStr"/>
       <c r="G366" t="inlineStr"/>
       <c r="H366" t="inlineStr">
         <is>
@@ -12584,11 +11124,7 @@
           <t>บาท (ต่อหน่วย)</t>
         </is>
       </c>
-      <c r="F367" t="inlineStr">
-        <is>
-          <t>4,669.74</t>
-        </is>
-      </c>
+      <c r="F367" t="inlineStr"/>
       <c r="G367" t="inlineStr"/>
       <c r="H367" t="inlineStr">
         <is>
@@ -12616,11 +11152,7 @@
           <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
-      <c r="F368" t="inlineStr">
-        <is>
-          <t>47.17</t>
-        </is>
-      </c>
+      <c r="F368" t="inlineStr"/>
       <c r="G368" t="inlineStr"/>
       <c r="H368" t="inlineStr">
         <is>
@@ -12648,11 +11180,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F369" t="inlineStr">
-        <is>
-          <t>459,737</t>
-        </is>
-      </c>
+      <c r="F369" t="inlineStr"/>
       <c r="G369" t="inlineStr"/>
       <c r="H369" t="inlineStr">
         <is>
@@ -12680,11 +11208,7 @@
           <t>บาท (ต่อหน่วย)</t>
         </is>
       </c>
-      <c r="F370" t="inlineStr">
-        <is>
-          <t>3,221.87</t>
-        </is>
-      </c>
+      <c r="F370" t="inlineStr"/>
       <c r="G370" t="inlineStr"/>
       <c r="H370" t="inlineStr">
         <is>
@@ -12714,14 +11238,10 @@
       </c>
       <c r="F371" s="2" t="inlineStr">
         <is>
-          <t>478,174.8000</t>
-        </is>
-      </c>
-      <c r="G371" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>478.1748</t>
+        </is>
+      </c>
+      <c r="G371" s="2" t="inlineStr"/>
       <c r="H371" s="2" t="inlineStr">
         <is>
           <t>รไลหน 478,174.8 ล้านบาท  ปรับปรุง</t>
@@ -12748,11 +11268,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F372" t="inlineStr">
-        <is>
-          <t>3,427,600</t>
-        </is>
-      </c>
+      <c r="F372" t="inlineStr"/>
       <c r="G372" t="inlineStr"/>
       <c r="H372" t="inlineStr"/>
     </row>
@@ -12776,11 +11292,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F373" t="inlineStr">
-        <is>
-          <t>5,168</t>
-        </is>
-      </c>
+      <c r="F373" t="inlineStr"/>
       <c r="G373" t="inlineStr"/>
       <c r="H373" t="inlineStr">
         <is>
@@ -12808,11 +11320,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F374" t="inlineStr">
-        <is>
-          <t>1.08</t>
-        </is>
-      </c>
+      <c r="F374" t="inlineStr"/>
       <c r="G374" t="inlineStr"/>
       <c r="H374" t="inlineStr">
         <is>
@@ -12840,11 +11348,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F375" t="inlineStr">
-        <is>
-          <t>7,256</t>
-        </is>
-      </c>
+      <c r="F375" t="inlineStr"/>
       <c r="G375" t="inlineStr"/>
       <c r="H375" t="inlineStr">
         <is>
@@ -12872,11 +11376,7 @@
           <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
-      <c r="F376" t="inlineStr">
-        <is>
-          <t>22.88</t>
-        </is>
-      </c>
+      <c r="F376" t="inlineStr"/>
       <c r="G376" t="inlineStr"/>
       <c r="H376" t="inlineStr">
         <is>
@@ -12906,14 +11406,10 @@
       </c>
       <c r="F377" s="2" t="inlineStr">
         <is>
-          <t>4,940.4000</t>
-        </is>
-      </c>
-      <c r="G377" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>4.9404</t>
+        </is>
+      </c>
+      <c r="G377" s="2" t="inlineStr"/>
       <c r="H377" s="2" t="inlineStr">
         <is>
           <t>ู้อื่น  4,940.4 ล้านบาท  ๑ พัฒนาศ</t>
@@ -12940,11 +11436,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F378" t="inlineStr">
-        <is>
-          <t>21,350</t>
-        </is>
-      </c>
+      <c r="F378" t="inlineStr"/>
       <c r="G378" t="inlineStr"/>
       <c r="H378" t="inlineStr">
         <is>
@@ -12974,14 +11466,10 @@
       </c>
       <c r="F379" s="2" t="inlineStr">
         <is>
-          <t>303,490.0000</t>
-        </is>
-      </c>
-      <c r="G379" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>30.3490</t>
+        </is>
+      </c>
+      <c r="G379" s="2" t="inlineStr"/>
       <c r="H379" s="2" t="inlineStr">
         <is>
           <t>ในชุมชน 303,490 au ได้รับการส่งเส</t>
@@ -13008,11 +11496,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F380" t="inlineStr">
-        <is>
-          <t>9,000</t>
-        </is>
-      </c>
+      <c r="F380" t="inlineStr"/>
       <c r="G380" t="inlineStr"/>
       <c r="H380" t="inlineStr">
         <is>
@@ -13040,11 +11524,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F381" t="inlineStr">
-        <is>
-          <t>52,827</t>
-        </is>
-      </c>
+      <c r="F381" t="inlineStr"/>
       <c r="G381" t="inlineStr"/>
       <c r="H381" t="inlineStr">
         <is>
@@ -13072,11 +11552,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F382" t="inlineStr">
-        <is>
-          <t>156,000</t>
-        </is>
-      </c>
+      <c r="F382" t="inlineStr"/>
       <c r="G382" t="inlineStr"/>
       <c r="H382" t="inlineStr">
         <is>
@@ -13104,11 +11580,7 @@
           <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
-      <c r="F383" t="inlineStr">
-        <is>
-          <t>1.8</t>
-        </is>
-      </c>
+      <c r="F383" t="inlineStr"/>
       <c r="G383" t="inlineStr"/>
       <c r="H383" t="inlineStr">
         <is>
@@ -13136,11 +11608,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F384" t="inlineStr">
-        <is>
-          <t>170,390.6</t>
-        </is>
-      </c>
+      <c r="F384" t="inlineStr"/>
       <c r="G384" t="inlineStr"/>
       <c r="H384" t="inlineStr"/>
     </row>
@@ -13164,11 +11632,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F385" t="inlineStr">
-        <is>
-          <t>240,901</t>
-        </is>
-      </c>
+      <c r="F385" t="inlineStr"/>
       <c r="G385" t="inlineStr"/>
       <c r="H385" t="inlineStr">
         <is>
@@ -13196,11 +11660,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F386" t="inlineStr">
-        <is>
-          <t>307,160</t>
-        </is>
-      </c>
+      <c r="F386" t="inlineStr"/>
       <c r="G386" t="inlineStr"/>
       <c r="H386" t="inlineStr">
         <is>
@@ -13228,11 +11688,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F387" t="inlineStr">
-        <is>
-          <t>230,941</t>
-        </is>
-      </c>
+      <c r="F387" t="inlineStr"/>
       <c r="G387" t="inlineStr"/>
       <c r="H387" t="inlineStr">
         <is>
@@ -13260,11 +11716,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F388" t="inlineStr">
-        <is>
-          <t>120,000</t>
-        </is>
-      </c>
+      <c r="F388" t="inlineStr"/>
       <c r="G388" t="inlineStr"/>
       <c r="H388" t="inlineStr">
         <is>
@@ -13292,11 +11744,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F389" t="inlineStr">
-        <is>
-          <t>2,275</t>
-        </is>
-      </c>
+      <c r="F389" t="inlineStr"/>
       <c r="G389" t="inlineStr"/>
       <c r="H389" t="inlineStr">
         <is>
@@ -13324,11 +11772,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F390" t="inlineStr">
-        <is>
-          <t>23,500</t>
-        </is>
-      </c>
+      <c r="F390" t="inlineStr"/>
       <c r="G390" t="inlineStr"/>
       <c r="H390" t="inlineStr">
         <is>
@@ -13356,11 +11800,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F391" t="inlineStr">
-        <is>
-          <t>33,444</t>
-        </is>
-      </c>
+      <c r="F391" t="inlineStr"/>
       <c r="G391" t="inlineStr"/>
       <c r="H391" t="inlineStr">
         <is>
@@ -13388,11 +11828,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F392" t="inlineStr">
-        <is>
-          <t>1,010</t>
-        </is>
-      </c>
+      <c r="F392" t="inlineStr"/>
       <c r="G392" t="inlineStr"/>
       <c r="H392" t="inlineStr">
         <is>
@@ -13420,11 +11856,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F393" t="inlineStr">
-        <is>
-          <t>148,929</t>
-        </is>
-      </c>
+      <c r="F393" t="inlineStr"/>
       <c r="G393" t="inlineStr"/>
       <c r="H393" t="inlineStr">
         <is>
@@ -13452,11 +11884,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F394" t="inlineStr">
-        <is>
-          <t>9.44</t>
-        </is>
-      </c>
+      <c r="F394" t="inlineStr"/>
       <c r="G394" t="inlineStr"/>
       <c r="H394" t="inlineStr">
         <is>
@@ -13486,14 +11914,10 @@
       </c>
       <c r="F395" s="2" t="inlineStr">
         <is>
-          <t>140,493.0000</t>
-        </is>
-      </c>
-      <c r="G395" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>14.0493</t>
+        </is>
+      </c>
+      <c r="G395" s="2" t="inlineStr"/>
       <c r="H395" s="2" t="inlineStr">
         <is>
           <t>DP/GPP) 140,493 ล้านบาท  ขยายระบบ</t>
@@ -13520,11 +11944,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F396" t="inlineStr">
-        <is>
-          <t>77,889</t>
-        </is>
-      </c>
+      <c r="F396" t="inlineStr"/>
       <c r="G396" t="inlineStr"/>
       <c r="H396" t="inlineStr">
         <is>
@@ -13552,11 +11972,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F397" t="inlineStr">
-        <is>
-          <t>277,698</t>
-        </is>
-      </c>
+      <c r="F397" t="inlineStr"/>
       <c r="G397" t="inlineStr"/>
       <c r="H397" t="inlineStr">
         <is>
@@ -13584,11 +12000,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F398" t="inlineStr">
-        <is>
-          <t>1,620</t>
-        </is>
-      </c>
+      <c r="F398" t="inlineStr"/>
       <c r="G398" t="inlineStr"/>
       <c r="H398" t="inlineStr">
         <is>
@@ -13616,11 +12028,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F399" t="inlineStr">
-        <is>
-          <t>115,694.0</t>
-        </is>
-      </c>
+      <c r="F399" t="inlineStr"/>
       <c r="G399" t="inlineStr"/>
       <c r="H399" t="inlineStr"/>
     </row>
@@ -13644,11 +12052,7 @@
           <t>บาท (ต่อหน่วย)</t>
         </is>
       </c>
-      <c r="F400" t="inlineStr">
-        <is>
-          <t>1,000</t>
-        </is>
-      </c>
+      <c r="F400" t="inlineStr"/>
       <c r="G400" t="inlineStr"/>
       <c r="H400" t="inlineStr">
         <is>
@@ -13676,11 +12080,7 @@
           <t>บาท (ต่อหน่วย)</t>
         </is>
       </c>
-      <c r="F401" t="inlineStr">
-        <is>
-          <t>88,600</t>
-        </is>
-      </c>
+      <c r="F401" t="inlineStr"/>
       <c r="G401" t="inlineStr"/>
       <c r="H401" t="inlineStr">
         <is>
@@ -13708,11 +12108,7 @@
           <t>บาท (ต่อหน่วย)</t>
         </is>
       </c>
-      <c r="F402" t="inlineStr">
-        <is>
-          <t>2,400</t>
-        </is>
-      </c>
+      <c r="F402" t="inlineStr"/>
       <c r="G402" t="inlineStr"/>
       <c r="H402" t="inlineStr">
         <is>
@@ -13742,14 +12138,10 @@
       </c>
       <c r="F403" s="2" t="inlineStr">
         <is>
-          <t>4,800.0000</t>
-        </is>
-      </c>
-      <c r="G403" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>0.4800</t>
+        </is>
+      </c>
+      <c r="G403" s="2" t="inlineStr"/>
       <c r="H403" s="2" t="inlineStr">
         <is>
           <t>4,800.0 ล้านบาท  ช่วยเห</t>
@@ -13776,11 +12168,7 @@
           <t>บาท (ต่อหน่วย)</t>
         </is>
       </c>
-      <c r="F404" t="inlineStr">
-        <is>
-          <t>88,600</t>
-        </is>
-      </c>
+      <c r="F404" t="inlineStr"/>
       <c r="G404" t="inlineStr"/>
       <c r="H404" t="inlineStr">
         <is>
@@ -13808,11 +12196,7 @@
           <t>บาท (ต่อหน่วย)</t>
         </is>
       </c>
-      <c r="F405" t="inlineStr">
-        <is>
-          <t>88,600</t>
-        </is>
-      </c>
+      <c r="F405" t="inlineStr"/>
       <c r="G405" t="inlineStr"/>
       <c r="H405" t="inlineStr">
         <is>
@@ -13840,11 +12224,7 @@
           <t>บาท (ต่อหน่วย)</t>
         </is>
       </c>
-      <c r="F406" t="inlineStr">
-        <is>
-          <t>88,600</t>
-        </is>
-      </c>
+      <c r="F406" t="inlineStr"/>
       <c r="G406" t="inlineStr"/>
       <c r="H406" t="inlineStr">
         <is>
@@ -13874,14 +12254,10 @@
       </c>
       <c r="F407" s="2" t="inlineStr">
         <is>
-          <t>4,800.0000</t>
-        </is>
-      </c>
-      <c r="G407" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>4.8000</t>
+        </is>
+      </c>
+      <c r="G407" s="2" t="inlineStr"/>
       <c r="H407" s="2" t="inlineStr">
         <is>
           <t>4,800.0 ล้านบาท  ช่วยเหลื</t>
@@ -13908,11 +12284,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F408" t="inlineStr">
-        <is>
-          <t>110,000</t>
-        </is>
-      </c>
+      <c r="F408" t="inlineStr"/>
       <c r="G408" t="inlineStr"/>
       <c r="H408" t="inlineStr">
         <is>
@@ -13940,11 +12312,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F409" t="inlineStr">
-        <is>
-          <t>135,230</t>
-        </is>
-      </c>
+      <c r="F409" t="inlineStr"/>
       <c r="G409" t="inlineStr"/>
       <c r="H409" t="inlineStr">
         <is>
@@ -13972,11 +12340,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F410" t="inlineStr">
-        <is>
-          <t>200,000</t>
-        </is>
-      </c>
+      <c r="F410" t="inlineStr"/>
       <c r="G410" t="inlineStr"/>
       <c r="H410" t="inlineStr">
         <is>
@@ -14004,11 +12368,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F411" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
+      <c r="F411" t="inlineStr"/>
       <c r="G411" t="inlineStr"/>
       <c r="H411" t="inlineStr">
         <is>
@@ -14036,11 +12396,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F412" t="inlineStr">
-        <is>
-          <t>100,000</t>
-        </is>
-      </c>
+      <c r="F412" t="inlineStr"/>
       <c r="G412" t="inlineStr"/>
       <c r="H412" t="inlineStr">
         <is>
@@ -14068,11 +12424,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F413" t="inlineStr">
-        <is>
-          <t>5,600</t>
-        </is>
-      </c>
+      <c r="F413" t="inlineStr"/>
       <c r="G413" t="inlineStr"/>
       <c r="H413" t="inlineStr">
         <is>
@@ -14100,11 +12452,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F414" t="inlineStr">
-        <is>
-          <t>10,600</t>
-        </is>
-      </c>
+      <c r="F414" t="inlineStr"/>
       <c r="G414" t="inlineStr"/>
       <c r="H414" t="inlineStr">
         <is>
@@ -14132,11 +12480,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F415" t="inlineStr">
-        <is>
-          <t>21.0685</t>
-        </is>
-      </c>
+      <c r="F415" t="inlineStr"/>
       <c r="G415" t="inlineStr"/>
       <c r="H415" t="inlineStr">
         <is>
@@ -14166,14 +12510,10 @@
       </c>
       <c r="F416" s="2" t="inlineStr">
         <is>
-          <t>6.4900</t>
-        </is>
-      </c>
-      <c r="G416" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>0.0649</t>
+        </is>
+      </c>
+      <c r="G416" s="2" t="inlineStr"/>
       <c r="H416" s="2" t="inlineStr">
         <is>
           <t>ยได้รวม 6.49 ล้านบาท และเพิ่มโ</t>
@@ -14202,14 +12542,10 @@
       </c>
       <c r="F417" s="2" t="inlineStr">
         <is>
-          <t>44,492.1000</t>
-        </is>
-      </c>
-      <c r="G417" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>44.4921</t>
+        </is>
+      </c>
+      <c r="G417" s="2" t="inlineStr"/>
       <c r="H417" s="2" t="inlineStr">
         <is>
           <t>44,492.1 ล้านบาท  พัฒนายกร</t>
@@ -14236,11 +12572,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F418" t="inlineStr">
-        <is>
-          <t>47,600</t>
-        </is>
-      </c>
+      <c r="F418" t="inlineStr"/>
       <c r="G418" t="inlineStr"/>
       <c r="H418" t="inlineStr">
         <is>
@@ -14268,11 +12600,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F419" t="inlineStr">
-        <is>
-          <t>2,320</t>
-        </is>
-      </c>
+      <c r="F419" t="inlineStr"/>
       <c r="G419" t="inlineStr"/>
       <c r="H419" t="inlineStr">
         <is>
@@ -14300,11 +12628,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F420" t="inlineStr">
-        <is>
-          <t>75,000</t>
-        </is>
-      </c>
+      <c r="F420" t="inlineStr"/>
       <c r="G420" t="inlineStr"/>
       <c r="H420" t="inlineStr">
         <is>
@@ -14332,11 +12656,7 @@
           <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
-      <c r="F421" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
+      <c r="F421" t="inlineStr"/>
       <c r="G421" t="inlineStr"/>
       <c r="H421" t="inlineStr">
         <is>
@@ -14364,11 +12684,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F422" t="inlineStr">
-        <is>
-          <t>3,190</t>
-        </is>
-      </c>
+      <c r="F422" t="inlineStr"/>
       <c r="G422" t="inlineStr"/>
       <c r="H422" t="inlineStr">
         <is>
@@ -14396,11 +12712,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F423" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
+      <c r="F423" t="inlineStr"/>
       <c r="G423" t="inlineStr"/>
       <c r="H423" t="inlineStr">
         <is>
@@ -14428,11 +12740,7 @@
           <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
-      <c r="F424" t="inlineStr">
-        <is>
-          <t>27.38</t>
-        </is>
-      </c>
+      <c r="F424" t="inlineStr"/>
       <c r="G424" t="inlineStr"/>
       <c r="H424" t="inlineStr">
         <is>
@@ -14460,11 +12768,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F425" t="inlineStr">
-        <is>
-          <t>3,895</t>
-        </is>
-      </c>
+      <c r="F425" t="inlineStr"/>
       <c r="G425" t="inlineStr"/>
       <c r="H425" t="inlineStr">
         <is>
@@ -14492,11 +12796,7 @@
           <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
-      <c r="F426" t="inlineStr">
-        <is>
-          <t>73.85</t>
-        </is>
-      </c>
+      <c r="F426" t="inlineStr"/>
       <c r="G426" t="inlineStr"/>
       <c r="H426" t="inlineStr">
         <is>
@@ -14524,11 +12824,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F427" t="inlineStr">
-        <is>
-          <t>25,394</t>
-        </is>
-      </c>
+      <c r="F427" t="inlineStr"/>
       <c r="G427" t="inlineStr"/>
       <c r="H427" t="inlineStr">
         <is>
@@ -14556,11 +12852,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F428" t="inlineStr">
-        <is>
-          <t>4,000</t>
-        </is>
-      </c>
+      <c r="F428" t="inlineStr"/>
       <c r="G428" t="inlineStr"/>
       <c r="H428" t="inlineStr">
         <is>
@@ -14588,11 +12880,7 @@
           <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
-      <c r="F429" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
+      <c r="F429" t="inlineStr"/>
       <c r="G429" t="inlineStr"/>
       <c r="H429" t="inlineStr">
         <is>
@@ -14620,11 +12908,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F430" t="inlineStr">
-        <is>
-          <t>3,230</t>
-        </is>
-      </c>
+      <c r="F430" t="inlineStr"/>
       <c r="G430" t="inlineStr"/>
       <c r="H430" t="inlineStr">
         <is>
@@ -14652,11 +12936,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F431" t="inlineStr">
-        <is>
-          <t>3,151</t>
-        </is>
-      </c>
+      <c r="F431" t="inlineStr"/>
       <c r="G431" t="inlineStr"/>
       <c r="H431" t="inlineStr">
         <is>
@@ -14684,11 +12964,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F432" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
+      <c r="F432" t="inlineStr"/>
       <c r="G432" t="inlineStr"/>
       <c r="H432" t="inlineStr">
         <is>
@@ -14716,11 +12992,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F433" t="inlineStr">
-        <is>
-          <t>200,000</t>
-        </is>
-      </c>
+      <c r="F433" t="inlineStr"/>
       <c r="G433" t="inlineStr"/>
       <c r="H433" t="inlineStr">
         <is>
@@ -14748,11 +13020,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F434" t="inlineStr">
-        <is>
-          <t>42,000</t>
-        </is>
-      </c>
+      <c r="F434" t="inlineStr"/>
       <c r="G434" t="inlineStr"/>
       <c r="H434" t="inlineStr">
         <is>
@@ -14780,11 +13048,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F435" t="inlineStr">
-        <is>
-          <t>17,250</t>
-        </is>
-      </c>
+      <c r="F435" t="inlineStr"/>
       <c r="G435" t="inlineStr"/>
       <c r="H435" t="inlineStr">
         <is>
@@ -14812,11 +13076,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F436" t="inlineStr">
-        <is>
-          <t>500,000</t>
-        </is>
-      </c>
+      <c r="F436" t="inlineStr"/>
       <c r="G436" t="inlineStr"/>
       <c r="H436" t="inlineStr">
         <is>
@@ -14844,11 +13104,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F437" t="inlineStr">
-        <is>
-          <t>5,404.5</t>
-        </is>
-      </c>
+      <c r="F437" t="inlineStr"/>
       <c r="G437" t="inlineStr"/>
       <c r="H437" t="inlineStr"/>
     </row>
@@ -14874,14 +13130,10 @@
       </c>
       <c r="F438" s="2" t="inlineStr">
         <is>
-          <t>35,411.9000</t>
-        </is>
-      </c>
-      <c r="G438" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>35.4119</t>
+        </is>
+      </c>
+      <c r="G438" s="2" t="inlineStr"/>
       <c r="H438" s="2" t="inlineStr">
         <is>
           <t>กฎหมาย  35,411.9 ล้านบาท  ราชการทั</t>
@@ -14908,11 +13160,7 @@
           <t>จำนวน (ล้านหน่วย)</t>
         </is>
       </c>
-      <c r="F439" t="inlineStr">
-        <is>
-          <t>13.65</t>
-        </is>
-      </c>
+      <c r="F439" t="inlineStr"/>
       <c r="G439" t="inlineStr"/>
       <c r="H439" t="inlineStr">
         <is>
@@ -14940,11 +13188,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F440" t="inlineStr">
-        <is>
-          <t>1,250</t>
-        </is>
-      </c>
+      <c r="F440" t="inlineStr"/>
       <c r="G440" t="inlineStr"/>
       <c r="H440" t="inlineStr">
         <is>
@@ -14972,11 +13216,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F441" t="inlineStr">
-        <is>
-          <t>25,537.2</t>
-        </is>
-      </c>
+      <c r="F441" t="inlineStr"/>
       <c r="G441" t="inlineStr"/>
       <c r="H441" t="inlineStr"/>
     </row>
@@ -15000,11 +13240,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F442" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
+      <c r="F442" t="inlineStr"/>
       <c r="G442" t="inlineStr"/>
       <c r="H442" t="inlineStr">
         <is>
@@ -15034,14 +13270,10 @@
       </c>
       <c r="F443" s="2" t="inlineStr">
         <is>
-          <t>611,220.0000</t>
-        </is>
-      </c>
-      <c r="G443" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>61.1220</t>
+        </is>
+      </c>
+      <c r="G443" s="2" t="inlineStr"/>
       <c r="H443" s="2" t="inlineStr">
         <is>
           <t>้อยกว่า 611,220 au.  จากสินค้าและ</t>
@@ -15070,14 +13302,10 @@
       </c>
       <c r="F444" s="2" t="inlineStr">
         <is>
-          <t>2,517,700.0000</t>
-        </is>
-      </c>
-      <c r="G444" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>251.7700</t>
+        </is>
+      </c>
+      <c r="G444" s="2" t="inlineStr"/>
       <c r="H444" s="2" t="inlineStr">
         <is>
           <t>้อยกว่า 2,517,700 au. อากภาษีรายได้</t>
@@ -15104,11 +13332,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F445" t="inlineStr">
-        <is>
-          <t>7,732.0</t>
-        </is>
-      </c>
+      <c r="F445" t="inlineStr"/>
       <c r="G445" t="inlineStr"/>
       <c r="H445" t="inlineStr"/>
     </row>
@@ -15134,14 +13358,10 @@
       </c>
       <c r="F446" s="2" t="inlineStr">
         <is>
-          <t>116,600.0000</t>
-        </is>
-      </c>
-      <c r="G446" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>11.6600</t>
+        </is>
+      </c>
+      <c r="G446" s="2" t="inlineStr"/>
       <c r="H446" s="2" t="inlineStr">
         <is>
           <t>้อยกว่า 116,600 ลบ. จากการนําเข้า</t>
@@ -15168,11 +13388,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F447" t="inlineStr">
-        <is>
-          <t>41,170</t>
-        </is>
-      </c>
+      <c r="F447" t="inlineStr"/>
       <c r="G447" t="inlineStr"/>
       <c r="H447" t="inlineStr">
         <is>
@@ -15200,11 +13416,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F448" t="inlineStr">
-        <is>
-          <t>1,247.0</t>
-        </is>
-      </c>
+      <c r="F448" t="inlineStr"/>
       <c r="G448" t="inlineStr"/>
       <c r="H448" t="inlineStr"/>
     </row>
@@ -15230,14 +13442,10 @@
       </c>
       <c r="F449" s="2" t="inlineStr">
         <is>
-          <t>3,000.0000</t>
-        </is>
-      </c>
-      <c r="G449" s="2" t="inlineStr">
-        <is>
-          <t>ใช่</t>
-        </is>
-      </c>
+          <t>0.3000</t>
+        </is>
+      </c>
+      <c r="G449" s="2" t="inlineStr"/>
       <c r="H449" s="2" t="inlineStr">
         <is>
           <t>้อยกว่า 3,000 ล้านบาท</t>
@@ -15264,11 +13472,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F450" t="inlineStr">
-        <is>
-          <t>895.7</t>
-        </is>
-      </c>
+      <c r="F450" t="inlineStr"/>
       <c r="G450" t="inlineStr"/>
       <c r="H450" t="inlineStr"/>
     </row>
@@ -15292,11 +13496,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F451" t="inlineStr">
-        <is>
-          <t>23,497</t>
-        </is>
-      </c>
+      <c r="F451" t="inlineStr"/>
       <c r="G451" t="inlineStr"/>
       <c r="H451" t="inlineStr">
         <is>
@@ -15324,11 +13524,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F452" t="inlineStr">
-        <is>
-          <t>4,228</t>
-        </is>
-      </c>
+      <c r="F452" t="inlineStr"/>
       <c r="G452" t="inlineStr"/>
       <c r="H452" t="inlineStr">
         <is>
@@ -15356,11 +13552,7 @@
           <t>ไม่ทราบหน่วย</t>
         </is>
       </c>
-      <c r="F453" t="inlineStr">
-        <is>
-          <t>4,228</t>
-        </is>
-      </c>
+      <c r="F453" t="inlineStr"/>
       <c r="G453" t="inlineStr"/>
       <c r="H453" t="inlineStr">
         <is>
@@ -15388,11 +13580,7 @@
           <t>จำนวน (นับ)</t>
         </is>
       </c>
-      <c r="F454" t="inlineStr">
-        <is>
-          <t>6,592</t>
-        </is>
-      </c>
+      <c r="F454" t="inlineStr"/>
       <c r="G454" t="inlineStr"/>
       <c r="H454" t="inlineStr">
         <is>
